--- a/gsmarena_new_2026-06-03.xlsx
+++ b/gsmarena_new_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK66"/>
+  <dimension ref="A1:DK88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15705,51 +15705,35 @@
           <t>2020, November 22. Released 2020, November 23</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H46" t="n">
+        <v>2020</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>165.6</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+      <c r="J46" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9.1</v>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="N46" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="O46" t="n">
+        <v>720</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>269</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -15761,20 +15745,14 @@
           <t>2GB | 3GB | 4GB</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T46" t="n">
+        <v>13</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>5000</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -16062,51 +16040,35 @@
           <t>2020, September 01. Released 2020, September 07</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H47" t="n">
+        <v>2020</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>165.6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+      <c r="J47" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9.1</v>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="N47" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="O47" t="n">
+        <v>720</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>269</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -16118,20 +16080,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T47" t="n">
+        <v>13</v>
+      </c>
+      <c r="U47" t="n">
+        <v>8</v>
+      </c>
+      <c r="V47" t="n">
+        <v>5000</v>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
@@ -16419,51 +16375,35 @@
           <t>2020, October 03. Released 2020, October 16</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H48" t="n">
+        <v>2020</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>171.2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
+      <c r="J48" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="K48" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9.4</v>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="N48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>720</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>263</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -16475,20 +16415,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T48" t="n">
+        <v>13</v>
+      </c>
+      <c r="U48" t="n">
+        <v>8</v>
+      </c>
+      <c r="V48" t="n">
+        <v>6000</v>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -16776,55 +16710,37 @@
           <t>2020, October 10. Released 2020, October 16</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H49" t="n">
+        <v>2020</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>170.9</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="J49" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M49" t="n">
+        <v>207</v>
+      </c>
+      <c r="N49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O49" t="n">
+        <v>720</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>263</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -16836,30 +16752,20 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
+      <c r="T49" t="n">
+        <v>64</v>
+      </c>
+      <c r="U49" t="n">
+        <v>16</v>
+      </c>
+      <c r="V49" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.82</v>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
@@ -17145,51 +17051,35 @@
           <t>2020, July 30. Released 2020, August 06</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H50" t="n">
+        <v>2020</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>174.7</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
+      <c r="J50" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="N50" t="n">
+        <v>7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>720</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>256</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -17201,20 +17091,14 @@
           <t>2GB | 3GB</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T50" t="n">
+        <v>13</v>
+      </c>
+      <c r="U50" t="n">
+        <v>8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>6000</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -17502,51 +17386,35 @@
           <t>2020, September 25. Released 2020, September 25</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H51" t="n">
+        <v>2020</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>170.8</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
+      <c r="J51" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="K51" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="N51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>720</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>263</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -17558,20 +17426,14 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T51" t="n">
+        <v>16</v>
+      </c>
+      <c r="U51" t="n">
+        <v>8</v>
+      </c>
+      <c r="V51" t="n">
+        <v>5000</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -17863,55 +17725,37 @@
           <t>2020, September 04. Released 2020, September 04</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H52" t="n">
+        <v>2020</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>170.6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>6.85</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2460</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
+      <c r="J52" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="K52" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>210</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2460</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>392</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -17923,30 +17767,20 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="T52" t="n">
+        <v>64</v>
+      </c>
+      <c r="U52" t="n">
+        <v>48</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4500</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.88</v>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
@@ -18268,51 +18102,35 @@
           <t>2020, July 07. Released 2020, July 23</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H53" t="n">
+        <v>2020</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>174.9</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
+      <c r="J53" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="K53" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="N53" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>720</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>256</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -18324,20 +18142,14 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T53" t="n">
+        <v>16</v>
+      </c>
+      <c r="U53" t="n">
+        <v>16</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6000</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -18613,51 +18425,35 @@
           <t>2020, July 24. Released 2020, July 24</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H54" t="n">
+        <v>2020</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
+      <c r="J54" t="n">
+        <v>160</v>
+      </c>
+      <c r="K54" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>9.5</v>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="N54" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" t="n">
+        <v>480</v>
+      </c>
+      <c r="P54" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>179</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -18669,20 +18465,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>8</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5000</v>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -18958,51 +18748,35 @@
           <t>2020, July 07. Released 2020, July 23</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H55" t="n">
+        <v>2020</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>174.9</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
+      <c r="J55" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="N55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>720</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>256</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -19014,20 +18788,14 @@
           <t>3GB</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="T55" t="n">
+        <v>13</v>
+      </c>
+      <c r="U55" t="n">
+        <v>8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6000</v>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -19307,55 +19075,37 @@
           <t>2020, June 17. Released 2020, June 23</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H56" t="n">
+        <v>2020</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>174.9</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="J56" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>220</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>720</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>256</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -19367,30 +19117,20 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
+      <c r="T56" t="n">
+        <v>16</v>
+      </c>
+      <c r="U56" t="n">
+        <v>16</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.8</v>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
@@ -19688,51 +19428,35 @@
           <t>2020, May 05. Released 2020, July</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H57" t="n">
+        <v>2020</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>174.6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>79.3</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+      <c r="J57" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="K57" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9.1</v>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="N57" t="n">
+        <v>7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>720</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1640</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>256</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -19744,20 +19468,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T57" t="n">
+        <v>13</v>
+      </c>
+      <c r="U57" t="n">
+        <v>8</v>
+      </c>
+      <c r="V57" t="n">
+        <v>5000</v>
       </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -20033,51 +19751,35 @@
           <t>2020, July 13. Released 2020, July 13</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H58" t="n">
+        <v>2020</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>164.7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
+      <c r="J58" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="K58" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="N58" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>720</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>266</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -20089,20 +19791,14 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T58" t="n">
+        <v>16</v>
+      </c>
+      <c r="U58" t="n">
+        <v>8</v>
+      </c>
+      <c r="V58" t="n">
+        <v>5000</v>
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -20386,51 +20082,35 @@
           <t>2020, May 04. Released 2020, May 26</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H59" t="n">
+        <v>2020</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>164.7</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>76.3</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
+      <c r="J59" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="L59" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="N59" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O59" t="n">
+        <v>720</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>266</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -20442,20 +20122,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T59" t="n">
+        <v>13</v>
+      </c>
+      <c r="U59" t="n">
+        <v>8</v>
+      </c>
+      <c r="V59" t="n">
+        <v>5000</v>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -20743,55 +20417,37 @@
           <t>2020, April 13. Released 2020, April 13</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H60" t="n">
+        <v>2020</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>163.3</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>77.7</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J60" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>203</v>
+      </c>
+      <c r="N60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>390</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -20803,20 +20459,14 @@
           <t>6GB</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
+      <c r="T60" t="n">
+        <v>64</v>
+      </c>
+      <c r="U60" t="n">
+        <v>32</v>
+      </c>
+      <c r="V60" t="n">
+        <v>4000</v>
       </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -21096,51 +20746,35 @@
           <t>2020, April 13. Released 2020, April 13</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H61" t="n">
+        <v>2020</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J61" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9</v>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="N61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O61" t="n">
+        <v>720</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>266</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -21152,20 +20786,14 @@
           <t>3GB</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T61" t="n">
+        <v>48</v>
+      </c>
+      <c r="U61" t="n">
+        <v>8</v>
+      </c>
+      <c r="V61" t="n">
+        <v>5000</v>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -21453,55 +21081,37 @@
           <t>2020, February 21. Released 2020, February 25</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H62" t="n">
+        <v>2020</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>163.3</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>77.7</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
+      <c r="J62" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>203</v>
+      </c>
+      <c r="N62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>390</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -21513,30 +21123,20 @@
           <t>6GB</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+      <c r="T62" t="n">
+        <v>48</v>
+      </c>
+      <c r="U62" t="n">
+        <v>32</v>
+      </c>
+      <c r="V62" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.79</v>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
@@ -21826,55 +21426,37 @@
           <t>2020, February 21. Released 2020, February 25</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="H63" t="n">
+        <v>2020</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>164.1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
+      <c r="J63" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="L63" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M63" t="n">
+        <v>196</v>
+      </c>
+      <c r="N63" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O63" t="n">
+        <v>720</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>266</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -21886,30 +21468,20 @@
           <t>4GB</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
+      <c r="T63" t="n">
+        <v>48</v>
+      </c>
+      <c r="U63" t="n">
+        <v>16</v>
+      </c>
+      <c r="V63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.82</v>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
@@ -22203,55 +21775,37 @@
           <t>2019, October. Released 2019, October</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H64" t="n">
+        <v>2019</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>164.2</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
+      <c r="J64" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="L64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M64" t="n">
+        <v>181</v>
+      </c>
+      <c r="N64" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O64" t="n">
+        <v>720</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>268</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -22263,20 +21817,14 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
+      <c r="T64" t="n">
+        <v>16</v>
+      </c>
+      <c r="U64" t="n">
+        <v>8</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4000</v>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -22556,55 +22104,37 @@
           <t>2019, December. Released 2019, December</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H65" t="n">
+        <v>2019</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>166.7</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>180.5</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="J65" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="K65" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L65" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M65" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="O65" t="n">
+        <v>720</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>269</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -22616,20 +22146,14 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
+      <c r="T65" t="n">
+        <v>8</v>
+      </c>
+      <c r="U65" t="n">
+        <v>8</v>
+      </c>
+      <c r="V65" t="n">
+        <v>4000</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -23010,6 +22534,7080 @@
       <c r="DJ66" t="inlineStr"/>
       <c r="DK66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ulefone Armor X</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/ulefone_armor_x-10037.php</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2018, April. Released 2018, April</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2GB</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Li-Po 5500 mAh</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Drop resistant up to 1.2m MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>163 x 76.6 x 13.9 mm (6.42 x 3.02 x 0.55 in)</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>256 g (9.03 oz)</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>4.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n, dual-band</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>720 x 1440 pixels, 18:9 ratio (~293 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>5.5 inches, 78.1 cm 2 (~62.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr"/>
+      <c r="BA67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr"/>
+      <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr"/>
+      <c r="BJ67" t="inlineStr"/>
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM67" t="inlineStr">
+        <is>
+          <t>2018, April. Released 2018, April</t>
+        </is>
+      </c>
+      <c r="BN67" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO67" t="inlineStr">
+        <is>
+          <t>8 MP, f/1.8, (wide), AF 5 MP</t>
+        </is>
+      </c>
+      <c r="BP67" t="inlineStr">
+        <is>
+          <t>Dual-LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="BQ67" t="inlineStr"/>
+      <c r="BR67" t="inlineStr"/>
+      <c r="BS67" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT67" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU67" t="inlineStr"/>
+      <c r="BV67" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BW67" t="inlineStr">
+        <is>
+          <t>16GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BX67" t="inlineStr"/>
+      <c r="BY67" t="inlineStr">
+        <is>
+          <t>Dark Gray, Rose Gold</t>
+        </is>
+      </c>
+      <c r="BZ67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr"/>
+      <c r="CB67" t="inlineStr"/>
+      <c r="CC67" t="inlineStr"/>
+      <c r="CD67" t="inlineStr"/>
+      <c r="CE67" t="inlineStr"/>
+      <c r="CF67" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG67" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH67" t="inlineStr">
+        <is>
+          <t>1, 3, 7, 8, 20</t>
+        </is>
+      </c>
+      <c r="CI67" t="inlineStr"/>
+      <c r="CJ67" t="inlineStr"/>
+      <c r="CK67" t="inlineStr"/>
+      <c r="CL67" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/5.76 Mbps, LTE Cat4 150/75 Mbps</t>
+        </is>
+      </c>
+      <c r="CM67" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN67" t="inlineStr"/>
+      <c r="CO67" t="inlineStr">
+        <is>
+          <t>Quad-core 1.5 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP67" t="inlineStr">
+        <is>
+          <t>Mediatek MT6739 (28 nm)</t>
+        </is>
+      </c>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>PowerVR GE8100</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>Android 8.1 (Oreo)</t>
+        </is>
+      </c>
+      <c r="CS67" t="inlineStr"/>
+      <c r="CT67" t="inlineStr">
+        <is>
+          <t>5 MP</t>
+        </is>
+      </c>
+      <c r="CU67" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="CV67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW67" t="inlineStr"/>
+      <c r="CX67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY67" t="inlineStr"/>
+      <c r="CZ67" t="inlineStr"/>
+      <c r="DA67" t="inlineStr"/>
+      <c r="DB67" t="inlineStr"/>
+      <c r="DC67" t="inlineStr"/>
+      <c r="DD67" t="inlineStr"/>
+      <c r="DE67" t="inlineStr"/>
+      <c r="DF67" t="inlineStr"/>
+      <c r="DG67" t="inlineStr"/>
+      <c r="DH67" t="inlineStr"/>
+      <c r="DI67" t="inlineStr"/>
+      <c r="DJ67" t="inlineStr"/>
+      <c r="DK67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unnecto</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unnecto Rush</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/unnecto_rush-6710.php</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2014, September. Released 2014, September</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Up to 750 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Up to 15 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Li-Ion 2000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>148 x 74 x 9 mm (5.83 x 2.91 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Dual SIM (dual stand-by)</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>180 g (6.35 oz)</t>
+        </is>
+      </c>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>2.1, EDR</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>720 x 1280 pixels, 16:9 ratio (~294 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>5.0 inches, 68.9 cm 2 (~62.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr"/>
+      <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr"/>
+      <c r="BJ68" t="inlineStr"/>
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM68" t="inlineStr">
+        <is>
+          <t>2014, September. Released 2014, September</t>
+        </is>
+      </c>
+      <c r="BN68" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO68" t="inlineStr"/>
+      <c r="BP68" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ68" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="BR68" t="inlineStr"/>
+      <c r="BS68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT68" t="inlineStr"/>
+      <c r="BU68" t="inlineStr"/>
+      <c r="BV68" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW68" t="inlineStr">
+        <is>
+          <t>4GB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BX68" t="inlineStr"/>
+      <c r="BY68" t="inlineStr">
+        <is>
+          <t>Black, White, Blue</t>
+        </is>
+      </c>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr"/>
+      <c r="CB68" t="inlineStr"/>
+      <c r="CC68" t="inlineStr"/>
+      <c r="CD68" t="inlineStr"/>
+      <c r="CE68" t="inlineStr"/>
+      <c r="CF68" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG68" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH68" t="inlineStr"/>
+      <c r="CI68" t="inlineStr"/>
+      <c r="CJ68" t="inlineStr"/>
+      <c r="CK68" t="inlineStr"/>
+      <c r="CL68" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/11.5 Mbps</t>
+        </is>
+      </c>
+      <c r="CM68" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN68" t="inlineStr"/>
+      <c r="CO68" t="inlineStr">
+        <is>
+          <t>Quad-core 1.3 GHz</t>
+        </is>
+      </c>
+      <c r="CP68" t="inlineStr"/>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>Mali-400</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="CS68" t="inlineStr"/>
+      <c r="CT68" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU68" t="inlineStr"/>
+      <c r="CV68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW68" t="inlineStr"/>
+      <c r="CX68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY68" t="inlineStr"/>
+      <c r="CZ68" t="inlineStr"/>
+      <c r="DA68" t="inlineStr"/>
+      <c r="DB68" t="inlineStr"/>
+      <c r="DC68" t="inlineStr"/>
+      <c r="DD68" t="inlineStr"/>
+      <c r="DE68" t="inlineStr"/>
+      <c r="DF68" t="inlineStr"/>
+      <c r="DG68" t="inlineStr"/>
+      <c r="DH68" t="inlineStr"/>
+      <c r="DI68" t="inlineStr"/>
+      <c r="DJ68" t="inlineStr"/>
+      <c r="DK68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unnecto</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unnecto Quattro Z</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/unnecto_quattro_z-6455.php</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2014, June. Released 2014, June</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Up to 600 h</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Up to 11 h</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>125.5 x 65 x 9.4 mm (4.94 x 2.56 x 0.37 in)</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Dual SIM (dual stand-by)</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>110 g (3.88 oz)</t>
+        </is>
+      </c>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct, hotspot</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~55.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr"/>
+      <c r="BA69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
+      <c r="BJ69" t="inlineStr"/>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr"/>
+      <c r="BM69" t="inlineStr">
+        <is>
+          <t>2014, June. Released 2014, June</t>
+        </is>
+      </c>
+      <c r="BN69" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO69" t="inlineStr"/>
+      <c r="BP69" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ69" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="BR69" t="inlineStr"/>
+      <c r="BS69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT69" t="inlineStr"/>
+      <c r="BU69" t="inlineStr"/>
+      <c r="BV69" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW69" t="inlineStr">
+        <is>
+          <t>4GB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BX69" t="inlineStr"/>
+      <c r="BY69" t="inlineStr">
+        <is>
+          <t>Black, White, Blue</t>
+        </is>
+      </c>
+      <c r="BZ69" t="inlineStr"/>
+      <c r="CA69" t="inlineStr"/>
+      <c r="CB69" t="inlineStr"/>
+      <c r="CC69" t="inlineStr"/>
+      <c r="CD69" t="inlineStr"/>
+      <c r="CE69" t="inlineStr"/>
+      <c r="CF69" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG69" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH69" t="inlineStr"/>
+      <c r="CI69" t="inlineStr"/>
+      <c r="CJ69" t="inlineStr"/>
+      <c r="CK69" t="inlineStr"/>
+      <c r="CL69" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="CM69" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN69" t="inlineStr"/>
+      <c r="CO69" t="inlineStr">
+        <is>
+          <t>Dual-core 1.2 GHz</t>
+        </is>
+      </c>
+      <c r="CP69" t="inlineStr"/>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>Mali-400</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>Android 4.2.2 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="CS69" t="inlineStr"/>
+      <c r="CT69" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU69" t="inlineStr"/>
+      <c r="CV69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW69" t="inlineStr"/>
+      <c r="CX69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY69" t="inlineStr"/>
+      <c r="CZ69" t="inlineStr"/>
+      <c r="DA69" t="inlineStr"/>
+      <c r="DB69" t="inlineStr"/>
+      <c r="DC69" t="inlineStr"/>
+      <c r="DD69" t="inlineStr"/>
+      <c r="DE69" t="inlineStr"/>
+      <c r="DF69" t="inlineStr"/>
+      <c r="DG69" t="inlineStr"/>
+      <c r="DH69" t="inlineStr"/>
+      <c r="DI69" t="inlineStr"/>
+      <c r="DJ69" t="inlineStr"/>
+      <c r="DK69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unnecto</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unnecto Drone Z</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/unnecto_drone_z-6454.php</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2014, June. Released 2014, June</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Up to 450 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Up to 9 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>116 x 61 x 11.5 mm (4.57 x 2.40 x 0.45 in)</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Dual SIM (dual stand-by)</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>100 g (3.53 oz)</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>320 x 480 pixels, 3:2 ratio (~165 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>3.5 inches, 36.5 cm 2 (~51.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr"/>
+      <c r="BA70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
+      <c r="BH70" t="inlineStr"/>
+      <c r="BI70" t="inlineStr"/>
+      <c r="BJ70" t="inlineStr"/>
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="inlineStr"/>
+      <c r="BM70" t="inlineStr">
+        <is>
+          <t>2014, June. Released 2014, June</t>
+        </is>
+      </c>
+      <c r="BN70" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO70" t="inlineStr"/>
+      <c r="BP70" t="inlineStr"/>
+      <c r="BQ70" t="inlineStr">
+        <is>
+          <t>3.15 MP</t>
+        </is>
+      </c>
+      <c r="BR70" t="inlineStr"/>
+      <c r="BS70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT70" t="inlineStr"/>
+      <c r="BU70" t="inlineStr"/>
+      <c r="BV70" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW70" t="inlineStr">
+        <is>
+          <t>512MB 256MB RAM</t>
+        </is>
+      </c>
+      <c r="BX70" t="inlineStr"/>
+      <c r="BY70" t="inlineStr">
+        <is>
+          <t>Black, White, Grey</t>
+        </is>
+      </c>
+      <c r="BZ70" t="inlineStr"/>
+      <c r="CA70" t="inlineStr"/>
+      <c r="CB70" t="inlineStr"/>
+      <c r="CC70" t="inlineStr"/>
+      <c r="CD70" t="inlineStr"/>
+      <c r="CE70" t="inlineStr"/>
+      <c r="CF70" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG70" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH70" t="inlineStr"/>
+      <c r="CI70" t="inlineStr"/>
+      <c r="CJ70" t="inlineStr"/>
+      <c r="CK70" t="inlineStr"/>
+      <c r="CL70" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="CM70" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN70" t="inlineStr"/>
+      <c r="CO70" t="inlineStr">
+        <is>
+          <t>Dual-core 1.0 GHz</t>
+        </is>
+      </c>
+      <c r="CP70" t="inlineStr"/>
+      <c r="CQ70" t="inlineStr"/>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>Android 4.2.2 (Jelly Bean)</t>
+        </is>
+      </c>
+      <c r="CS70" t="inlineStr"/>
+      <c r="CT70" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU70" t="inlineStr"/>
+      <c r="CV70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW70" t="inlineStr"/>
+      <c r="CX70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY70" t="inlineStr"/>
+      <c r="CZ70" t="inlineStr"/>
+      <c r="DA70" t="inlineStr"/>
+      <c r="DB70" t="inlineStr"/>
+      <c r="DC70" t="inlineStr"/>
+      <c r="DD70" t="inlineStr"/>
+      <c r="DE70" t="inlineStr"/>
+      <c r="DF70" t="inlineStr"/>
+      <c r="DG70" t="inlineStr"/>
+      <c r="DH70" t="inlineStr"/>
+      <c r="DI70" t="inlineStr"/>
+      <c r="DJ70" t="inlineStr"/>
+      <c r="DK70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>verykool s4010 Gazelle</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_s4010_gazelle-6994.php</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2015, January. Released 2015, January</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Up to 336 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Up to 6 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Li-Ion 1400 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>127.5 x 64.9 x 11 mm (5.02 x 2.56 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM)</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>128 g (4.52 oz)</t>
+        </is>
+      </c>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>4.0, LE</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~55.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr"/>
+      <c r="BA71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM71" t="inlineStr">
+        <is>
+          <t>2015, January. Released 2015, January</t>
+        </is>
+      </c>
+      <c r="BN71" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO71" t="inlineStr"/>
+      <c r="BP71" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ71" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="BR71" t="inlineStr"/>
+      <c r="BS71" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT71" t="inlineStr"/>
+      <c r="BU71" t="inlineStr"/>
+      <c r="BV71" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW71" t="inlineStr">
+        <is>
+          <t>4GB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BX71" t="inlineStr"/>
+      <c r="BY71" t="inlineStr">
+        <is>
+          <t>White, Blue, Grey</t>
+        </is>
+      </c>
+      <c r="BZ71" t="inlineStr"/>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="CB71" t="inlineStr"/>
+      <c r="CC71" t="inlineStr">
+        <is>
+          <t>0.66 W/kg (head)     1.38 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD71" t="inlineStr"/>
+      <c r="CE71" t="inlineStr"/>
+      <c r="CF71" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG71" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1700 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH71" t="inlineStr"/>
+      <c r="CI71" t="inlineStr"/>
+      <c r="CJ71" t="inlineStr"/>
+      <c r="CK71" t="inlineStr"/>
+      <c r="CL71" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="CM71" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN71" t="inlineStr"/>
+      <c r="CO71" t="inlineStr">
+        <is>
+          <t>Dual-core 1.0 GHz Cortex-A7</t>
+        </is>
+      </c>
+      <c r="CP71" t="inlineStr">
+        <is>
+          <t>Mediatek MT6572M (28 nm)</t>
+        </is>
+      </c>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>Mali-400</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="CS71" t="inlineStr"/>
+      <c r="CT71" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="CU71" t="inlineStr"/>
+      <c r="CV71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW71" t="inlineStr"/>
+      <c r="CX71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY71" t="inlineStr"/>
+      <c r="CZ71" t="inlineStr"/>
+      <c r="DA71" t="inlineStr"/>
+      <c r="DB71" t="inlineStr"/>
+      <c r="DC71" t="inlineStr"/>
+      <c r="DD71" t="inlineStr"/>
+      <c r="DE71" t="inlineStr"/>
+      <c r="DF71" t="inlineStr"/>
+      <c r="DG71" t="inlineStr"/>
+      <c r="DH71" t="inlineStr"/>
+      <c r="DI71" t="inlineStr"/>
+      <c r="DJ71" t="inlineStr"/>
+      <c r="DK71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>verykool s4002 Leo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_s4002_leo-6993.php</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2015, January. Released 2015, January</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>About 50 EUR</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Up to 240 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Up to 7 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Li-Ion 1450 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>122 x 63 x 10.7 mm (4.80 x 2.48 x 0.42 in)</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM)</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>112 g (3.95 oz)</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>4.0, LE</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~59.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM72" t="inlineStr">
+        <is>
+          <t>2015, January. Released 2015, January</t>
+        </is>
+      </c>
+      <c r="BN72" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO72" t="inlineStr"/>
+      <c r="BP72" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ72" t="inlineStr">
+        <is>
+          <t>5 MP</t>
+        </is>
+      </c>
+      <c r="BR72" t="inlineStr"/>
+      <c r="BS72" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT72" t="inlineStr"/>
+      <c r="BU72" t="inlineStr"/>
+      <c r="BV72" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW72" t="inlineStr">
+        <is>
+          <t>512MB 256MB RAM</t>
+        </is>
+      </c>
+      <c r="BX72" t="inlineStr"/>
+      <c r="BY72" t="inlineStr">
+        <is>
+          <t>Black, White, Yellow, Blue</t>
+        </is>
+      </c>
+      <c r="BZ72" t="inlineStr"/>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>About 50 EUR</t>
+        </is>
+      </c>
+      <c r="CB72" t="inlineStr"/>
+      <c r="CC72" t="inlineStr">
+        <is>
+          <t>0.49 W/kg (head)     0.74 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD72" t="inlineStr"/>
+      <c r="CE72" t="inlineStr"/>
+      <c r="CF72" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG72" t="inlineStr"/>
+      <c r="CH72" t="inlineStr"/>
+      <c r="CI72" t="inlineStr"/>
+      <c r="CJ72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CL72" t="inlineStr"/>
+      <c r="CM72" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN72" t="inlineStr"/>
+      <c r="CO72" t="inlineStr">
+        <is>
+          <t>Dual-core 1.3 GHz Cortex-A7</t>
+        </is>
+      </c>
+      <c r="CP72" t="inlineStr">
+        <is>
+          <t>Mediatek MT6571E</t>
+        </is>
+      </c>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>Mali-400</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="CS72" t="inlineStr"/>
+      <c r="CT72" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="CU72" t="inlineStr"/>
+      <c r="CV72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW72" t="inlineStr"/>
+      <c r="CX72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY72" t="inlineStr"/>
+      <c r="CZ72" t="inlineStr"/>
+      <c r="DA72" t="inlineStr"/>
+      <c r="DB72" t="inlineStr"/>
+      <c r="DC72" t="inlineStr"/>
+      <c r="DD72" t="inlineStr"/>
+      <c r="DE72" t="inlineStr"/>
+      <c r="DF72" t="inlineStr"/>
+      <c r="DG72" t="inlineStr"/>
+      <c r="DH72" t="inlineStr"/>
+      <c r="DI72" t="inlineStr"/>
+      <c r="DJ72" t="inlineStr"/>
+      <c r="DK72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>verykool s3501 Lynx</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_s3501_lynx-6786.php</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2014, November. Released 2014, November</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>113.4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>60.2</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>256MB</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Up to 120 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Up to 3 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>113.4 x 60.2 x 12.5 mm (4.46 x 2.37 x 0.49 in)</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM/ Micro-SIM)</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>88.5 g (3.14 oz)</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>320 x 480 pixels, 3:2 ratio (~165 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>3.5 inches, 36.5 cm 2 (~53.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM73" t="inlineStr">
+        <is>
+          <t>2014, November. Released 2014, November</t>
+        </is>
+      </c>
+      <c r="BN73" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO73" t="inlineStr"/>
+      <c r="BP73" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ73" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR73" t="inlineStr"/>
+      <c r="BS73" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT73" t="inlineStr"/>
+      <c r="BU73" t="inlineStr"/>
+      <c r="BV73" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW73" t="inlineStr">
+        <is>
+          <t>512MB 256MB RAM</t>
+        </is>
+      </c>
+      <c r="BX73" t="inlineStr"/>
+      <c r="BY73" t="inlineStr">
+        <is>
+          <t>Yellow, Blue</t>
+        </is>
+      </c>
+      <c r="BZ73" t="inlineStr"/>
+      <c r="CA73" t="inlineStr"/>
+      <c r="CB73" t="inlineStr"/>
+      <c r="CC73" t="inlineStr"/>
+      <c r="CD73" t="inlineStr"/>
+      <c r="CE73" t="inlineStr"/>
+      <c r="CF73" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG73" t="inlineStr"/>
+      <c r="CH73" t="inlineStr"/>
+      <c r="CI73" t="inlineStr"/>
+      <c r="CJ73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CL73" t="inlineStr"/>
+      <c r="CM73" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN73" t="inlineStr"/>
+      <c r="CO73" t="inlineStr">
+        <is>
+          <t>Dual-core 1.3 GHz Cortex-A7</t>
+        </is>
+      </c>
+      <c r="CP73" t="inlineStr">
+        <is>
+          <t>Mediatek MT6571 (28 nm)</t>
+        </is>
+      </c>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>Mali-400</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="CS73" t="inlineStr"/>
+      <c r="CT73" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU73" t="inlineStr"/>
+      <c r="CV73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW73" t="inlineStr"/>
+      <c r="CX73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY73" t="inlineStr"/>
+      <c r="CZ73" t="inlineStr"/>
+      <c r="DA73" t="inlineStr"/>
+      <c r="DB73" t="inlineStr"/>
+      <c r="DC73" t="inlineStr"/>
+      <c r="DD73" t="inlineStr"/>
+      <c r="DE73" t="inlineStr"/>
+      <c r="DF73" t="inlineStr"/>
+      <c r="DG73" t="inlineStr"/>
+      <c r="DH73" t="inlineStr"/>
+      <c r="DI73" t="inlineStr"/>
+      <c r="DJ73" t="inlineStr"/>
+      <c r="DK73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>verykool R27</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_r27-6772.php</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2014, September. Released 2014, October</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>111.4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>128MB | 32MB</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>32MB</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Up to 216 h</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Li-Ion 900 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>IP65 dust tight and water resistant (low pressure water jets) Flashlight</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>111.4 x 51.5 x 15.6 mm (4.39 x 2.03 x 0.61 in)</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>110 g (3.88 oz)</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>2.1, A2DP, EDR</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, built-in antenna</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>Scratch-resistant glass</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels (~128 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.2 cm 2 (~26.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr"/>
+      <c r="BA74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr"/>
+      <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>MP3/WAV/MP4 player Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr"/>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL74" t="inlineStr"/>
+      <c r="BM74" t="inlineStr">
+        <is>
+          <t>2014, September. Released 2014, October</t>
+        </is>
+      </c>
+      <c r="BN74" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO74" t="inlineStr"/>
+      <c r="BP74" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ74" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR74" t="inlineStr"/>
+      <c r="BS74" t="inlineStr">
+        <is>
+          <t>144p</t>
+        </is>
+      </c>
+      <c r="BT74" t="inlineStr"/>
+      <c r="BU74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV74" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW74" t="inlineStr">
+        <is>
+          <t>128MB ROM, 32MB RAM</t>
+        </is>
+      </c>
+      <c r="BX74" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="BY74" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ74" t="inlineStr"/>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="CB74" t="inlineStr">
+        <is>
+          <t>1.33 W/kg (head)     1.28 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC74" t="inlineStr"/>
+      <c r="CD74" t="inlineStr"/>
+      <c r="CE74" t="inlineStr"/>
+      <c r="CF74" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG74" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900</t>
+        </is>
+      </c>
+      <c r="CH74" t="inlineStr"/>
+      <c r="CI74" t="inlineStr"/>
+      <c r="CJ74" t="inlineStr"/>
+      <c r="CK74" t="inlineStr"/>
+      <c r="CL74" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="CM74" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN74" t="inlineStr"/>
+      <c r="CO74" t="inlineStr"/>
+      <c r="CP74" t="inlineStr"/>
+      <c r="CQ74" t="inlineStr"/>
+      <c r="CR74" t="inlineStr"/>
+      <c r="CS74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT74" t="inlineStr"/>
+      <c r="CU74" t="inlineStr"/>
+      <c r="CV74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW74" t="inlineStr"/>
+      <c r="CX74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY74" t="inlineStr"/>
+      <c r="CZ74" t="inlineStr"/>
+      <c r="DA74" t="inlineStr"/>
+      <c r="DB74" t="inlineStr"/>
+      <c r="DC74" t="inlineStr"/>
+      <c r="DD74" t="inlineStr"/>
+      <c r="DE74" t="inlineStr"/>
+      <c r="DF74" t="inlineStr"/>
+      <c r="DG74" t="inlineStr"/>
+      <c r="DH74" t="inlineStr"/>
+      <c r="DI74" t="inlineStr"/>
+      <c r="DJ74" t="inlineStr"/>
+      <c r="DK74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>verykool s5511 Juno Quatro</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_s5511_juno_quatro-6760.php</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2014, October. Released 2014, October</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>150.4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Up to 240 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Up to 7 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Li-Ion 2300 mAh, removable</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>150.4 x 77.2 x 8.5 mm (5.92 x 3.04 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM/ Micro-SIM)</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>157 g (5.54 oz)</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>4.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, hotspot</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>540 x 960 pixels, 16:9 ratio (~200 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>5.5 inches, 83.4 cm 2 (~71.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr"/>
+      <c r="BA75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr"/>
+      <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
+      <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr"/>
+      <c r="BJ75" t="inlineStr"/>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM75" t="inlineStr">
+        <is>
+          <t>2014, October. Released 2014, October</t>
+        </is>
+      </c>
+      <c r="BN75" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO75" t="inlineStr"/>
+      <c r="BP75" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ75" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="BR75" t="inlineStr"/>
+      <c r="BS75" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT75" t="inlineStr"/>
+      <c r="BU75" t="inlineStr"/>
+      <c r="BV75" t="inlineStr">
+        <is>
+          <t>microSDHC</t>
+        </is>
+      </c>
+      <c r="BW75" t="inlineStr">
+        <is>
+          <t>4GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BX75" t="inlineStr"/>
+      <c r="BY75" t="inlineStr">
+        <is>
+          <t>Yellow, Blue</t>
+        </is>
+      </c>
+      <c r="BZ75" t="inlineStr"/>
+      <c r="CA75" t="inlineStr"/>
+      <c r="CB75" t="inlineStr"/>
+      <c r="CC75" t="inlineStr"/>
+      <c r="CD75" t="inlineStr"/>
+      <c r="CE75" t="inlineStr"/>
+      <c r="CF75" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG75" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900</t>
+        </is>
+      </c>
+      <c r="CH75" t="inlineStr"/>
+      <c r="CI75" t="inlineStr"/>
+      <c r="CJ75" t="inlineStr"/>
+      <c r="CK75" t="inlineStr"/>
+      <c r="CL75" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="CM75" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN75" t="inlineStr"/>
+      <c r="CO75" t="inlineStr">
+        <is>
+          <t>Quad-core 1.3 GHz Cortex-A7</t>
+        </is>
+      </c>
+      <c r="CP75" t="inlineStr">
+        <is>
+          <t>Mediatek MT6582M (28 nm)</t>
+        </is>
+      </c>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>Mali-400MP2</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>Android 4.4.2 (KitKat)</t>
+        </is>
+      </c>
+      <c r="CS75" t="inlineStr"/>
+      <c r="CT75" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CU75" t="inlineStr"/>
+      <c r="CV75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW75" t="inlineStr"/>
+      <c r="CX75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY75" t="inlineStr"/>
+      <c r="CZ75" t="inlineStr"/>
+      <c r="DA75" t="inlineStr"/>
+      <c r="DB75" t="inlineStr"/>
+      <c r="DC75" t="inlineStr"/>
+      <c r="DD75" t="inlineStr"/>
+      <c r="DE75" t="inlineStr"/>
+      <c r="DF75" t="inlineStr"/>
+      <c r="DG75" t="inlineStr"/>
+      <c r="DH75" t="inlineStr"/>
+      <c r="DI75" t="inlineStr"/>
+      <c r="DJ75" t="inlineStr"/>
+      <c r="DK75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>verykool i604</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i604-4631.php</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2012, Q1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Up to 240 h</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Flashlight</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>118 x 49.8 x 13.5 mm (4.65 x 1.96 x 0.53 in)</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM)</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>79 g (2.79 oz)</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.4 cm 2 (~21.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr"/>
+      <c r="BA76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>SNS applications MP3/MP4/3GP player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ76" t="inlineStr"/>
+      <c r="BK76" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL76" t="inlineStr"/>
+      <c r="BM76" t="inlineStr">
+        <is>
+          <t>2012, Q1</t>
+        </is>
+      </c>
+      <c r="BN76" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO76" t="inlineStr"/>
+      <c r="BP76" t="inlineStr"/>
+      <c r="BQ76" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR76" t="inlineStr"/>
+      <c r="BS76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT76" t="inlineStr"/>
+      <c r="BU76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV76" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW76" t="inlineStr"/>
+      <c r="BX76" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="BY76" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BZ76" t="inlineStr"/>
+      <c r="CA76" t="inlineStr"/>
+      <c r="CB76" t="inlineStr"/>
+      <c r="CC76" t="inlineStr"/>
+      <c r="CD76" t="inlineStr"/>
+      <c r="CE76" t="inlineStr"/>
+      <c r="CF76" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+        </is>
+      </c>
+      <c r="CG76" t="inlineStr"/>
+      <c r="CH76" t="inlineStr"/>
+      <c r="CI76" t="inlineStr"/>
+      <c r="CJ76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK76" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL76" t="inlineStr"/>
+      <c r="CM76" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN76" t="inlineStr"/>
+      <c r="CO76" t="inlineStr"/>
+      <c r="CP76" t="inlineStr"/>
+      <c r="CQ76" t="inlineStr"/>
+      <c r="CR76" t="inlineStr"/>
+      <c r="CS76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT76" t="inlineStr"/>
+      <c r="CU76" t="inlineStr"/>
+      <c r="CV76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW76" t="inlineStr"/>
+      <c r="CX76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY76" t="inlineStr"/>
+      <c r="CZ76" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA76" t="inlineStr"/>
+      <c r="DB76" t="inlineStr"/>
+      <c r="DC76" t="inlineStr"/>
+      <c r="DD76" t="inlineStr"/>
+      <c r="DE76" t="inlineStr"/>
+      <c r="DF76" t="inlineStr"/>
+      <c r="DG76" t="inlineStr"/>
+      <c r="DH76" t="inlineStr"/>
+      <c r="DI76" t="inlineStr"/>
+      <c r="DJ76" t="inlineStr"/>
+      <c r="DK76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>verykool i125</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i125-4438.php</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2012, January. Released 2012, January</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Up to 192 h</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Flashlight</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>107 x 45 x 12 mm (4.21 x 1.77 x 0.47 in)</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM)</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>63 g (2.22 oz)</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>160 x 240 pixels, 3:2 ratio</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>1.8 inches, 9.6 cm 2 (~20.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr"/>
+      <c r="BA77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>MP3/3GP player Organizer Unit &amp; currency converter Predictive text input Voice memo</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BJ77" t="inlineStr"/>
+      <c r="BK77" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL77" t="inlineStr"/>
+      <c r="BM77" t="inlineStr">
+        <is>
+          <t>2012, January. Released 2012, January</t>
+        </is>
+      </c>
+      <c r="BN77" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO77" t="inlineStr"/>
+      <c r="BP77" t="inlineStr"/>
+      <c r="BQ77" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="BR77" t="inlineStr"/>
+      <c r="BS77" t="inlineStr"/>
+      <c r="BT77" t="inlineStr"/>
+      <c r="BU77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV77" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW77" t="inlineStr"/>
+      <c r="BX77" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="BY77" t="inlineStr">
+        <is>
+          <t>Black/Red, Black/Blue, Black/Green</t>
+        </is>
+      </c>
+      <c r="BZ77" t="inlineStr"/>
+      <c r="CA77" t="inlineStr"/>
+      <c r="CB77" t="inlineStr"/>
+      <c r="CC77" t="inlineStr"/>
+      <c r="CD77" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 2</t>
+        </is>
+      </c>
+      <c r="CE77" t="inlineStr"/>
+      <c r="CF77" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1</t>
+        </is>
+      </c>
+      <c r="CG77" t="inlineStr"/>
+      <c r="CH77" t="inlineStr"/>
+      <c r="CI77" t="inlineStr"/>
+      <c r="CJ77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CL77" t="inlineStr"/>
+      <c r="CM77" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN77" t="inlineStr"/>
+      <c r="CO77" t="inlineStr"/>
+      <c r="CP77" t="inlineStr"/>
+      <c r="CQ77" t="inlineStr"/>
+      <c r="CR77" t="inlineStr"/>
+      <c r="CS77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT77" t="inlineStr"/>
+      <c r="CU77" t="inlineStr"/>
+      <c r="CV77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW77" t="inlineStr"/>
+      <c r="CX77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY77" t="inlineStr"/>
+      <c r="CZ77" t="inlineStr"/>
+      <c r="DA77" t="inlineStr"/>
+      <c r="DB77" t="inlineStr"/>
+      <c r="DC77" t="inlineStr"/>
+      <c r="DD77" t="inlineStr"/>
+      <c r="DE77" t="inlineStr"/>
+      <c r="DF77" t="inlineStr"/>
+      <c r="DG77" t="inlineStr"/>
+      <c r="DH77" t="inlineStr"/>
+      <c r="DI77" t="inlineStr"/>
+      <c r="DJ77" t="inlineStr"/>
+      <c r="DK77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>verykool S815</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_s815-4393.php</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2011, Q4. Released 2011, December</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Up to 192 h</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>105.5 x 58 x 11.7 mm (4.15 x 2.28 x 0.46 in)</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>90 g (3.17 oz)</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>320 x 240 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~29.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr"/>
+      <c r="BA78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>SNS applications MP3/MP4/3GP player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr"/>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL78" t="inlineStr"/>
+      <c r="BM78" t="inlineStr">
+        <is>
+          <t>2011, Q4. Released 2011, December</t>
+        </is>
+      </c>
+      <c r="BN78" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO78" t="inlineStr"/>
+      <c r="BP78" t="inlineStr"/>
+      <c r="BQ78" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR78" t="inlineStr"/>
+      <c r="BS78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT78" t="inlineStr"/>
+      <c r="BU78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV78" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW78" t="inlineStr"/>
+      <c r="BX78" t="inlineStr">
+        <is>
+          <t>1000 entries</t>
+        </is>
+      </c>
+      <c r="BY78" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ78" t="inlineStr"/>
+      <c r="CA78" t="inlineStr"/>
+      <c r="CB78" t="inlineStr"/>
+      <c r="CC78" t="inlineStr"/>
+      <c r="CD78" t="inlineStr"/>
+      <c r="CE78" t="inlineStr"/>
+      <c r="CF78" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG78" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900</t>
+        </is>
+      </c>
+      <c r="CH78" t="inlineStr"/>
+      <c r="CI78" t="inlineStr"/>
+      <c r="CJ78" t="inlineStr"/>
+      <c r="CK78" t="inlineStr"/>
+      <c r="CL78" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM78" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN78" t="inlineStr"/>
+      <c r="CO78" t="inlineStr"/>
+      <c r="CP78" t="inlineStr"/>
+      <c r="CQ78" t="inlineStr"/>
+      <c r="CR78" t="inlineStr"/>
+      <c r="CS78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT78" t="inlineStr"/>
+      <c r="CU78" t="inlineStr"/>
+      <c r="CV78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW78" t="inlineStr"/>
+      <c r="CX78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY78" t="inlineStr"/>
+      <c r="CZ78" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA78" t="inlineStr"/>
+      <c r="DB78" t="inlineStr"/>
+      <c r="DC78" t="inlineStr"/>
+      <c r="DD78" t="inlineStr"/>
+      <c r="DE78" t="inlineStr"/>
+      <c r="DF78" t="inlineStr"/>
+      <c r="DG78" t="inlineStr"/>
+      <c r="DH78" t="inlineStr"/>
+      <c r="DI78" t="inlineStr"/>
+      <c r="DJ78" t="inlineStr"/>
+      <c r="DK78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>verykool R23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_r23-4368.php</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>IPX5 splash resistant</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>111 x 51.5 x 15 mm (4.37 x 2.03 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>110 g (3.88 oz)</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.2 cm 2 (~26.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr"/>
+      <c r="BA79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>MP3/MP4 player</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr"/>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL79" t="inlineStr"/>
+      <c r="BM79" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN79" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO79" t="inlineStr"/>
+      <c r="BP79" t="inlineStr"/>
+      <c r="BQ79" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR79" t="inlineStr"/>
+      <c r="BS79" t="inlineStr"/>
+      <c r="BT79" t="inlineStr"/>
+      <c r="BU79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV79" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW79" t="inlineStr"/>
+      <c r="BX79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY79" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ79" t="inlineStr"/>
+      <c r="CA79" t="inlineStr"/>
+      <c r="CB79" t="inlineStr"/>
+      <c r="CC79" t="inlineStr"/>
+      <c r="CD79" t="inlineStr"/>
+      <c r="CE79" t="inlineStr"/>
+      <c r="CF79" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG79" t="inlineStr"/>
+      <c r="CH79" t="inlineStr"/>
+      <c r="CI79" t="inlineStr"/>
+      <c r="CJ79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK79" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL79" t="inlineStr"/>
+      <c r="CM79" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN79" t="inlineStr"/>
+      <c r="CO79" t="inlineStr"/>
+      <c r="CP79" t="inlineStr"/>
+      <c r="CQ79" t="inlineStr"/>
+      <c r="CR79" t="inlineStr"/>
+      <c r="CS79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT79" t="inlineStr"/>
+      <c r="CU79" t="inlineStr"/>
+      <c r="CV79" t="inlineStr"/>
+      <c r="CW79" t="inlineStr"/>
+      <c r="CX79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY79" t="inlineStr"/>
+      <c r="CZ79" t="inlineStr"/>
+      <c r="DA79" t="inlineStr"/>
+      <c r="DB79" t="inlineStr"/>
+      <c r="DC79" t="inlineStr"/>
+      <c r="DD79" t="inlineStr"/>
+      <c r="DE79" t="inlineStr"/>
+      <c r="DF79" t="inlineStr"/>
+      <c r="DG79" t="inlineStr"/>
+      <c r="DH79" t="inlineStr"/>
+      <c r="DI79" t="inlineStr"/>
+      <c r="DJ79" t="inlineStr"/>
+      <c r="DK79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>verykool R620</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_r620-4338.php</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2011, Q3</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>115.8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>26MB</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Up to 240 h</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>IPX5 splash resistant</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>115.8 x 62 x 13.2 mm (4.56 x 2.44 x 0.52 in)</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>110 g (3.88 oz)</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>320 x 240 pixels, 4:3 ratio (~174 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>2.3 inches, 16.4 cm 2 (~22.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>MP3/MP4/3GP player Organizer Unit &amp; currency converter SNS applications Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr">
+        <is>
+          <t>2011, Q3</t>
+        </is>
+      </c>
+      <c r="BN80" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO80" t="inlineStr"/>
+      <c r="BP80" t="inlineStr"/>
+      <c r="BQ80" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR80" t="inlineStr"/>
+      <c r="BS80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT80" t="inlineStr"/>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV80" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW80" t="inlineStr">
+        <is>
+          <t>26MB</t>
+        </is>
+      </c>
+      <c r="BX80" t="inlineStr">
+        <is>
+          <t>1000 entries</t>
+        </is>
+      </c>
+      <c r="BY80" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ80" t="inlineStr"/>
+      <c r="CA80" t="inlineStr"/>
+      <c r="CB80" t="inlineStr"/>
+      <c r="CC80" t="inlineStr"/>
+      <c r="CD80" t="inlineStr"/>
+      <c r="CE80" t="inlineStr"/>
+      <c r="CF80" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG80" t="inlineStr"/>
+      <c r="CH80" t="inlineStr"/>
+      <c r="CI80" t="inlineStr"/>
+      <c r="CJ80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CL80" t="inlineStr"/>
+      <c r="CM80" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN80" t="inlineStr"/>
+      <c r="CO80" t="inlineStr"/>
+      <c r="CP80" t="inlineStr"/>
+      <c r="CQ80" t="inlineStr"/>
+      <c r="CR80" t="inlineStr"/>
+      <c r="CS80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT80" t="inlineStr"/>
+      <c r="CU80" t="inlineStr"/>
+      <c r="CV80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW80" t="inlineStr"/>
+      <c r="CX80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY80" t="inlineStr"/>
+      <c r="CZ80" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA80" t="inlineStr"/>
+      <c r="DB80" t="inlineStr"/>
+      <c r="DC80" t="inlineStr"/>
+      <c r="DD80" t="inlineStr"/>
+      <c r="DE80" t="inlineStr"/>
+      <c r="DF80" t="inlineStr"/>
+      <c r="DG80" t="inlineStr"/>
+      <c r="DH80" t="inlineStr"/>
+      <c r="DI80" t="inlineStr"/>
+      <c r="DJ80" t="inlineStr"/>
+      <c r="DK80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>verykool i285</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i285-4225.php</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2011, Q2</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>80MB</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1100 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>117 x 57 x 12.1 mm (4.61 x 2.24 x 0.48 in)</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>106 g (3.74 oz)</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~43.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>MP3/AAC+ player MP4/3GP player Organizer Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="BL81" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM81" t="inlineStr">
+        <is>
+          <t>2011, Q2</t>
+        </is>
+      </c>
+      <c r="BN81" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+      <c r="BQ81" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR81" t="inlineStr"/>
+      <c r="BS81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV81" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW81" t="inlineStr">
+        <is>
+          <t>80MB</t>
+        </is>
+      </c>
+      <c r="BX81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY81" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="BZ81" t="inlineStr"/>
+      <c r="CA81" t="inlineStr"/>
+      <c r="CB81" t="inlineStr"/>
+      <c r="CC81" t="inlineStr"/>
+      <c r="CD81" t="inlineStr"/>
+      <c r="CE81" t="inlineStr"/>
+      <c r="CF81" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG81" t="inlineStr"/>
+      <c r="CH81" t="inlineStr"/>
+      <c r="CI81" t="inlineStr"/>
+      <c r="CJ81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK81" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL81" t="inlineStr"/>
+      <c r="CM81" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN81" t="inlineStr"/>
+      <c r="CO81" t="inlineStr"/>
+      <c r="CP81" t="inlineStr"/>
+      <c r="CQ81" t="inlineStr"/>
+      <c r="CR81" t="inlineStr"/>
+      <c r="CS81" t="inlineStr"/>
+      <c r="CT81" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU81" t="inlineStr"/>
+      <c r="CV81" t="inlineStr"/>
+      <c r="CW81" t="inlineStr"/>
+      <c r="CX81" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY81" t="inlineStr"/>
+      <c r="CZ81" t="inlineStr"/>
+      <c r="DA81" t="inlineStr"/>
+      <c r="DB81" t="inlineStr"/>
+      <c r="DC81" t="inlineStr"/>
+      <c r="DD81" t="inlineStr"/>
+      <c r="DE81" t="inlineStr"/>
+      <c r="DF81" t="inlineStr"/>
+      <c r="DG81" t="inlineStr"/>
+      <c r="DH81" t="inlineStr"/>
+      <c r="DI81" t="inlineStr"/>
+      <c r="DJ81" t="inlineStr"/>
+      <c r="DK81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>verykool i725</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i725-4214.php</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2011, Q2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>80MB</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 700 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>107 x 57 x 11.8 mm (4.21 x 2.24 x 0.46 in)</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>106 g (3.74 oz)</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~133 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>3.0 inches, 27.9 cm 2 (~45.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>MP3/MP4/3GP player Organizer Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr">
+        <is>
+          <t>2011, Q2</t>
+        </is>
+      </c>
+      <c r="BN82" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR82" t="inlineStr"/>
+      <c r="BS82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT82" t="inlineStr"/>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV82" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW82" t="inlineStr">
+        <is>
+          <t>80MB</t>
+        </is>
+      </c>
+      <c r="BX82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY82" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ82" t="inlineStr"/>
+      <c r="CA82" t="inlineStr"/>
+      <c r="CB82" t="inlineStr"/>
+      <c r="CC82" t="inlineStr"/>
+      <c r="CD82" t="inlineStr"/>
+      <c r="CE82" t="inlineStr"/>
+      <c r="CF82" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG82" t="inlineStr"/>
+      <c r="CH82" t="inlineStr"/>
+      <c r="CI82" t="inlineStr"/>
+      <c r="CJ82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CL82" t="inlineStr"/>
+      <c r="CM82" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN82" t="inlineStr"/>
+      <c r="CO82" t="inlineStr"/>
+      <c r="CP82" t="inlineStr"/>
+      <c r="CQ82" t="inlineStr"/>
+      <c r="CR82" t="inlineStr"/>
+      <c r="CS82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT82" t="inlineStr"/>
+      <c r="CU82" t="inlineStr"/>
+      <c r="CV82" t="inlineStr"/>
+      <c r="CW82" t="inlineStr"/>
+      <c r="CX82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY82" t="inlineStr"/>
+      <c r="CZ82" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA82" t="inlineStr"/>
+      <c r="DB82" t="inlineStr"/>
+      <c r="DC82" t="inlineStr"/>
+      <c r="DD82" t="inlineStr"/>
+      <c r="DE82" t="inlineStr"/>
+      <c r="DF82" t="inlineStr"/>
+      <c r="DG82" t="inlineStr"/>
+      <c r="DH82" t="inlineStr"/>
+      <c r="DI82" t="inlineStr"/>
+      <c r="DJ82" t="inlineStr"/>
+      <c r="DK82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>verykool CD611</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_cd611-4049.php</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>103 x 56 x 13.5 mm (4.06 x 2.20 x 0.53 in)</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.4 cm 2 (~21.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr"/>
+      <c r="BA83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>MP3/MP4/3GP player Organizer Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN83" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO83" t="inlineStr"/>
+      <c r="BP83" t="inlineStr"/>
+      <c r="BQ83" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="BR83" t="inlineStr"/>
+      <c r="BS83" t="inlineStr"/>
+      <c r="BT83" t="inlineStr"/>
+      <c r="BU83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV83" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW83" t="inlineStr"/>
+      <c r="BX83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY83" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ83" t="inlineStr"/>
+      <c r="CA83" t="inlineStr"/>
+      <c r="CB83" t="inlineStr"/>
+      <c r="CC83" t="inlineStr"/>
+      <c r="CD83" t="inlineStr"/>
+      <c r="CE83" t="inlineStr"/>
+      <c r="CF83" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG83" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CH83" t="inlineStr"/>
+      <c r="CI83" t="inlineStr"/>
+      <c r="CJ83" t="inlineStr"/>
+      <c r="CK83" t="inlineStr"/>
+      <c r="CL83" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM83" t="inlineStr">
+        <is>
+          <t>CDMA / CDMA2000</t>
+        </is>
+      </c>
+      <c r="CN83" t="inlineStr"/>
+      <c r="CO83" t="inlineStr"/>
+      <c r="CP83" t="inlineStr"/>
+      <c r="CQ83" t="inlineStr"/>
+      <c r="CR83" t="inlineStr"/>
+      <c r="CS83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT83" t="inlineStr"/>
+      <c r="CU83" t="inlineStr"/>
+      <c r="CV83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW83" t="inlineStr"/>
+      <c r="CX83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY83" t="inlineStr"/>
+      <c r="CZ83" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA83" t="inlineStr"/>
+      <c r="DB83" t="inlineStr"/>
+      <c r="DC83" t="inlineStr"/>
+      <c r="DD83" t="inlineStr"/>
+      <c r="DE83" t="inlineStr"/>
+      <c r="DF83" t="inlineStr"/>
+      <c r="DG83" t="inlineStr"/>
+      <c r="DH83" t="inlineStr"/>
+      <c r="DI83" t="inlineStr"/>
+      <c r="DJ83" t="inlineStr"/>
+      <c r="DK83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>verykool i800</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i800-4008.php</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>40MB</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Up to 200 h</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Up to 2 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>111 x 58.5 x 13.2 mm (4.37 x 2.30 x 0.52 in)</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>107 g (3.77 oz)</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>A-GPS only</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~143 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>2.8 inches, 24.3 cm 2 (~37.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr"/>
+      <c r="BA84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr"/>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>TV Out MP3/MP4/3GP player Organizer Unit &amp; currency converter SNS applications Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI84" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL84" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM84" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN84" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO84" t="inlineStr"/>
+      <c r="BP84" t="inlineStr"/>
+      <c r="BQ84" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR84" t="inlineStr"/>
+      <c r="BS84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT84" t="inlineStr"/>
+      <c r="BU84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV84" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW84" t="inlineStr">
+        <is>
+          <t>40MB</t>
+        </is>
+      </c>
+      <c r="BX84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY84" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ84" t="inlineStr"/>
+      <c r="CA84" t="inlineStr"/>
+      <c r="CB84" t="inlineStr"/>
+      <c r="CC84" t="inlineStr"/>
+      <c r="CD84" t="inlineStr"/>
+      <c r="CE84" t="inlineStr"/>
+      <c r="CF84" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG84" t="inlineStr">
+        <is>
+          <t>Tri-Band HSDPA</t>
+        </is>
+      </c>
+      <c r="CH84" t="inlineStr"/>
+      <c r="CI84" t="inlineStr"/>
+      <c r="CJ84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CK84" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL84" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="CM84" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN84" t="inlineStr"/>
+      <c r="CO84" t="inlineStr"/>
+      <c r="CP84" t="inlineStr"/>
+      <c r="CQ84" t="inlineStr"/>
+      <c r="CR84" t="inlineStr"/>
+      <c r="CS84" t="inlineStr"/>
+      <c r="CT84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CU84" t="inlineStr"/>
+      <c r="CV84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW84" t="inlineStr"/>
+      <c r="CX84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY84" t="inlineStr"/>
+      <c r="CZ84" t="inlineStr"/>
+      <c r="DA84" t="inlineStr"/>
+      <c r="DB84" t="inlineStr"/>
+      <c r="DC84" t="inlineStr"/>
+      <c r="DD84" t="inlineStr"/>
+      <c r="DE84" t="inlineStr"/>
+      <c r="DF84" t="inlineStr"/>
+      <c r="DG84" t="inlineStr"/>
+      <c r="DH84" t="inlineStr"/>
+      <c r="DI84" t="inlineStr"/>
+      <c r="DJ84" t="inlineStr"/>
+      <c r="DK84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>verykool i720</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i720-4009.php</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Up to 350 h</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>102 x 62 x 16.3 mm (4.02 x 2.44 x 0.64 in)</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>145 g (5.11 oz)</t>
+        </is>
+      </c>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr"/>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~143 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>2.8 inches, 24.3 cm 2 (~38.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr"/>
+      <c r="BA85" t="inlineStr"/>
+      <c r="BB85" t="inlineStr"/>
+      <c r="BC85" t="inlineStr"/>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>Webcam MP3/MP4/3GP player Organizer Unit &amp; currency converter SNS applications Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr"/>
+      <c r="BG85" t="inlineStr"/>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ85" t="inlineStr"/>
+      <c r="BK85" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL85" t="inlineStr"/>
+      <c r="BM85" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN85" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO85" t="inlineStr"/>
+      <c r="BP85" t="inlineStr"/>
+      <c r="BQ85" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR85" t="inlineStr"/>
+      <c r="BS85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT85" t="inlineStr"/>
+      <c r="BU85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV85" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW85" t="inlineStr"/>
+      <c r="BX85" t="inlineStr">
+        <is>
+          <t>1000 entries</t>
+        </is>
+      </c>
+      <c r="BY85" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ85" t="inlineStr"/>
+      <c r="CA85" t="inlineStr"/>
+      <c r="CB85" t="inlineStr"/>
+      <c r="CC85" t="inlineStr"/>
+      <c r="CD85" t="inlineStr"/>
+      <c r="CE85" t="inlineStr"/>
+      <c r="CF85" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG85" t="inlineStr"/>
+      <c r="CH85" t="inlineStr"/>
+      <c r="CI85" t="inlineStr"/>
+      <c r="CJ85" t="inlineStr">
+        <is>
+          <t>Class 12 (4+1/3+2 slots), 180 - 230 kbps</t>
+        </is>
+      </c>
+      <c r="CK85" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL85" t="inlineStr"/>
+      <c r="CM85" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN85" t="inlineStr"/>
+      <c r="CO85" t="inlineStr"/>
+      <c r="CP85" t="inlineStr"/>
+      <c r="CQ85" t="inlineStr"/>
+      <c r="CR85" t="inlineStr"/>
+      <c r="CS85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT85" t="inlineStr"/>
+      <c r="CU85" t="inlineStr"/>
+      <c r="CV85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW85" t="inlineStr"/>
+      <c r="CX85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY85" t="inlineStr"/>
+      <c r="CZ85" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA85" t="inlineStr"/>
+      <c r="DB85" t="inlineStr"/>
+      <c r="DC85" t="inlineStr"/>
+      <c r="DD85" t="inlineStr"/>
+      <c r="DE85" t="inlineStr"/>
+      <c r="DF85" t="inlineStr"/>
+      <c r="DG85" t="inlineStr"/>
+      <c r="DH85" t="inlineStr"/>
+      <c r="DI85" t="inlineStr"/>
+      <c r="DJ85" t="inlineStr"/>
+      <c r="DK85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>verykool i705</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_i705-4010.php</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>94 x 45 x 18.6 mm (3.70 x 1.77 x 0.73 in)</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>90 g (3.17 oz)</t>
+        </is>
+      </c>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.4 cm 2 (~29.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr"/>
+      <c r="BA86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr"/>
+      <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>MP3 player Organizer Unit &amp; currency converter Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL86" t="inlineStr"/>
+      <c r="BM86" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN86" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO86" t="inlineStr"/>
+      <c r="BP86" t="inlineStr"/>
+      <c r="BQ86" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="BR86" t="inlineStr"/>
+      <c r="BS86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BT86" t="inlineStr"/>
+      <c r="BU86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV86" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW86" t="inlineStr"/>
+      <c r="BX86" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="BY86" t="inlineStr">
+        <is>
+          <t>Black, White</t>
+        </is>
+      </c>
+      <c r="BZ86" t="inlineStr"/>
+      <c r="CA86" t="inlineStr"/>
+      <c r="CB86" t="inlineStr"/>
+      <c r="CC86" t="inlineStr"/>
+      <c r="CD86" t="inlineStr"/>
+      <c r="CE86" t="inlineStr"/>
+      <c r="CF86" t="inlineStr">
+        <is>
+          <t>GSM 850 / 1900</t>
+        </is>
+      </c>
+      <c r="CG86" t="inlineStr"/>
+      <c r="CH86" t="inlineStr"/>
+      <c r="CI86" t="inlineStr"/>
+      <c r="CJ86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK86" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL86" t="inlineStr"/>
+      <c r="CM86" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN86" t="inlineStr"/>
+      <c r="CO86" t="inlineStr"/>
+      <c r="CP86" t="inlineStr"/>
+      <c r="CQ86" t="inlineStr"/>
+      <c r="CR86" t="inlineStr"/>
+      <c r="CS86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT86" t="inlineStr"/>
+      <c r="CU86" t="inlineStr"/>
+      <c r="CV86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW86" t="inlineStr"/>
+      <c r="CX86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY86" t="inlineStr"/>
+      <c r="CZ86" t="inlineStr"/>
+      <c r="DA86" t="inlineStr"/>
+      <c r="DB86" t="inlineStr"/>
+      <c r="DC86" t="inlineStr"/>
+      <c r="DD86" t="inlineStr"/>
+      <c r="DE86" t="inlineStr"/>
+      <c r="DF86" t="inlineStr"/>
+      <c r="DG86" t="inlineStr"/>
+      <c r="DH86" t="inlineStr"/>
+      <c r="DI86" t="inlineStr"/>
+      <c r="DJ86" t="inlineStr"/>
+      <c r="DK86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>verykool R80</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_r80-4000.php</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>30MB</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Up to 240 h</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Up to 4 h</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Flashlight IPX5 splash resistant</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>118 x 53 x 15.8 mm (4.65 x 2.09 x 0.62 in)</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Dual SIM (Mini-SIM)</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>114 g (4.02 oz)</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Proprietary</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>1” Sub-OLED display</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~28.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>TFT</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr"/>
+      <c r="BA87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr"/>
+      <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>Pedometer MP3/MP4/3GP player Organizer Webcam SNS applications Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI87" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL87" t="inlineStr">
+        <is>
+          <t>Compass, barometer, thermometer, altimeter, UV detector</t>
+        </is>
+      </c>
+      <c r="BM87" t="inlineStr">
+        <is>
+          <t>2011. Released 2011</t>
+        </is>
+      </c>
+      <c r="BN87" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR87" t="inlineStr"/>
+      <c r="BS87" t="inlineStr"/>
+      <c r="BT87" t="inlineStr"/>
+      <c r="BU87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV87" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW87" t="inlineStr">
+        <is>
+          <t>30MB</t>
+        </is>
+      </c>
+      <c r="BX87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BY87" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ87" t="inlineStr">
+        <is>
+          <t>newvers, newvers2, newvers3</t>
+        </is>
+      </c>
+      <c r="CA87" t="inlineStr"/>
+      <c r="CB87" t="inlineStr"/>
+      <c r="CC87" t="inlineStr"/>
+      <c r="CD87" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 2 (optional)</t>
+        </is>
+      </c>
+      <c r="CE87" t="inlineStr"/>
+      <c r="CF87" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900 - SIM 1</t>
+        </is>
+      </c>
+      <c r="CG87" t="inlineStr"/>
+      <c r="CH87" t="inlineStr"/>
+      <c r="CI87" t="inlineStr"/>
+      <c r="CJ87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK87" t="inlineStr">
+        <is>
+          <t>Class 12</t>
+        </is>
+      </c>
+      <c r="CL87" t="inlineStr"/>
+      <c r="CM87" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN87" t="inlineStr"/>
+      <c r="CO87" t="inlineStr"/>
+      <c r="CP87" t="inlineStr"/>
+      <c r="CQ87" t="inlineStr"/>
+      <c r="CR87" t="inlineStr"/>
+      <c r="CS87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT87" t="inlineStr"/>
+      <c r="CU87" t="inlineStr"/>
+      <c r="CV87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW87" t="inlineStr"/>
+      <c r="CX87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY87" t="inlineStr"/>
+      <c r="CZ87" t="inlineStr"/>
+      <c r="DA87" t="inlineStr"/>
+      <c r="DB87" t="inlineStr"/>
+      <c r="DC87" t="inlineStr"/>
+      <c r="DD87" t="inlineStr"/>
+      <c r="DE87" t="inlineStr"/>
+      <c r="DF87" t="inlineStr"/>
+      <c r="DG87" t="inlineStr"/>
+      <c r="DH87" t="inlineStr"/>
+      <c r="DI87" t="inlineStr"/>
+      <c r="DJ87" t="inlineStr"/>
+      <c r="DK87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>verykool</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/verykool_r13-4001.php</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr"/>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr"/>
+      <c r="BA88" t="inlineStr"/>
+      <c r="BB88" t="inlineStr"/>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
+      <c r="BR88" t="inlineStr"/>
+      <c r="BS88" t="inlineStr"/>
+      <c r="BT88" t="inlineStr"/>
+      <c r="BU88" t="inlineStr"/>
+      <c r="BV88" t="inlineStr"/>
+      <c r="BW88" t="inlineStr"/>
+      <c r="BX88" t="inlineStr"/>
+      <c r="BY88" t="inlineStr"/>
+      <c r="BZ88" t="inlineStr"/>
+      <c r="CA88" t="inlineStr"/>
+      <c r="CB88" t="inlineStr"/>
+      <c r="CC88" t="inlineStr"/>
+      <c r="CD88" t="inlineStr"/>
+      <c r="CE88" t="inlineStr"/>
+      <c r="CF88" t="inlineStr"/>
+      <c r="CG88" t="inlineStr"/>
+      <c r="CH88" t="inlineStr"/>
+      <c r="CI88" t="inlineStr"/>
+      <c r="CJ88" t="inlineStr"/>
+      <c r="CK88" t="inlineStr"/>
+      <c r="CL88" t="inlineStr"/>
+      <c r="CM88" t="inlineStr"/>
+      <c r="CN88" t="inlineStr"/>
+      <c r="CO88" t="inlineStr"/>
+      <c r="CP88" t="inlineStr"/>
+      <c r="CQ88" t="inlineStr"/>
+      <c r="CR88" t="inlineStr"/>
+      <c r="CS88" t="inlineStr"/>
+      <c r="CT88" t="inlineStr"/>
+      <c r="CU88" t="inlineStr"/>
+      <c r="CV88" t="inlineStr"/>
+      <c r="CW88" t="inlineStr"/>
+      <c r="CX88" t="inlineStr"/>
+      <c r="CY88" t="inlineStr"/>
+      <c r="CZ88" t="inlineStr"/>
+      <c r="DA88" t="inlineStr"/>
+      <c r="DB88" t="inlineStr"/>
+      <c r="DC88" t="inlineStr"/>
+      <c r="DD88" t="inlineStr"/>
+      <c r="DE88" t="inlineStr"/>
+      <c r="DF88" t="inlineStr"/>
+      <c r="DG88" t="inlineStr"/>
+      <c r="DH88" t="inlineStr"/>
+      <c r="DI88" t="inlineStr"/>
+      <c r="DJ88" t="inlineStr"/>
+      <c r="DK88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-03.xlsx
+++ b/gsmarena_new_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK88"/>
+  <dimension ref="A1:DK90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22566,55 +22566,37 @@
           <t>2018, April. Released 2018, April</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="H67" t="n">
+        <v>2018</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
+      <c r="J67" t="n">
+        <v>163</v>
+      </c>
+      <c r="K67" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="L67" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M67" t="n">
+        <v>256</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>720</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1440</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>293</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -22626,20 +22608,14 @@
           <t>2GB</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
+      <c r="T67" t="n">
+        <v>8</v>
+      </c>
+      <c r="U67" t="n">
+        <v>5</v>
+      </c>
+      <c r="V67" t="n">
+        <v>5500</v>
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -22919,55 +22895,37 @@
           <t>2014, September. Released 2014, September</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H68" t="n">
+        <v>2014</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="J68" t="n">
+        <v>148</v>
+      </c>
+      <c r="K68" t="n">
+        <v>74</v>
+      </c>
+      <c r="L68" t="n">
+        <v>9</v>
+      </c>
+      <c r="M68" t="n">
+        <v>180</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>720</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>294</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -22979,16 +22937,12 @@
           <t>512MB</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="T68" t="n">
+        <v>8</v>
       </c>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+      <c r="V68" t="n">
+        <v>2000</v>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
@@ -23252,55 +23206,37 @@
           <t>2014, June. Released 2014, June</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H69" t="n">
+        <v>2014</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
+      <c r="J69" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>65</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M69" t="n">
+        <v>110</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4</v>
+      </c>
+      <c r="O69" t="n">
+        <v>480</v>
+      </c>
+      <c r="P69" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>233</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -23312,16 +23248,12 @@
           <t>512MB</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="T69" t="n">
+        <v>8</v>
       </c>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
+      <c r="V69" t="n">
+        <v>1500</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
@@ -23581,55 +23513,37 @@
           <t>2014, June. Released 2014, June</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H70" t="n">
+        <v>2014</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="J70" t="n">
+        <v>116</v>
+      </c>
+      <c r="K70" t="n">
+        <v>61</v>
+      </c>
+      <c r="L70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>100</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O70" t="n">
+        <v>320</v>
+      </c>
+      <c r="P70" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>165</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -23641,16 +23555,12 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T70" t="n">
+        <v>15</v>
       </c>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
+      <c r="V70" t="n">
+        <v>1200</v>
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
@@ -23902,55 +23812,37 @@
           <t>2015, January. Released 2015, January</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="H71" t="n">
+        <v>2015</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>64.9</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
+      <c r="J71" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>11</v>
+      </c>
+      <c r="M71" t="n">
+        <v>128</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>480</v>
+      </c>
+      <c r="P71" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>233</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -23962,32 +23854,22 @@
           <t>512MB</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
+      <c r="T71" t="n">
+        <v>8</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1400</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="Y71" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.38</v>
       </c>
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
@@ -24263,55 +24145,37 @@
           <t>2015, January. Released 2015, January</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+      <c r="H72" t="n">
+        <v>2015</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
+      <c r="J72" t="n">
+        <v>122</v>
+      </c>
+      <c r="K72" t="n">
+        <v>63</v>
+      </c>
+      <c r="L72" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M72" t="n">
+        <v>112</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4</v>
+      </c>
+      <c r="O72" t="n">
+        <v>480</v>
+      </c>
+      <c r="P72" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>233</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -24323,32 +24187,22 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
+      <c r="T72" t="n">
+        <v>5</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1450</v>
       </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
+      <c r="Y72" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.74</v>
       </c>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
@@ -24624,55 +24478,37 @@
           <t>2014, November. Released 2014, November</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H73" t="n">
+        <v>2014</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>113.4</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>60.2</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="J73" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L73" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O73" t="n">
+        <v>320</v>
+      </c>
+      <c r="P73" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>165</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -24684,16 +24520,12 @@
           <t>256MB</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T73" t="n">
+        <v>2</v>
       </c>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="V73" t="n">
+        <v>1000</v>
       </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
@@ -24961,55 +24793,37 @@
           <t>2014, September. Released 2014, October</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H74" t="n">
+        <v>2014</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>111.4</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="J74" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M74" t="n">
+        <v>110</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>176</v>
+      </c>
+      <c r="P74" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>128</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -25021,26 +24835,18 @@
           <t>32MB</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T74" t="n">
+        <v>2</v>
       </c>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
+      <c r="V74" t="n">
+        <v>900</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.28</v>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
@@ -25330,55 +25136,37 @@
           <t>2014, October. Released 2014, October</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="H75" t="n">
+        <v>2014</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="J75" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>157</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O75" t="n">
+        <v>540</v>
+      </c>
+      <c r="P75" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>200</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -25390,20 +25178,14 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
+      <c r="T75" t="n">
+        <v>8</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2300</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -25671,58 +25453,40 @@
           <t>2012, Q1</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H76" t="n">
+        <v>2012</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="J76" t="n">
+        <v>118</v>
+      </c>
+      <c r="K76" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="L76" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>79</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>176</v>
+      </c>
+      <c r="P76" t="n">
+        <v>220</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="T76" t="n">
+        <v>3</v>
       </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
@@ -25992,50 +25756,34 @@
           <t>2012, January. Released 2012, January</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="H77" t="n">
+        <v>2012</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="J77" t="n">
+        <v>107</v>
+      </c>
+      <c r="K77" t="n">
+        <v>45</v>
+      </c>
+      <c r="L77" t="n">
+        <v>12</v>
+      </c>
+      <c r="M77" t="n">
+        <v>63</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O77" t="n">
+        <v>160</v>
+      </c>
+      <c r="P77" t="n">
+        <v>240</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -26305,62 +26053,42 @@
           <t>2011, Q4. Released 2011, December</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H78" t="n">
+        <v>2011</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>105.5</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="J78" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>58</v>
+      </c>
+      <c r="L78" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M78" t="n">
+        <v>90</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O78" t="n">
+        <v>320</v>
+      </c>
+      <c r="P78" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>167</v>
       </c>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T78" t="n">
+        <v>2</v>
       </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
@@ -26626,58 +26354,40 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H79" t="n">
+        <v>2011</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="J79" t="n">
+        <v>111</v>
+      </c>
+      <c r="K79" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>110</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>176</v>
+      </c>
+      <c r="P79" t="n">
+        <v>220</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="T79" t="n">
+        <v>3</v>
       </c>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
@@ -26927,55 +26637,37 @@
           <t>2011, Q3</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H80" t="n">
+        <v>2011</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>115.8</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="J80" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K80" t="n">
+        <v>62</v>
+      </c>
+      <c r="L80" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>110</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>320</v>
+      </c>
+      <c r="P80" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>174</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -26983,10 +26675,8 @@
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T80" t="n">
+        <v>2</v>
       </c>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
@@ -27260,55 +26950,37 @@
           <t>2011, Q2</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H81" t="n">
+        <v>2011</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="J81" t="n">
+        <v>117</v>
+      </c>
+      <c r="K81" t="n">
+        <v>57</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>106</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>240</v>
+      </c>
+      <c r="P81" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>146</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -27316,16 +26988,12 @@
         </is>
       </c>
       <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T81" t="n">
+        <v>2</v>
       </c>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+      <c r="V81" t="n">
+        <v>1100</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -27581,55 +27249,37 @@
           <t>2011, Q2</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H82" t="n">
+        <v>2011</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="J82" t="n">
+        <v>107</v>
+      </c>
+      <c r="K82" t="n">
+        <v>57</v>
+      </c>
+      <c r="L82" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M82" t="n">
+        <v>106</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>240</v>
+      </c>
+      <c r="P82" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>133</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -27637,16 +27287,12 @@
         </is>
       </c>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T82" t="n">
+        <v>2</v>
       </c>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+      <c r="V82" t="n">
+        <v>700</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -27898,46 +27544,32 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H83" t="n">
+        <v>2011</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
+      <c r="J83" t="n">
+        <v>103</v>
+      </c>
+      <c r="K83" t="n">
+        <v>56</v>
+      </c>
+      <c r="L83" t="n">
+        <v>13.5</v>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
+        <v>240</v>
+      </c>
+      <c r="P83" t="n">
+        <v>320</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -28195,55 +27827,37 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H84" t="n">
+        <v>2011</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="J84" t="n">
+        <v>111</v>
+      </c>
+      <c r="K84" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>107</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O84" t="n">
+        <v>240</v>
+      </c>
+      <c r="P84" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>143</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -28251,10 +27865,8 @@
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="T84" t="n">
+        <v>15</v>
       </c>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
@@ -28532,62 +28144,42 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H85" t="n">
+        <v>2011</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="J85" t="n">
+        <v>102</v>
+      </c>
+      <c r="K85" t="n">
+        <v>62</v>
+      </c>
+      <c r="L85" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M85" t="n">
+        <v>145</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O85" t="n">
+        <v>240</v>
+      </c>
+      <c r="P85" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>143</v>
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T85" t="n">
+        <v>2</v>
       </c>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -28853,50 +28445,34 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H86" t="n">
+        <v>2011</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="J86" t="n">
+        <v>94</v>
+      </c>
+      <c r="K86" t="n">
+        <v>45</v>
+      </c>
+      <c r="L86" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>90</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" t="n">
+        <v>240</v>
+      </c>
+      <c r="P86" t="n">
+        <v>320</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -29158,55 +28734,37 @@
           <t>2011. Released 2011</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="H87" t="n">
+        <v>2011</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="J87" t="n">
+        <v>118</v>
+      </c>
+      <c r="K87" t="n">
+        <v>53</v>
+      </c>
+      <c r="L87" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>114</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O87" t="n">
+        <v>240</v>
+      </c>
+      <c r="P87" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>167</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -29214,10 +28772,8 @@
         </is>
       </c>
       <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="T87" t="n">
+        <v>2</v>
       </c>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
@@ -29608,6 +29164,712 @@
       <c r="DJ88" t="inlineStr"/>
       <c r="DK88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tecno</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tecno Spark 4</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/tecno_spark_4-10695.php</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:21 UTC</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2019, September 25. Released 2019, September 25</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>165.3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>2GB | 3GB</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Li-Ion 4000 mAh</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>165.3 x 75.9 x 8.2 mm (6.51 x 2.99 x 0.32 in)</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr"/>
+      <c r="AV89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~269 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>6.52 inches, 102.6 cm 2 (~81.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr"/>
+      <c r="BA89" t="inlineStr"/>
+      <c r="BB89" t="inlineStr"/>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM89" t="inlineStr">
+        <is>
+          <t>2019, September 25. Released 2019, September 25</t>
+        </is>
+      </c>
+      <c r="BN89" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr">
+        <is>
+          <t>Dual LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ89" t="inlineStr"/>
+      <c r="BR89" t="inlineStr">
+        <is>
+          <t>13 MP, AF Auxiliary lenses</t>
+        </is>
+      </c>
+      <c r="BS89" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT89" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU89" t="inlineStr"/>
+      <c r="BV89" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW89" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BX89" t="inlineStr"/>
+      <c r="BY89" t="inlineStr">
+        <is>
+          <t>Royal Purple, Vacation Blue</t>
+        </is>
+      </c>
+      <c r="BZ89" t="inlineStr">
+        <is>
+          <t>KC8</t>
+        </is>
+      </c>
+      <c r="CA89" t="inlineStr"/>
+      <c r="CB89" t="inlineStr"/>
+      <c r="CC89" t="inlineStr"/>
+      <c r="CD89" t="inlineStr"/>
+      <c r="CE89" t="inlineStr"/>
+      <c r="CF89" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG89" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH89" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI89" t="inlineStr"/>
+      <c r="CJ89" t="inlineStr"/>
+      <c r="CK89" t="inlineStr"/>
+      <c r="CL89" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM89" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN89" t="inlineStr"/>
+      <c r="CO89" t="inlineStr">
+        <is>
+          <t>Quad-core 2.0 GHz</t>
+        </is>
+      </c>
+      <c r="CP89" t="inlineStr"/>
+      <c r="CQ89" t="inlineStr"/>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), HIOS 5.5</t>
+        </is>
+      </c>
+      <c r="CS89" t="inlineStr"/>
+      <c r="CT89" t="inlineStr">
+        <is>
+          <t>8 MP</t>
+        </is>
+      </c>
+      <c r="CU89" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW89" t="inlineStr"/>
+      <c r="CX89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY89" t="inlineStr"/>
+      <c r="CZ89" t="inlineStr"/>
+      <c r="DA89" t="inlineStr"/>
+      <c r="DB89" t="inlineStr"/>
+      <c r="DC89" t="inlineStr"/>
+      <c r="DD89" t="inlineStr"/>
+      <c r="DE89" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF89" t="inlineStr"/>
+      <c r="DG89" t="inlineStr"/>
+      <c r="DH89" t="inlineStr"/>
+      <c r="DI89" t="inlineStr"/>
+      <c r="DJ89" t="inlineStr"/>
+      <c r="DK89" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Tecno</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tecno Camon 12 Pro</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/tecno_camon_12_pro-9865.php</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:21 UTC</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2019, September. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>158.6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>6.35</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>6GB</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>About 10000 INR</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>3500 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>158.6 x 75.5 x 7.8 mm (6.24 x 2.97 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>161 g (5.68 oz)</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr"/>
+      <c r="AV90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>720 x 1600 pixels, 20:9 ratio (~276 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>6.35 inches, 97.4 cm 2 (~81.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr"/>
+      <c r="BA90" t="inlineStr"/>
+      <c r="BB90" t="inlineStr"/>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM90" t="inlineStr">
+        <is>
+          <t>2019, September. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="BN90" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr">
+        <is>
+          <t>Quad-LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ90" t="inlineStr"/>
+      <c r="BR90" t="inlineStr">
+        <is>
+          <t>16 MP, PDAF 8 MP Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="BS90" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT90" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU90" t="inlineStr"/>
+      <c r="BV90" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW90" t="inlineStr">
+        <is>
+          <t>64GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BX90" t="inlineStr"/>
+      <c r="BY90" t="inlineStr">
+        <is>
+          <t>Dawn Blue</t>
+        </is>
+      </c>
+      <c r="BZ90" t="inlineStr"/>
+      <c r="CA90" t="inlineStr">
+        <is>
+          <t>About 10000 INR</t>
+        </is>
+      </c>
+      <c r="CB90" t="inlineStr"/>
+      <c r="CC90" t="inlineStr"/>
+      <c r="CD90" t="inlineStr"/>
+      <c r="CE90" t="inlineStr"/>
+      <c r="CF90" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG90" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH90" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 20, 28</t>
+        </is>
+      </c>
+      <c r="CI90" t="inlineStr"/>
+      <c r="CJ90" t="inlineStr"/>
+      <c r="CK90" t="inlineStr"/>
+      <c r="CL90" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM90" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN90" t="inlineStr"/>
+      <c r="CO90" t="inlineStr">
+        <is>
+          <t>Octa-core 2.0 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP90" t="inlineStr">
+        <is>
+          <t>Mediatek MT6762 Helio P22 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CQ90" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), HIOS 5.5</t>
+        </is>
+      </c>
+      <c r="CS90" t="inlineStr"/>
+      <c r="CT90" t="inlineStr">
+        <is>
+          <t>32 MP, f/2.0, 26mm (wide), 1/2.8", 0.8µm</t>
+        </is>
+      </c>
+      <c r="CU90" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW90" t="inlineStr"/>
+      <c r="CX90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY90" t="inlineStr"/>
+      <c r="CZ90" t="inlineStr"/>
+      <c r="DA90" t="inlineStr"/>
+      <c r="DB90" t="inlineStr"/>
+      <c r="DC90" t="inlineStr"/>
+      <c r="DD90" t="inlineStr"/>
+      <c r="DE90" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF90" t="inlineStr"/>
+      <c r="DG90" t="inlineStr"/>
+      <c r="DH90" t="inlineStr"/>
+      <c r="DI90" t="inlineStr"/>
+      <c r="DJ90" t="inlineStr"/>
+      <c r="DK90" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-03.xlsx
+++ b/gsmarena_new_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK90"/>
+  <dimension ref="A1:DO108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,6 +990,26 @@
       <c r="DK1" t="inlineStr">
         <is>
           <t>Selfie camera_Features</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>Main Camera</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>Network_3</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>Network_4</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>Network_5</t>
         </is>
       </c>
     </row>
@@ -1327,6 +1347,10 @@
       <c r="DI2" t="inlineStr"/>
       <c r="DJ2" t="inlineStr"/>
       <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1668,6 +1692,10 @@
       <c r="DI3" t="inlineStr"/>
       <c r="DJ3" t="inlineStr"/>
       <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1999,6 +2027,10 @@
       <c r="DI4" t="inlineStr"/>
       <c r="DJ4" t="inlineStr"/>
       <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2344,6 +2376,10 @@
       <c r="DI5" t="inlineStr"/>
       <c r="DJ5" t="inlineStr"/>
       <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2681,6 +2717,10 @@
       <c r="DI6" t="inlineStr"/>
       <c r="DJ6" t="inlineStr"/>
       <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3022,6 +3062,10 @@
       <c r="DI7" t="inlineStr"/>
       <c r="DJ7" t="inlineStr"/>
       <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3315,6 +3359,10 @@
       <c r="DI8" t="inlineStr"/>
       <c r="DJ8" t="inlineStr"/>
       <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3608,6 +3656,10 @@
       <c r="DI9" t="inlineStr"/>
       <c r="DJ9" t="inlineStr"/>
       <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3893,6 +3945,10 @@
       <c r="DI10" t="inlineStr"/>
       <c r="DJ10" t="inlineStr"/>
       <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4178,6 +4234,10 @@
       <c r="DI11" t="inlineStr"/>
       <c r="DJ11" t="inlineStr"/>
       <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="inlineStr"/>
+      <c r="DM11" t="inlineStr"/>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4543,6 +4603,10 @@
       <c r="DI12" t="inlineStr"/>
       <c r="DJ12" t="inlineStr"/>
       <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4908,6 +4972,10 @@
       <c r="DI13" t="inlineStr"/>
       <c r="DJ13" t="inlineStr"/>
       <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5245,6 +5313,10 @@
       <c r="DI14" t="inlineStr"/>
       <c r="DJ14" t="inlineStr"/>
       <c r="DK14" t="inlineStr"/>
+      <c r="DL14" t="inlineStr"/>
+      <c r="DM14" t="inlineStr"/>
+      <c r="DN14" t="inlineStr"/>
+      <c r="DO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5586,6 +5658,10 @@
       <c r="DI15" t="inlineStr"/>
       <c r="DJ15" t="inlineStr"/>
       <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="inlineStr"/>
+      <c r="DM15" t="inlineStr"/>
+      <c r="DN15" t="inlineStr"/>
+      <c r="DO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5931,6 +6007,10 @@
       <c r="DI16" t="inlineStr"/>
       <c r="DJ16" t="inlineStr"/>
       <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="inlineStr"/>
+      <c r="DM16" t="inlineStr"/>
+      <c r="DN16" t="inlineStr"/>
+      <c r="DO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6254,6 +6334,10 @@
       <c r="DI17" t="inlineStr"/>
       <c r="DJ17" t="inlineStr"/>
       <c r="DK17" t="inlineStr"/>
+      <c r="DL17" t="inlineStr"/>
+      <c r="DM17" t="inlineStr"/>
+      <c r="DN17" t="inlineStr"/>
+      <c r="DO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6581,6 +6665,10 @@
       <c r="DI18" t="inlineStr"/>
       <c r="DJ18" t="inlineStr"/>
       <c r="DK18" t="inlineStr"/>
+      <c r="DL18" t="inlineStr"/>
+      <c r="DM18" t="inlineStr"/>
+      <c r="DN18" t="inlineStr"/>
+      <c r="DO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6900,6 +6988,10 @@
       <c r="DI19" t="inlineStr"/>
       <c r="DJ19" t="inlineStr"/>
       <c r="DK19" t="inlineStr"/>
+      <c r="DL19" t="inlineStr"/>
+      <c r="DM19" t="inlineStr"/>
+      <c r="DN19" t="inlineStr"/>
+      <c r="DO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7227,6 +7319,10 @@
       <c r="DI20" t="inlineStr"/>
       <c r="DJ20" t="inlineStr"/>
       <c r="DK20" t="inlineStr"/>
+      <c r="DL20" t="inlineStr"/>
+      <c r="DM20" t="inlineStr"/>
+      <c r="DN20" t="inlineStr"/>
+      <c r="DO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7562,6 +7658,10 @@
       <c r="DI21" t="inlineStr"/>
       <c r="DJ21" t="inlineStr"/>
       <c r="DK21" t="inlineStr"/>
+      <c r="DL21" t="inlineStr"/>
+      <c r="DM21" t="inlineStr"/>
+      <c r="DN21" t="inlineStr"/>
+      <c r="DO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7699,6 +7799,10 @@
       <c r="DI22" t="inlineStr"/>
       <c r="DJ22" t="inlineStr"/>
       <c r="DK22" t="inlineStr"/>
+      <c r="DL22" t="inlineStr"/>
+      <c r="DM22" t="inlineStr"/>
+      <c r="DN22" t="inlineStr"/>
+      <c r="DO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8040,6 +8144,10 @@
       <c r="DI23" t="inlineStr"/>
       <c r="DJ23" t="inlineStr"/>
       <c r="DK23" t="inlineStr"/>
+      <c r="DL23" t="inlineStr"/>
+      <c r="DM23" t="inlineStr"/>
+      <c r="DN23" t="inlineStr"/>
+      <c r="DO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8365,6 +8473,10 @@
       <c r="DI24" t="inlineStr"/>
       <c r="DJ24" t="inlineStr"/>
       <c r="DK24" t="inlineStr"/>
+      <c r="DL24" t="inlineStr"/>
+      <c r="DM24" t="inlineStr"/>
+      <c r="DN24" t="inlineStr"/>
+      <c r="DO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8734,6 +8846,10 @@
       <c r="DI25" t="inlineStr"/>
       <c r="DJ25" t="inlineStr"/>
       <c r="DK25" t="inlineStr"/>
+      <c r="DL25" t="inlineStr"/>
+      <c r="DM25" t="inlineStr"/>
+      <c r="DN25" t="inlineStr"/>
+      <c r="DO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9075,6 +9191,10 @@
       <c r="DI26" t="inlineStr"/>
       <c r="DJ26" t="inlineStr"/>
       <c r="DK26" t="inlineStr"/>
+      <c r="DL26" t="inlineStr"/>
+      <c r="DM26" t="inlineStr"/>
+      <c r="DN26" t="inlineStr"/>
+      <c r="DO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9416,6 +9536,10 @@
       <c r="DI27" t="inlineStr"/>
       <c r="DJ27" t="inlineStr"/>
       <c r="DK27" t="inlineStr"/>
+      <c r="DL27" t="inlineStr"/>
+      <c r="DM27" t="inlineStr"/>
+      <c r="DN27" t="inlineStr"/>
+      <c r="DO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9771,6 +9895,10 @@
       <c r="DI28" t="inlineStr"/>
       <c r="DJ28" t="inlineStr"/>
       <c r="DK28" t="inlineStr"/>
+      <c r="DL28" t="inlineStr"/>
+      <c r="DM28" t="inlineStr"/>
+      <c r="DN28" t="inlineStr"/>
+      <c r="DO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10126,6 +10254,10 @@
       <c r="DI29" t="inlineStr"/>
       <c r="DJ29" t="inlineStr"/>
       <c r="DK29" t="inlineStr"/>
+      <c r="DL29" t="inlineStr"/>
+      <c r="DM29" t="inlineStr"/>
+      <c r="DN29" t="inlineStr"/>
+      <c r="DO29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10473,6 +10605,10 @@
       <c r="DI30" t="inlineStr"/>
       <c r="DJ30" t="inlineStr"/>
       <c r="DK30" t="inlineStr"/>
+      <c r="DL30" t="inlineStr"/>
+      <c r="DM30" t="inlineStr"/>
+      <c r="DN30" t="inlineStr"/>
+      <c r="DO30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10808,6 +10944,10 @@
       <c r="DI31" t="inlineStr"/>
       <c r="DJ31" t="inlineStr"/>
       <c r="DK31" t="inlineStr"/>
+      <c r="DL31" t="inlineStr"/>
+      <c r="DM31" t="inlineStr"/>
+      <c r="DN31" t="inlineStr"/>
+      <c r="DO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11165,6 +11305,10 @@
       <c r="DI32" t="inlineStr"/>
       <c r="DJ32" t="inlineStr"/>
       <c r="DK32" t="inlineStr"/>
+      <c r="DL32" t="inlineStr"/>
+      <c r="DM32" t="inlineStr"/>
+      <c r="DN32" t="inlineStr"/>
+      <c r="DO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11522,6 +11666,10 @@
       <c r="DI33" t="inlineStr"/>
       <c r="DJ33" t="inlineStr"/>
       <c r="DK33" t="inlineStr"/>
+      <c r="DL33" t="inlineStr"/>
+      <c r="DM33" t="inlineStr"/>
+      <c r="DN33" t="inlineStr"/>
+      <c r="DO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11875,6 +12023,10 @@
       <c r="DI34" t="inlineStr"/>
       <c r="DJ34" t="inlineStr"/>
       <c r="DK34" t="inlineStr"/>
+      <c r="DL34" t="inlineStr"/>
+      <c r="DM34" t="inlineStr"/>
+      <c r="DN34" t="inlineStr"/>
+      <c r="DO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12232,6 +12384,10 @@
       <c r="DI35" t="inlineStr"/>
       <c r="DJ35" t="inlineStr"/>
       <c r="DK35" t="inlineStr"/>
+      <c r="DL35" t="inlineStr"/>
+      <c r="DM35" t="inlineStr"/>
+      <c r="DN35" t="inlineStr"/>
+      <c r="DO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12577,6 +12733,10 @@
       <c r="DI36" t="inlineStr"/>
       <c r="DJ36" t="inlineStr"/>
       <c r="DK36" t="inlineStr"/>
+      <c r="DL36" t="inlineStr"/>
+      <c r="DM36" t="inlineStr"/>
+      <c r="DN36" t="inlineStr"/>
+      <c r="DO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12938,6 +13098,10 @@
       <c r="DI37" t="inlineStr"/>
       <c r="DJ37" t="inlineStr"/>
       <c r="DK37" t="inlineStr"/>
+      <c r="DL37" t="inlineStr"/>
+      <c r="DM37" t="inlineStr"/>
+      <c r="DN37" t="inlineStr"/>
+      <c r="DO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13295,6 +13459,10 @@
       <c r="DI38" t="inlineStr"/>
       <c r="DJ38" t="inlineStr"/>
       <c r="DK38" t="inlineStr"/>
+      <c r="DL38" t="inlineStr"/>
+      <c r="DM38" t="inlineStr"/>
+      <c r="DN38" t="inlineStr"/>
+      <c r="DO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13624,6 +13792,10 @@
       <c r="DI39" t="inlineStr"/>
       <c r="DJ39" t="inlineStr"/>
       <c r="DK39" t="inlineStr"/>
+      <c r="DL39" t="inlineStr"/>
+      <c r="DM39" t="inlineStr"/>
+      <c r="DN39" t="inlineStr"/>
+      <c r="DO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13989,6 +14161,10 @@
       <c r="DI40" t="inlineStr"/>
       <c r="DJ40" t="inlineStr"/>
       <c r="DK40" t="inlineStr"/>
+      <c r="DL40" t="inlineStr"/>
+      <c r="DM40" t="inlineStr"/>
+      <c r="DN40" t="inlineStr"/>
+      <c r="DO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14354,6 +14530,10 @@
       <c r="DI41" t="inlineStr"/>
       <c r="DJ41" t="inlineStr"/>
       <c r="DK41" t="inlineStr"/>
+      <c r="DL41" t="inlineStr"/>
+      <c r="DM41" t="inlineStr"/>
+      <c r="DN41" t="inlineStr"/>
+      <c r="DO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14689,6 +14869,10 @@
       <c r="DI42" t="inlineStr"/>
       <c r="DJ42" t="inlineStr"/>
       <c r="DK42" t="inlineStr"/>
+      <c r="DL42" t="inlineStr"/>
+      <c r="DM42" t="inlineStr"/>
+      <c r="DN42" t="inlineStr"/>
+      <c r="DO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -15024,6 +15208,10 @@
       <c r="DI43" t="inlineStr"/>
       <c r="DJ43" t="inlineStr"/>
       <c r="DK43" t="inlineStr"/>
+      <c r="DL43" t="inlineStr"/>
+      <c r="DM43" t="inlineStr"/>
+      <c r="DN43" t="inlineStr"/>
+      <c r="DO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15361,6 +15549,10 @@
       <c r="DI44" t="inlineStr"/>
       <c r="DJ44" t="inlineStr"/>
       <c r="DK44" t="inlineStr"/>
+      <c r="DL44" t="inlineStr"/>
+      <c r="DM44" t="inlineStr"/>
+      <c r="DN44" t="inlineStr"/>
+      <c r="DO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15672,6 +15864,10 @@
       <c r="DI45" t="inlineStr"/>
       <c r="DJ45" t="inlineStr"/>
       <c r="DK45" t="inlineStr"/>
+      <c r="DL45" t="inlineStr"/>
+      <c r="DM45" t="inlineStr"/>
+      <c r="DN45" t="inlineStr"/>
+      <c r="DO45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16007,6 +16203,10 @@
           <t>LED flash</t>
         </is>
       </c>
+      <c r="DL46" t="inlineStr"/>
+      <c r="DM46" t="inlineStr"/>
+      <c r="DN46" t="inlineStr"/>
+      <c r="DO46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16342,6 +16542,10 @@
           <t>LED flash</t>
         </is>
       </c>
+      <c r="DL47" t="inlineStr"/>
+      <c r="DM47" t="inlineStr"/>
+      <c r="DN47" t="inlineStr"/>
+      <c r="DO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16677,6 +16881,10 @@
           <t>Dual-LED flash</t>
         </is>
       </c>
+      <c r="DL48" t="inlineStr"/>
+      <c r="DM48" t="inlineStr"/>
+      <c r="DN48" t="inlineStr"/>
+      <c r="DO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17018,6 +17226,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL49" t="inlineStr"/>
+      <c r="DM49" t="inlineStr"/>
+      <c r="DN49" t="inlineStr"/>
+      <c r="DO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17353,6 +17565,10 @@
           <t>Dual-LED flash</t>
         </is>
       </c>
+      <c r="DL50" t="inlineStr"/>
+      <c r="DM50" t="inlineStr"/>
+      <c r="DN50" t="inlineStr"/>
+      <c r="DO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17692,6 +17908,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL51" t="inlineStr"/>
+      <c r="DM51" t="inlineStr"/>
+      <c r="DN51" t="inlineStr"/>
+      <c r="DO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18069,6 +18289,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL52" t="inlineStr"/>
+      <c r="DM52" t="inlineStr"/>
+      <c r="DN52" t="inlineStr"/>
+      <c r="DO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -18392,6 +18616,10 @@
           <t>Dual-LED flash</t>
         </is>
       </c>
+      <c r="DL53" t="inlineStr"/>
+      <c r="DM53" t="inlineStr"/>
+      <c r="DN53" t="inlineStr"/>
+      <c r="DO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18715,6 +18943,10 @@
           <t>LED flash</t>
         </is>
       </c>
+      <c r="DL54" t="inlineStr"/>
+      <c r="DM54" t="inlineStr"/>
+      <c r="DN54" t="inlineStr"/>
+      <c r="DO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19042,6 +19274,10 @@
           <t>Dual-LED flash</t>
         </is>
       </c>
+      <c r="DL55" t="inlineStr"/>
+      <c r="DM55" t="inlineStr"/>
+      <c r="DN55" t="inlineStr"/>
+      <c r="DO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19395,6 +19631,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL56" t="inlineStr"/>
+      <c r="DM56" t="inlineStr"/>
+      <c r="DN56" t="inlineStr"/>
+      <c r="DO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19718,6 +19958,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL57" t="inlineStr"/>
+      <c r="DM57" t="inlineStr"/>
+      <c r="DN57" t="inlineStr"/>
+      <c r="DO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20049,6 +20293,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL58" t="inlineStr"/>
+      <c r="DM58" t="inlineStr"/>
+      <c r="DN58" t="inlineStr"/>
+      <c r="DO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20384,6 +20632,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL59" t="inlineStr"/>
+      <c r="DM59" t="inlineStr"/>
+      <c r="DN59" t="inlineStr"/>
+      <c r="DO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20713,6 +20965,10 @@
       <c r="DI60" t="inlineStr"/>
       <c r="DJ60" t="inlineStr"/>
       <c r="DK60" t="inlineStr"/>
+      <c r="DL60" t="inlineStr"/>
+      <c r="DM60" t="inlineStr"/>
+      <c r="DN60" t="inlineStr"/>
+      <c r="DO60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21048,6 +21304,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL61" t="inlineStr"/>
+      <c r="DM61" t="inlineStr"/>
+      <c r="DN61" t="inlineStr"/>
+      <c r="DO61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21393,6 +21653,10 @@
       <c r="DI62" t="inlineStr"/>
       <c r="DJ62" t="inlineStr"/>
       <c r="DK62" t="inlineStr"/>
+      <c r="DL62" t="inlineStr"/>
+      <c r="DM62" t="inlineStr"/>
+      <c r="DN62" t="inlineStr"/>
+      <c r="DO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21742,6 +22006,10 @@
           <t>Dual-LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL63" t="inlineStr"/>
+      <c r="DM63" t="inlineStr"/>
+      <c r="DN63" t="inlineStr"/>
+      <c r="DO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22071,6 +22339,10 @@
           <t>HDR</t>
         </is>
       </c>
+      <c r="DL64" t="inlineStr"/>
+      <c r="DM64" t="inlineStr"/>
+      <c r="DN64" t="inlineStr"/>
+      <c r="DO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22396,6 +22668,10 @@
           <t>LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL65" t="inlineStr"/>
+      <c r="DM65" t="inlineStr"/>
+      <c r="DN65" t="inlineStr"/>
+      <c r="DO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22533,6 +22809,10 @@
       <c r="DI66" t="inlineStr"/>
       <c r="DJ66" t="inlineStr"/>
       <c r="DK66" t="inlineStr"/>
+      <c r="DL66" t="inlineStr"/>
+      <c r="DM66" t="inlineStr"/>
+      <c r="DN66" t="inlineStr"/>
+      <c r="DO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22862,6 +23142,10 @@
       <c r="DI67" t="inlineStr"/>
       <c r="DJ67" t="inlineStr"/>
       <c r="DK67" t="inlineStr"/>
+      <c r="DL67" t="inlineStr"/>
+      <c r="DM67" t="inlineStr"/>
+      <c r="DN67" t="inlineStr"/>
+      <c r="DO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -23173,6 +23457,10 @@
       <c r="DI68" t="inlineStr"/>
       <c r="DJ68" t="inlineStr"/>
       <c r="DK68" t="inlineStr"/>
+      <c r="DL68" t="inlineStr"/>
+      <c r="DM68" t="inlineStr"/>
+      <c r="DN68" t="inlineStr"/>
+      <c r="DO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23480,6 +23768,10 @@
       <c r="DI69" t="inlineStr"/>
       <c r="DJ69" t="inlineStr"/>
       <c r="DK69" t="inlineStr"/>
+      <c r="DL69" t="inlineStr"/>
+      <c r="DM69" t="inlineStr"/>
+      <c r="DN69" t="inlineStr"/>
+      <c r="DO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23779,6 +24071,10 @@
       <c r="DI70" t="inlineStr"/>
       <c r="DJ70" t="inlineStr"/>
       <c r="DK70" t="inlineStr"/>
+      <c r="DL70" t="inlineStr"/>
+      <c r="DM70" t="inlineStr"/>
+      <c r="DN70" t="inlineStr"/>
+      <c r="DO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -24112,6 +24408,10 @@
       <c r="DI71" t="inlineStr"/>
       <c r="DJ71" t="inlineStr"/>
       <c r="DK71" t="inlineStr"/>
+      <c r="DL71" t="inlineStr"/>
+      <c r="DM71" t="inlineStr"/>
+      <c r="DN71" t="inlineStr"/>
+      <c r="DO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -24445,6 +24745,10 @@
       <c r="DI72" t="inlineStr"/>
       <c r="DJ72" t="inlineStr"/>
       <c r="DK72" t="inlineStr"/>
+      <c r="DL72" t="inlineStr"/>
+      <c r="DM72" t="inlineStr"/>
+      <c r="DN72" t="inlineStr"/>
+      <c r="DO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -24760,6 +25064,10 @@
       <c r="DI73" t="inlineStr"/>
       <c r="DJ73" t="inlineStr"/>
       <c r="DK73" t="inlineStr"/>
+      <c r="DL73" t="inlineStr"/>
+      <c r="DM73" t="inlineStr"/>
+      <c r="DN73" t="inlineStr"/>
+      <c r="DO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -25103,6 +25411,10 @@
       <c r="DI74" t="inlineStr"/>
       <c r="DJ74" t="inlineStr"/>
       <c r="DK74" t="inlineStr"/>
+      <c r="DL74" t="inlineStr"/>
+      <c r="DM74" t="inlineStr"/>
+      <c r="DN74" t="inlineStr"/>
+      <c r="DO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -25420,6 +25732,10 @@
       <c r="DI75" t="inlineStr"/>
       <c r="DJ75" t="inlineStr"/>
       <c r="DK75" t="inlineStr"/>
+      <c r="DL75" t="inlineStr"/>
+      <c r="DM75" t="inlineStr"/>
+      <c r="DN75" t="inlineStr"/>
+      <c r="DO75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -25723,6 +26039,10 @@
       <c r="DI76" t="inlineStr"/>
       <c r="DJ76" t="inlineStr"/>
       <c r="DK76" t="inlineStr"/>
+      <c r="DL76" t="inlineStr"/>
+      <c r="DM76" t="inlineStr"/>
+      <c r="DN76" t="inlineStr"/>
+      <c r="DO76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -26020,6 +26340,10 @@
       <c r="DI77" t="inlineStr"/>
       <c r="DJ77" t="inlineStr"/>
       <c r="DK77" t="inlineStr"/>
+      <c r="DL77" t="inlineStr"/>
+      <c r="DM77" t="inlineStr"/>
+      <c r="DN77" t="inlineStr"/>
+      <c r="DO77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26321,6 +26645,10 @@
       <c r="DI78" t="inlineStr"/>
       <c r="DJ78" t="inlineStr"/>
       <c r="DK78" t="inlineStr"/>
+      <c r="DL78" t="inlineStr"/>
+      <c r="DM78" t="inlineStr"/>
+      <c r="DN78" t="inlineStr"/>
+      <c r="DO78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26604,6 +26932,10 @@
       <c r="DI79" t="inlineStr"/>
       <c r="DJ79" t="inlineStr"/>
       <c r="DK79" t="inlineStr"/>
+      <c r="DL79" t="inlineStr"/>
+      <c r="DM79" t="inlineStr"/>
+      <c r="DN79" t="inlineStr"/>
+      <c r="DO79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26917,6 +27249,10 @@
       <c r="DI80" t="inlineStr"/>
       <c r="DJ80" t="inlineStr"/>
       <c r="DK80" t="inlineStr"/>
+      <c r="DL80" t="inlineStr"/>
+      <c r="DM80" t="inlineStr"/>
+      <c r="DN80" t="inlineStr"/>
+      <c r="DO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -27216,6 +27552,10 @@
       <c r="DI81" t="inlineStr"/>
       <c r="DJ81" t="inlineStr"/>
       <c r="DK81" t="inlineStr"/>
+      <c r="DL81" t="inlineStr"/>
+      <c r="DM81" t="inlineStr"/>
+      <c r="DN81" t="inlineStr"/>
+      <c r="DO81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27511,6 +27851,10 @@
       <c r="DI82" t="inlineStr"/>
       <c r="DJ82" t="inlineStr"/>
       <c r="DK82" t="inlineStr"/>
+      <c r="DL82" t="inlineStr"/>
+      <c r="DM82" t="inlineStr"/>
+      <c r="DN82" t="inlineStr"/>
+      <c r="DO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27794,6 +28138,10 @@
       <c r="DI83" t="inlineStr"/>
       <c r="DJ83" t="inlineStr"/>
       <c r="DK83" t="inlineStr"/>
+      <c r="DL83" t="inlineStr"/>
+      <c r="DM83" t="inlineStr"/>
+      <c r="DN83" t="inlineStr"/>
+      <c r="DO83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -28111,6 +28459,10 @@
       <c r="DI84" t="inlineStr"/>
       <c r="DJ84" t="inlineStr"/>
       <c r="DK84" t="inlineStr"/>
+      <c r="DL84" t="inlineStr"/>
+      <c r="DM84" t="inlineStr"/>
+      <c r="DN84" t="inlineStr"/>
+      <c r="DO84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -28412,6 +28764,10 @@
       <c r="DI85" t="inlineStr"/>
       <c r="DJ85" t="inlineStr"/>
       <c r="DK85" t="inlineStr"/>
+      <c r="DL85" t="inlineStr"/>
+      <c r="DM85" t="inlineStr"/>
+      <c r="DN85" t="inlineStr"/>
+      <c r="DO85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -28701,6 +29057,10 @@
       <c r="DI86" t="inlineStr"/>
       <c r="DJ86" t="inlineStr"/>
       <c r="DK86" t="inlineStr"/>
+      <c r="DL86" t="inlineStr"/>
+      <c r="DM86" t="inlineStr"/>
+      <c r="DN86" t="inlineStr"/>
+      <c r="DO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -29026,6 +29386,10 @@
       <c r="DI87" t="inlineStr"/>
       <c r="DJ87" t="inlineStr"/>
       <c r="DK87" t="inlineStr"/>
+      <c r="DL87" t="inlineStr"/>
+      <c r="DM87" t="inlineStr"/>
+      <c r="DN87" t="inlineStr"/>
+      <c r="DO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -29163,6 +29527,10 @@
       <c r="DI88" t="inlineStr"/>
       <c r="DJ88" t="inlineStr"/>
       <c r="DK88" t="inlineStr"/>
+      <c r="DL88" t="inlineStr"/>
+      <c r="DM88" t="inlineStr"/>
+      <c r="DN88" t="inlineStr"/>
+      <c r="DO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -29196,51 +29564,35 @@
           <t>2019, September 25. Released 2019, September 25</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H89" t="n">
+        <v>2019</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>165.3</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>75.9</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
+      <c r="J89" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="K89" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="L89" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="N89" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="O89" t="n">
+        <v>720</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>269</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -29252,20 +29604,14 @@
           <t>2GB | 3GB</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
+      <c r="T89" t="n">
+        <v>13</v>
+      </c>
+      <c r="U89" t="n">
+        <v>8</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4000</v>
       </c>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
@@ -29508,6 +29854,10 @@
           <t>LED flash</t>
         </is>
       </c>
+      <c r="DL89" t="inlineStr"/>
+      <c r="DM89" t="inlineStr"/>
+      <c r="DN89" t="inlineStr"/>
+      <c r="DO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -29541,55 +29891,37 @@
           <t>2019, September. Released 2019, September</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H90" t="n">
+        <v>2019</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>158.6</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>6.35</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
+      <c r="J90" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="K90" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L90" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M90" t="n">
+        <v>161</v>
+      </c>
+      <c r="N90" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="O90" t="n">
+        <v>720</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>276</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -29601,20 +29933,14 @@
           <t>6GB</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="T90" t="n">
+        <v>16</v>
+      </c>
+      <c r="U90" t="n">
+        <v>32</v>
+      </c>
+      <c r="V90" t="n">
+        <v>3500</v>
       </c>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
@@ -29869,6 +30195,7268 @@
           <t>LED flash, HDR</t>
         </is>
       </c>
+      <c r="DL90" t="inlineStr"/>
+      <c r="DM90" t="inlineStr"/>
+      <c r="DN90" t="inlineStr"/>
+      <c r="DO90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Note10</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Also available with 5GVersions: SM-N970F (Europe); SM-N970F/DS (Global); SM-N970U (USA); SM-N970U1 (USA unlocked); SM-N970W (Canada); SM-N9700/DS (LATAM, Brazil, China); SM-N970N (South Korea)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_note10-9788.php</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2019, August 07. Released 2019, August 23</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>256GB</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>About 590 EUR</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>25W wired, PD3.0 12W wireless (Qi) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Li-Ion 3500 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Stylus, 42ms latency (Bluetooth integration, accelerometer, gyro)</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>151 x 71.8 x 7.9 mm (5.94 x 2.83 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>168 g (5.93 oz)</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>FM radio (USA &amp; Canada only)</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr"/>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 6</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>1080 x 2280 pixels, 19:9 ratio (~401 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>6.3 inches, 98.6 cm 2 (~90.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED, HDR10+</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr"/>
+      <c r="BA91" t="inlineStr"/>
+      <c r="BB91" t="inlineStr"/>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>Samsung DeX, Samsung Wireless DeX (desktop experience support) ANT+</t>
+        </is>
+      </c>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BM91" t="inlineStr">
+        <is>
+          <t>2019, August 07. Released 2019, August 23</t>
+        </is>
+      </c>
+      <c r="BN91" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr">
+        <is>
+          <t>LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ91" t="inlineStr"/>
+      <c r="BR91" t="inlineStr">
+        <is>
+          <t>12 MP, f/1.5-2.4, 27mm (wide), 1/2.55", 1.4µm, dual pixel PDAF, OIS 12 MP, f/2.1, 52mm (telephoto), 1/3.6", 1.0µm, PDAF, OIS, 2x optical zoom 16 MP, f/2.2, 12mm (ultrawide), 1/3.1", 1.0µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="BS91" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30/60/240fps, 720p@960fps, HDR10+, stereo sound rec., gyro-EIS &amp; OIS</t>
+        </is>
+      </c>
+      <c r="BT91" t="inlineStr">
+        <is>
+          <t>UFS 3.0</t>
+        </is>
+      </c>
+      <c r="BU91" t="inlineStr"/>
+      <c r="BV91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW91" t="inlineStr">
+        <is>
+          <t>256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BX91" t="inlineStr"/>
+      <c r="BY91" t="inlineStr">
+        <is>
+          <t>Aura Glow, Aura White, Aura Black, Aura Pink, Aura Red</t>
+        </is>
+      </c>
+      <c r="BZ91" t="inlineStr">
+        <is>
+          <t>SM-N970F, SM-N970U, SM-N970U1, SM-N9700, SM-N970W, SM-N9700, SM-N970N, SM-N970X</t>
+        </is>
+      </c>
+      <c r="CA91" t="inlineStr">
+        <is>
+          <t>About 590 EUR</t>
+        </is>
+      </c>
+      <c r="CB91" t="inlineStr">
+        <is>
+          <t>0.85 W/kg (head)     1.08 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC91" t="inlineStr">
+        <is>
+          <t>0.21 W/kg (head)     1.52 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD91" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 - USA</t>
+        </is>
+      </c>
+      <c r="CE91" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO - USA</t>
+        </is>
+      </c>
+      <c r="CF91" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG91" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - Global, LATAM</t>
+        </is>
+      </c>
+      <c r="CI91" t="inlineStr"/>
+      <c r="CJ91" t="inlineStr"/>
+      <c r="CK91" t="inlineStr"/>
+      <c r="CL91" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (7CA) Cat20 2000/150 Mbps</t>
+        </is>
+      </c>
+      <c r="CM91" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="CN91" t="inlineStr">
+        <is>
+          <t>-26.2 LUFS (Good)</t>
+        </is>
+      </c>
+      <c r="CO91" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.73 GHz Mongoose M4 &amp; 2x2.4 GHz Cortex-A75 &amp; 4x1.9 GHz Cortex-A55) - EMEA/LATAM Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485) - USA/China</t>
+        </is>
+      </c>
+      <c r="CP91" t="inlineStr">
+        <is>
+          <t>Exynos 9825 (7 nm) - EMEA/LATAM Qualcomm SM8150 Snapdragon 855 (7 nm) - USA/China</t>
+        </is>
+      </c>
+      <c r="CQ91" t="inlineStr">
+        <is>
+          <t>Mali-G76 MP12 - EMEA/LATAM Adreno 640 - USA/China</t>
+        </is>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4</t>
+        </is>
+      </c>
+      <c r="CS91" t="inlineStr"/>
+      <c r="CT91" t="inlineStr">
+        <is>
+          <t>10 MP, f/2.2, 26mm (wide), 1/3", 1.22µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CU91" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW91" t="inlineStr"/>
+      <c r="CX91" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY91" t="inlineStr"/>
+      <c r="CZ91" t="inlineStr"/>
+      <c r="DA91" t="inlineStr"/>
+      <c r="DB91" t="inlineStr">
+        <is>
+          <t>Noise -92.8dB / Crosstalk -94.0dB</t>
+        </is>
+      </c>
+      <c r="DC91" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD91" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support Tuned by AKG</t>
+        </is>
+      </c>
+      <c r="DE91" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 6), glass back (Gorilla Glass 6), aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF91" t="inlineStr"/>
+      <c r="DG91" t="inlineStr">
+        <is>
+          <t>Endurance rating 92h</t>
+        </is>
+      </c>
+      <c r="DH91" t="inlineStr">
+        <is>
+          <t>789 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="DI91" t="inlineStr">
+        <is>
+          <t>AnTuTu: 344442 (v7), 452400 (v8) GeekBench: 10353 (v4.4), 2241 (v5.1) GFXBench: 28fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ91" t="inlineStr"/>
+      <c r="DK91" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL91" t="inlineStr"/>
+      <c r="DM91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 18, 19, 20, 25, 26, 28, 29, 30, 46, 48, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="DN91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 18, 19, 20, 25, 29, 30, 38, 39, 40, 41, 46, 66, 71 - Canada</t>
+        </is>
+      </c>
+      <c r="DO91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Watch Active2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Versions: SM-R825F, SM-R835F (Global, Canada); SM-R825U, SM-R835U (USA)44mm model: 1.4-inch display; 340 mAh battery; Wi-Fi/LTE40mm model: 1.2-inch display; 247 mAh battery; Wi-Fi/LTERequires:Android 5.0; RAM 1.5 GB or higheriOS 9.0; iPhone 5 or above</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_watch_active2-9784.php</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2019, August. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>5GB | 768MB</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>Wireless</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Li-Ion 340 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>MIL-STD-810G compliant* IP68 dust tight and water resistant (immersible up to 50m) Compatible with standard 20mm straps ECG certified Touch-sensitive bezel *does not guarantee ruggedness or use in extreme conditions</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>44 x 44 x 10.9 mm (1.73 x 1.73 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>42 g (1.48 oz)</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr"/>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass DX+</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>360 x 360 pixels (~364 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>1.4 inches</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr"/>
+      <c r="BA92" t="inlineStr"/>
+      <c r="BB92" t="inlineStr"/>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, heart rate, barometer, VO2max</t>
+        </is>
+      </c>
+      <c r="BM92" t="inlineStr">
+        <is>
+          <t>2019, August. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="BN92" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
+      <c r="BR92" t="inlineStr"/>
+      <c r="BS92" t="inlineStr"/>
+      <c r="BT92" t="inlineStr">
+        <is>
+          <t>eMMC</t>
+        </is>
+      </c>
+      <c r="BU92" t="inlineStr"/>
+      <c r="BV92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW92" t="inlineStr">
+        <is>
+          <t>4GB 768MB RAM, 4GB 1.5GB RAM</t>
+        </is>
+      </c>
+      <c r="BX92" t="inlineStr"/>
+      <c r="BY92" t="inlineStr">
+        <is>
+          <t>Black, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="BZ92" t="inlineStr">
+        <is>
+          <t>SM-R825F, SM-R835F, SM-R825U, SM-R835U</t>
+        </is>
+      </c>
+      <c r="CA92" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="CB92" t="inlineStr"/>
+      <c r="CC92" t="inlineStr"/>
+      <c r="CD92" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1700(AWS) / 1900 - USA/Canada</t>
+        </is>
+      </c>
+      <c r="CE92" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 13, 25, 26, 66 - USA</t>
+        </is>
+      </c>
+      <c r="CF92" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG92" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100 - Global</t>
+        </is>
+      </c>
+      <c r="CH92" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20 - Global</t>
+        </is>
+      </c>
+      <c r="CI92" t="inlineStr"/>
+      <c r="CJ92" t="inlineStr"/>
+      <c r="CK92" t="inlineStr"/>
+      <c r="CL92" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="CM92" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN92" t="inlineStr"/>
+      <c r="CO92" t="inlineStr">
+        <is>
+          <t>Dual-core 1.15 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP92" t="inlineStr">
+        <is>
+          <t>Exynos 9110 (10 nm)</t>
+        </is>
+      </c>
+      <c r="CQ92" t="inlineStr">
+        <is>
+          <t>Mali-T720</t>
+        </is>
+      </c>
+      <c r="CR92" t="inlineStr">
+        <is>
+          <t>Tizen OS 5.5</t>
+        </is>
+      </c>
+      <c r="CS92" t="inlineStr"/>
+      <c r="CT92" t="inlineStr"/>
+      <c r="CU92" t="inlineStr"/>
+      <c r="CV92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW92" t="inlineStr"/>
+      <c r="CX92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY92" t="inlineStr"/>
+      <c r="CZ92" t="inlineStr"/>
+      <c r="DA92" t="inlineStr"/>
+      <c r="DB92" t="inlineStr"/>
+      <c r="DC92" t="inlineStr"/>
+      <c r="DD92" t="inlineStr"/>
+      <c r="DE92" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass DX+), stainless steel frame 316L</t>
+        </is>
+      </c>
+      <c r="DF92" t="inlineStr"/>
+      <c r="DG92" t="inlineStr"/>
+      <c r="DH92" t="inlineStr"/>
+      <c r="DI92" t="inlineStr"/>
+      <c r="DJ92" t="inlineStr"/>
+      <c r="DK92" t="inlineStr"/>
+      <c r="DL92" t="inlineStr"/>
+      <c r="DM92" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 13, 66 - Canada</t>
+        </is>
+      </c>
+      <c r="DN92" t="inlineStr"/>
+      <c r="DO92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Watch Active2 Aluminum</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Versions:44mm model: 1.4-inch display; 340 mAh battery; LTE44mm model: 1.4-inch display; 340 mAh battery; Wi-Fi only40mm model: 1.2-inch display; 247 mAh battery; Wi-Fi onlyRequires:Android 5.0; RAM 1.5 GB or higheriOS 9.0; iPhone 5 or above</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_watch_active2_aluminum-9786.php</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2019, August. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>5GB | 768MB</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>About 300 EUR</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>Wireless</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Li-Ion 340 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 50m) Compatible with standard 20mm straps ECG certified Touch-sensitive bezel MIL-STD-810G compliant* *does not guarantee ruggedness or use in extreme conditions</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>44 x 44 x 10.9 mm (1.73 x 1.73 x 0.43 in)</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>30 g (1.06 oz)</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr"/>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass DX+</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>360 x 360 pixels (~364 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>1.4 inches</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr"/>
+      <c r="BA93" t="inlineStr"/>
+      <c r="BB93" t="inlineStr"/>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, heart rate, barometer</t>
+        </is>
+      </c>
+      <c r="BM93" t="inlineStr">
+        <is>
+          <t>2019, August. Released 2019, September</t>
+        </is>
+      </c>
+      <c r="BN93" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
+      <c r="BR93" t="inlineStr"/>
+      <c r="BS93" t="inlineStr"/>
+      <c r="BT93" t="inlineStr"/>
+      <c r="BU93" t="inlineStr"/>
+      <c r="BV93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW93" t="inlineStr">
+        <is>
+          <t>4GB 768MB RAM, 4GB 1.5GB RAM</t>
+        </is>
+      </c>
+      <c r="BX93" t="inlineStr"/>
+      <c r="BY93" t="inlineStr">
+        <is>
+          <t>Cloud Silver, Aqua Black, Pink Gold, Phantom Violet</t>
+        </is>
+      </c>
+      <c r="BZ93" t="inlineStr">
+        <is>
+          <t>SM-R830</t>
+        </is>
+      </c>
+      <c r="CA93" t="inlineStr">
+        <is>
+          <t>About 300 EUR</t>
+        </is>
+      </c>
+      <c r="CB93" t="inlineStr"/>
+      <c r="CC93" t="inlineStr"/>
+      <c r="CD93" t="inlineStr"/>
+      <c r="CE93" t="inlineStr"/>
+      <c r="CF93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="CG93" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100 - 44mm LTE version only</t>
+        </is>
+      </c>
+      <c r="CH93" t="inlineStr">
+        <is>
+          <t>1, 3, 7, 8, 20 - 44mm LTE version only</t>
+        </is>
+      </c>
+      <c r="CI93" t="inlineStr"/>
+      <c r="CJ93" t="inlineStr"/>
+      <c r="CK93" t="inlineStr"/>
+      <c r="CL93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CM93" t="inlineStr">
+        <is>
+          <t>HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN93" t="inlineStr"/>
+      <c r="CO93" t="inlineStr">
+        <is>
+          <t>Dual-core 1.15 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP93" t="inlineStr">
+        <is>
+          <t>Exynos 9110 (10 nm)</t>
+        </is>
+      </c>
+      <c r="CQ93" t="inlineStr">
+        <is>
+          <t>Mali-T720</t>
+        </is>
+      </c>
+      <c r="CR93" t="inlineStr">
+        <is>
+          <t>Tizen OS 5.5</t>
+        </is>
+      </c>
+      <c r="CS93" t="inlineStr"/>
+      <c r="CT93" t="inlineStr"/>
+      <c r="CU93" t="inlineStr"/>
+      <c r="CV93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW93" t="inlineStr"/>
+      <c r="CX93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY93" t="inlineStr"/>
+      <c r="CZ93" t="inlineStr"/>
+      <c r="DA93" t="inlineStr"/>
+      <c r="DB93" t="inlineStr"/>
+      <c r="DC93" t="inlineStr"/>
+      <c r="DD93" t="inlineStr"/>
+      <c r="DE93" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass DX+), aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF93" t="inlineStr"/>
+      <c r="DG93" t="inlineStr"/>
+      <c r="DH93" t="inlineStr"/>
+      <c r="DI93" t="inlineStr"/>
+      <c r="DJ93" t="inlineStr"/>
+      <c r="DK93" t="inlineStr"/>
+      <c r="DL93" t="inlineStr"/>
+      <c r="DM93" t="inlineStr"/>
+      <c r="DN93" t="inlineStr"/>
+      <c r="DO93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A10s</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Versions: SM-A107F/DS (Global); SM-A107M/DS (LATAM)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a10s-9793.php</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2019, August 12. Released 2019, August 27</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>156.9</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>2GB | 3GB</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>About 180 EUR</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Li-Po 4000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>156.9 x 75.8 x 7.8 mm (6.18 x 2.98 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>168 g (5.93 oz)</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr"/>
+      <c r="AV94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>720 x 1520 pixels, 19:9 ratio (~271 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>6.2 inches, 95.9 cm 2 (~80.7% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr"/>
+      <c r="BA94" t="inlineStr"/>
+      <c r="BB94" t="inlineStr"/>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM94" t="inlineStr">
+        <is>
+          <t>2019, August 12. Released 2019, August 27</t>
+        </is>
+      </c>
+      <c r="BN94" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO94" t="inlineStr">
+        <is>
+          <t>13 MP, f/1.8, 28mm (wide), AF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="BP94" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ94" t="inlineStr"/>
+      <c r="BR94" t="inlineStr"/>
+      <c r="BS94" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT94" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU94" t="inlineStr"/>
+      <c r="BV94" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW94" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BX94" t="inlineStr"/>
+      <c r="BY94" t="inlineStr">
+        <is>
+          <t>Blue, Green, Red, Black</t>
+        </is>
+      </c>
+      <c r="BZ94" t="inlineStr">
+        <is>
+          <t>SM-A107F, SM-A107M</t>
+        </is>
+      </c>
+      <c r="CA94" t="inlineStr">
+        <is>
+          <t>About 180 EUR</t>
+        </is>
+      </c>
+      <c r="CB94" t="inlineStr">
+        <is>
+          <t>0.25 W/kg (head)     1.06 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC94" t="inlineStr"/>
+      <c r="CD94" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - SM-A107M/DS</t>
+        </is>
+      </c>
+      <c r="CE94" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 12, 17, 28 - SM-A107M/DS</t>
+        </is>
+      </c>
+      <c r="CF94" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG94" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH94" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 20, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI94" t="inlineStr"/>
+      <c r="CJ94" t="inlineStr"/>
+      <c r="CK94" t="inlineStr"/>
+      <c r="CL94" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM94" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN94" t="inlineStr"/>
+      <c r="CO94" t="inlineStr">
+        <is>
+          <t>Octa-core 2.0 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP94" t="inlineStr">
+        <is>
+          <t>Mediatek MT6762 Helio P22 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CQ94" t="inlineStr">
+        <is>
+          <t>PowerVR GE8320</t>
+        </is>
+      </c>
+      <c r="CR94" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 11, One UI 3.1</t>
+        </is>
+      </c>
+      <c r="CS94" t="inlineStr"/>
+      <c r="CT94" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0</t>
+        </is>
+      </c>
+      <c r="CU94" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW94" t="inlineStr"/>
+      <c r="CX94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY94" t="inlineStr"/>
+      <c r="CZ94" t="inlineStr"/>
+      <c r="DA94" t="inlineStr"/>
+      <c r="DB94" t="inlineStr"/>
+      <c r="DC94" t="inlineStr"/>
+      <c r="DD94" t="inlineStr"/>
+      <c r="DE94" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF94" t="inlineStr"/>
+      <c r="DG94" t="inlineStr"/>
+      <c r="DH94" t="inlineStr"/>
+      <c r="DI94" t="inlineStr"/>
+      <c r="DJ94" t="inlineStr"/>
+      <c r="DK94" t="inlineStr"/>
+      <c r="DL94" t="inlineStr"/>
+      <c r="DM94" t="inlineStr"/>
+      <c r="DN94" t="inlineStr"/>
+      <c r="DO94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A10e</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Versions: SM-A102U (AT&amp;T, Verizon, Metro PCS, Sprint, T-Mobile, Virgin Mobile, Boost Mobile); SM-A102U1 (Unlocked)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a10e-9790.php</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2019, July. Released 2019, August</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>147.3</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>2GB | 3GB</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Li-Ion 3000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>147.3 x 69.6 x 8.4 mm (5.80 x 2.74 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>141 g (4.97 oz)</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr"/>
+      <c r="AV95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>720 x 1560 pixels, 19.5:9 ratio (~295 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>5.83 inches, 83.4 cm 2 (~81.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr"/>
+      <c r="BA95" t="inlineStr"/>
+      <c r="BB95" t="inlineStr"/>
+      <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM95" t="inlineStr">
+        <is>
+          <t>2019, July. Released 2019, August</t>
+        </is>
+      </c>
+      <c r="BN95" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ95" t="inlineStr">
+        <is>
+          <t>8 MP, f/1.9, AF or 5 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR95" t="inlineStr"/>
+      <c r="BS95" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT95" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU95" t="inlineStr"/>
+      <c r="BV95" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW95" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BX95" t="inlineStr"/>
+      <c r="BY95" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ95" t="inlineStr">
+        <is>
+          <t>SM-A102U, SM-S102DL, SM-A102U1, SM-A102W, SM-A102N</t>
+        </is>
+      </c>
+      <c r="CA95" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="CB95" t="inlineStr">
+        <is>
+          <t>0.47 W/kg (head)     0.54 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC95" t="inlineStr"/>
+      <c r="CD95" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 - Verizon, Metro PCS, Sprint, T-Mobile, Virgin Mobile, Boost Mobile</t>
+        </is>
+      </c>
+      <c r="CE95" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - Verizon, Metro PCS, Sprint, T-Mobile, Virgin Mobile, Boost Mobile</t>
+        </is>
+      </c>
+      <c r="CF95" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG95" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1700(AWS) / 1900 / 2100 - AT&amp;T</t>
+        </is>
+      </c>
+      <c r="CH95" t="inlineStr">
+        <is>
+          <t>2, 3, 4, 5, 7, 12, 14, 29, 30, 66 - AT&amp;T</t>
+        </is>
+      </c>
+      <c r="CI95" t="inlineStr"/>
+      <c r="CJ95" t="inlineStr"/>
+      <c r="CK95" t="inlineStr"/>
+      <c r="CL95" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM95" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN95" t="inlineStr"/>
+      <c r="CO95" t="inlineStr">
+        <is>
+          <t>Octa-core (2x1.6 GHz Cortex-A73 &amp; 6x1.35 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="CP95" t="inlineStr">
+        <is>
+          <t>Exynos 7884 (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ95" t="inlineStr">
+        <is>
+          <t>Mali-G71 MP2</t>
+        </is>
+      </c>
+      <c r="CR95" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 11, One UI 3.1</t>
+        </is>
+      </c>
+      <c r="CS95" t="inlineStr"/>
+      <c r="CT95" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.0 or 2 MP</t>
+        </is>
+      </c>
+      <c r="CU95" t="inlineStr"/>
+      <c r="CV95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW95" t="inlineStr"/>
+      <c r="CX95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY95" t="inlineStr"/>
+      <c r="CZ95" t="inlineStr"/>
+      <c r="DA95" t="inlineStr"/>
+      <c r="DB95" t="inlineStr"/>
+      <c r="DC95" t="inlineStr"/>
+      <c r="DD95" t="inlineStr"/>
+      <c r="DE95" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF95" t="inlineStr"/>
+      <c r="DG95" t="inlineStr"/>
+      <c r="DH95" t="inlineStr"/>
+      <c r="DI95" t="inlineStr"/>
+      <c r="DJ95" t="inlineStr"/>
+      <c r="DK95" t="inlineStr"/>
+      <c r="DL95" t="inlineStr"/>
+      <c r="DM95" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 13, 25, 26, 41, 71 - Verizon, Sprint, Virgin Mobile, Boost Mobile</t>
+        </is>
+      </c>
+      <c r="DN95" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 20, 25, 26, 28, 38, 39, 40, 41, 66, 71 - Metro PCS, T-Mobile</t>
+        </is>
+      </c>
+      <c r="DO95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Tab S6</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Versions: SM-T860 (Wi-Fi); SM-T865 (LTE)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_tab_s6-9781.php</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2019, July 31. Released 2019, August</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>244.5</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>159.5</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>4GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>7040</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>About 600 EUR</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>15W wired</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Li-Po 7040 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Stylus support (Bluetooth integration; magnetic)</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>244.5 x 159.5 x 5.7 mm (9.63 x 6.28 x 0.22 in)</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Nano-SIM (cellular model only)</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>420 g (14.82 oz)</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO - cellular model only</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1, magnetic connector</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr"/>
+      <c r="AV96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>1600 x 2560 pixels, 16:10 ratio (~287 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>10.5 inches, 321.9 cm 2 (~82.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr"/>
+      <c r="BA96" t="inlineStr"/>
+      <c r="BB96" t="inlineStr"/>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>Samsung DeX (desktop experience support) ANT+</t>
+        </is>
+      </c>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, optical), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM96" t="inlineStr">
+        <is>
+          <t>2019, July 31. Released 2019, August</t>
+        </is>
+      </c>
+      <c r="BN96" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO96" t="inlineStr">
+        <is>
+          <t>13 MP, f/2.0, 26mm (wide), 1/3.4", 1.0µm, AF 5 MP, f/2.2, 12mm (ultrawide), 1.12µm</t>
+        </is>
+      </c>
+      <c r="BP96" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ96" t="inlineStr"/>
+      <c r="BR96" t="inlineStr"/>
+      <c r="BS96" t="inlineStr">
+        <is>
+          <t>4K@30fps</t>
+        </is>
+      </c>
+      <c r="BT96" t="inlineStr">
+        <is>
+          <t>UFS 3.0</t>
+        </is>
+      </c>
+      <c r="BU96" t="inlineStr"/>
+      <c r="BV96" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW96" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 6GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BX96" t="inlineStr"/>
+      <c r="BY96" t="inlineStr">
+        <is>
+          <t>Mountain Gray, Cloud Blue, Rose Blush</t>
+        </is>
+      </c>
+      <c r="BZ96" t="inlineStr">
+        <is>
+          <t>SM-T860, SM-T865</t>
+        </is>
+      </c>
+      <c r="CA96" t="inlineStr">
+        <is>
+          <t>About 600 EUR</t>
+        </is>
+      </c>
+      <c r="CB96" t="inlineStr">
+        <is>
+          <t>0.70 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC96" t="inlineStr">
+        <is>
+          <t>1.22 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD96" t="inlineStr"/>
+      <c r="CE96" t="inlineStr"/>
+      <c r="CF96" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG96" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH96" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 20, 25, 26, 28, 32, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CI96" t="inlineStr"/>
+      <c r="CJ96" t="inlineStr"/>
+      <c r="CK96" t="inlineStr"/>
+      <c r="CL96" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (6CA) Cat20 2000/150 Mbps - cellular model only</t>
+        </is>
+      </c>
+      <c r="CM96" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN96" t="inlineStr"/>
+      <c r="CO96" t="inlineStr">
+        <is>
+          <t>Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485)</t>
+        </is>
+      </c>
+      <c r="CP96" t="inlineStr">
+        <is>
+          <t>Qualcomm SM8150 Snapdragon 855 (7 nm)</t>
+        </is>
+      </c>
+      <c r="CQ96" t="inlineStr">
+        <is>
+          <t>Adreno 640</t>
+        </is>
+      </c>
+      <c r="CR96" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4.0</t>
+        </is>
+      </c>
+      <c r="CS96" t="inlineStr"/>
+      <c r="CT96" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 26mm (wide), 1/4.0", 1.12µm</t>
+        </is>
+      </c>
+      <c r="CU96" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW96" t="inlineStr"/>
+      <c r="CX96" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers (4 speakers)</t>
+        </is>
+      </c>
+      <c r="CY96" t="inlineStr"/>
+      <c r="CZ96" t="inlineStr"/>
+      <c r="DA96" t="inlineStr"/>
+      <c r="DB96" t="inlineStr"/>
+      <c r="DC96" t="inlineStr"/>
+      <c r="DD96" t="inlineStr"/>
+      <c r="DE96" t="inlineStr">
+        <is>
+          <t>Glass front, aluminum back, aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF96" t="inlineStr"/>
+      <c r="DG96" t="inlineStr"/>
+      <c r="DH96" t="inlineStr"/>
+      <c r="DI96" t="inlineStr"/>
+      <c r="DJ96" t="inlineStr"/>
+      <c r="DK96" t="inlineStr"/>
+      <c r="DL96" t="inlineStr"/>
+      <c r="DM96" t="inlineStr"/>
+      <c r="DN96" t="inlineStr"/>
+      <c r="DO96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Tab A 8.0 (2019)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Versions: SM-T290 (Wi-Fi); SM-T295 (LTE)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_tab_a_8_0_(2019)-9760.php</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2019, July 05. Released 2019, July</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>124.4</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2GB | 3GB</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Li-Po 5100 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>210 x 124.4 x 8 mm (8.27 x 4.90 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Nano-SIM (cellular model only)</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>345g (Wi-Fi), 347g (LTE) (12.24 oz)</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS - cellular model only</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr"/>
+      <c r="AV97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>800 x 1280 pixels, 16:10 ratio (~189 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>8.0 inches, 185.6 cm 2 (~71.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>TFT LCD</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr"/>
+      <c r="BA97" t="inlineStr"/>
+      <c r="BB97" t="inlineStr"/>
+      <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
+      <c r="BI97" t="inlineStr"/>
+      <c r="BJ97" t="inlineStr"/>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM97" t="inlineStr">
+        <is>
+          <t>2019, July 05. Released 2019, July</t>
+        </is>
+      </c>
+      <c r="BN97" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO97" t="inlineStr"/>
+      <c r="BP97" t="inlineStr"/>
+      <c r="BQ97" t="inlineStr">
+        <is>
+          <t>8 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR97" t="inlineStr"/>
+      <c r="BS97" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT97" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU97" t="inlineStr"/>
+      <c r="BV97" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW97" t="inlineStr">
+        <is>
+          <t>32GB 2GB RAM, 32GB 3GB RAM, 64GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="BX97" t="inlineStr"/>
+      <c r="BY97" t="inlineStr">
+        <is>
+          <t>Carbon Black, Silver Gray</t>
+        </is>
+      </c>
+      <c r="BZ97" t="inlineStr">
+        <is>
+          <t>SM-T290, SM-T295</t>
+        </is>
+      </c>
+      <c r="CA97" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB97" t="inlineStr"/>
+      <c r="CC97" t="inlineStr">
+        <is>
+          <t>0.75 W/kg (head)     1.19 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD97" t="inlineStr"/>
+      <c r="CE97" t="inlineStr"/>
+      <c r="CF97" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG97" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH97" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 17, 20, 28, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI97" t="inlineStr"/>
+      <c r="CJ97" t="inlineStr"/>
+      <c r="CK97" t="inlineStr"/>
+      <c r="CL97" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps - cellular model only</t>
+        </is>
+      </c>
+      <c r="CM97" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN97" t="inlineStr"/>
+      <c r="CO97" t="inlineStr">
+        <is>
+          <t>Quad-core 2.0 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP97" t="inlineStr">
+        <is>
+          <t>Qualcomm SDM429 Snapdragon 429 (12 nm)</t>
+        </is>
+      </c>
+      <c r="CQ97" t="inlineStr">
+        <is>
+          <t>Adreno 504</t>
+        </is>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 11</t>
+        </is>
+      </c>
+      <c r="CS97" t="inlineStr"/>
+      <c r="CT97" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="CU97" t="inlineStr"/>
+      <c r="CV97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW97" t="inlineStr"/>
+      <c r="CX97" t="inlineStr">
+        <is>
+          <t>Yes, with dual speakers</t>
+        </is>
+      </c>
+      <c r="CY97" t="inlineStr"/>
+      <c r="CZ97" t="inlineStr"/>
+      <c r="DA97" t="inlineStr"/>
+      <c r="DB97" t="inlineStr"/>
+      <c r="DC97" t="inlineStr"/>
+      <c r="DD97" t="inlineStr"/>
+      <c r="DE97" t="inlineStr">
+        <is>
+          <t>Glass front, aluminum back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF97" t="inlineStr"/>
+      <c r="DG97" t="inlineStr"/>
+      <c r="DH97" t="inlineStr"/>
+      <c r="DI97" t="inlineStr"/>
+      <c r="DJ97" t="inlineStr"/>
+      <c r="DK97" t="inlineStr"/>
+      <c r="DL97" t="inlineStr"/>
+      <c r="DM97" t="inlineStr"/>
+      <c r="DN97" t="inlineStr"/>
+      <c r="DO97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy XCover 4s</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Versions: SM-G398F, SM-G398FN/DS (Europe)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_xcover_4s-9730.php</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2019, June. Released 2019, July</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>146.2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>32GB</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>3GB</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Li-Ion 2800 mAh, removable</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>146.2 x 73.3 x 9.7 mm (5.76 x 2.89 x 0.38 in)</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Single SIM (Micro-SIM) or Dual SIM (Micro-SIM, dual stand-by)</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>172 g (6.07 oz)</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr"/>
+      <c r="AV98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>720 x 1280 pixels, 16:9 ratio (~294 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>5.0 inches, 68.9 cm 2 (~64.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr"/>
+      <c r="BA98" t="inlineStr"/>
+      <c r="BB98" t="inlineStr"/>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM98" t="inlineStr">
+        <is>
+          <t>2019, June. Released 2019, July</t>
+        </is>
+      </c>
+      <c r="BN98" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO98" t="inlineStr"/>
+      <c r="BP98" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ98" t="inlineStr">
+        <is>
+          <t>16 MP, f/1.7, PDAF</t>
+        </is>
+      </c>
+      <c r="BR98" t="inlineStr"/>
+      <c r="BS98" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT98" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU98" t="inlineStr"/>
+      <c r="BV98" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW98" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BX98" t="inlineStr"/>
+      <c r="BY98" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="BZ98" t="inlineStr">
+        <is>
+          <t>SM-G398F, SM-G398FN/DS, SM-G398FN</t>
+        </is>
+      </c>
+      <c r="CA98" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="CB98" t="inlineStr"/>
+      <c r="CC98" t="inlineStr">
+        <is>
+          <t>0.91 W/kg (head)     1.31 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD98" t="inlineStr"/>
+      <c r="CE98" t="inlineStr"/>
+      <c r="CF98" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG98" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH98" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 28, 38, 40</t>
+        </is>
+      </c>
+      <c r="CI98" t="inlineStr"/>
+      <c r="CJ98" t="inlineStr"/>
+      <c r="CK98" t="inlineStr"/>
+      <c r="CL98" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (2CA) Cat6 300/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM98" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN98" t="inlineStr"/>
+      <c r="CO98" t="inlineStr">
+        <is>
+          <t>Octa-core (2x1.6 GHz Cortex-A73 &amp; 6x1.6 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="CP98" t="inlineStr">
+        <is>
+          <t>Exynos 7885 (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ98" t="inlineStr">
+        <is>
+          <t>Mali-G71 MP2</t>
+        </is>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 11, One UI 3.1</t>
+        </is>
+      </c>
+      <c r="CS98" t="inlineStr"/>
+      <c r="CT98" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2</t>
+        </is>
+      </c>
+      <c r="CU98" t="inlineStr"/>
+      <c r="CV98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW98" t="inlineStr"/>
+      <c r="CX98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY98" t="inlineStr"/>
+      <c r="CZ98" t="inlineStr"/>
+      <c r="DA98" t="inlineStr"/>
+      <c r="DB98" t="inlineStr"/>
+      <c r="DC98" t="inlineStr"/>
+      <c r="DD98" t="inlineStr"/>
+      <c r="DE98" t="inlineStr"/>
+      <c r="DF98" t="inlineStr"/>
+      <c r="DG98" t="inlineStr"/>
+      <c r="DH98" t="inlineStr"/>
+      <c r="DI98" t="inlineStr"/>
+      <c r="DJ98" t="inlineStr"/>
+      <c r="DK98" t="inlineStr"/>
+      <c r="DL98" t="inlineStr"/>
+      <c r="DM98" t="inlineStr"/>
+      <c r="DN98" t="inlineStr"/>
+      <c r="DO98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A2 Core</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Versions: SM-A260F/DS (Global); SM-A260G/DS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_a2_core-9636.php</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2019, April. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>141.6</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>16GB | 8GB</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1GB</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Li-Ion 2600 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>141.6 x 71 x 9.1 mm (5.57 x 2.80 x 0.36 in)</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>142 g (5.01 oz)</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>microUSB 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr"/>
+      <c r="AV99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>540 x 960 pixels, 16:9 ratio (~220 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>5.0 inches, 68.9 cm 2 (~68.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr"/>
+      <c r="BA99" t="inlineStr"/>
+      <c r="BB99" t="inlineStr"/>
+      <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="BM99" t="inlineStr">
+        <is>
+          <t>2019, April. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="BN99" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO99" t="inlineStr"/>
+      <c r="BP99" t="inlineStr">
+        <is>
+          <t>LED flash, HDR</t>
+        </is>
+      </c>
+      <c r="BQ99" t="inlineStr">
+        <is>
+          <t>5 MP, f/1.9, AF</t>
+        </is>
+      </c>
+      <c r="BR99" t="inlineStr"/>
+      <c r="BS99" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT99" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU99" t="inlineStr"/>
+      <c r="BV99" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW99" t="inlineStr">
+        <is>
+          <t>8GB 1GB RAM, 16GB 1GB RAM</t>
+        </is>
+      </c>
+      <c r="BX99" t="inlineStr"/>
+      <c r="BY99" t="inlineStr">
+        <is>
+          <t>Black, Blue, Red, Gold</t>
+        </is>
+      </c>
+      <c r="BZ99" t="inlineStr">
+        <is>
+          <t>SM-A260F, SM-A260G</t>
+        </is>
+      </c>
+      <c r="CA99" t="inlineStr">
+        <is>
+          <t>About 120 EUR</t>
+        </is>
+      </c>
+      <c r="CB99" t="inlineStr"/>
+      <c r="CC99" t="inlineStr">
+        <is>
+          <t>0.53 W/kg (head)     1.09 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD99" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100 - A260G/DS</t>
+        </is>
+      </c>
+      <c r="CE99" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 40, 41 - A260G/DS</t>
+        </is>
+      </c>
+      <c r="CF99" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800</t>
+        </is>
+      </c>
+      <c r="CG99" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100 - A260F/DS</t>
+        </is>
+      </c>
+      <c r="CH99" t="inlineStr">
+        <is>
+          <t>1, 3, 7, 8, 20 - A260F/DS</t>
+        </is>
+      </c>
+      <c r="CI99" t="inlineStr"/>
+      <c r="CJ99" t="inlineStr"/>
+      <c r="CK99" t="inlineStr"/>
+      <c r="CL99" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM99" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN99" t="inlineStr"/>
+      <c r="CO99" t="inlineStr">
+        <is>
+          <t>Octa-core 1.6 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP99" t="inlineStr">
+        <is>
+          <t>Exynos 7870 Octa (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ99" t="inlineStr">
+        <is>
+          <t>Mali-T830 MP1</t>
+        </is>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>Android 8.0 Oreo (Go edition)</t>
+        </is>
+      </c>
+      <c r="CS99" t="inlineStr"/>
+      <c r="CT99" t="inlineStr">
+        <is>
+          <t>5 MP, f/2.2</t>
+        </is>
+      </c>
+      <c r="CU99" t="inlineStr"/>
+      <c r="CV99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW99" t="inlineStr"/>
+      <c r="CX99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY99" t="inlineStr"/>
+      <c r="CZ99" t="inlineStr"/>
+      <c r="DA99" t="inlineStr"/>
+      <c r="DB99" t="inlineStr"/>
+      <c r="DC99" t="inlineStr"/>
+      <c r="DD99" t="inlineStr"/>
+      <c r="DE99" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF99" t="inlineStr"/>
+      <c r="DG99" t="inlineStr"/>
+      <c r="DH99" t="inlineStr"/>
+      <c r="DI99" t="inlineStr"/>
+      <c r="DJ99" t="inlineStr"/>
+      <c r="DK99" t="inlineStr"/>
+      <c r="DL99" t="inlineStr"/>
+      <c r="DM99" t="inlineStr"/>
+      <c r="DN99" t="inlineStr"/>
+      <c r="DO99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Watch Active</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_watch_active-9589.php</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2019, February. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>4GB</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>768MB</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>Wireless</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Li-Ion 230 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 50m) Compatible with standard 20mm straps MIL-STD-810G compliant* *does not guarantee ruggedness or use in extreme conditions</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>39.5 x 39.5 x 10.5 mm (1.56 x 1.56 x 0.41 in)</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>25 g (0.88 oz)</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr"/>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>360 x 360 pixels (~302 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>1.1 inches</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr"/>
+      <c r="BA100" t="inlineStr"/>
+      <c r="BB100" t="inlineStr"/>
+      <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr">
+        <is>
+          <t>Accelerometer, gyro, heart rate, barometer</t>
+        </is>
+      </c>
+      <c r="BM100" t="inlineStr">
+        <is>
+          <t>2019, February. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="BN100" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO100" t="inlineStr"/>
+      <c r="BP100" t="inlineStr"/>
+      <c r="BQ100" t="inlineStr"/>
+      <c r="BR100" t="inlineStr"/>
+      <c r="BS100" t="inlineStr"/>
+      <c r="BT100" t="inlineStr"/>
+      <c r="BU100" t="inlineStr"/>
+      <c r="BV100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW100" t="inlineStr">
+        <is>
+          <t>4GB 768MB RAM</t>
+        </is>
+      </c>
+      <c r="BX100" t="inlineStr"/>
+      <c r="BY100" t="inlineStr">
+        <is>
+          <t>Silver, Black, Rose Gold, Sea Green</t>
+        </is>
+      </c>
+      <c r="BZ100" t="inlineStr">
+        <is>
+          <t>SM-R500</t>
+        </is>
+      </c>
+      <c r="CA100" t="inlineStr">
+        <is>
+          <t>About 210 EUR</t>
+        </is>
+      </c>
+      <c r="CB100" t="inlineStr"/>
+      <c r="CC100" t="inlineStr"/>
+      <c r="CD100" t="inlineStr"/>
+      <c r="CE100" t="inlineStr"/>
+      <c r="CF100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="CG100" t="inlineStr"/>
+      <c r="CH100" t="inlineStr"/>
+      <c r="CI100" t="inlineStr"/>
+      <c r="CJ100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CK100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CL100" t="inlineStr"/>
+      <c r="CM100" t="inlineStr">
+        <is>
+          <t>No cellular connectivity</t>
+        </is>
+      </c>
+      <c r="CN100" t="inlineStr"/>
+      <c r="CO100" t="inlineStr">
+        <is>
+          <t>Dual-core 1.15 GHz Cortex-A53</t>
+        </is>
+      </c>
+      <c r="CP100" t="inlineStr">
+        <is>
+          <t>Exynos 9110 (10 nm)</t>
+        </is>
+      </c>
+      <c r="CQ100" t="inlineStr">
+        <is>
+          <t>Mali-T720</t>
+        </is>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>Tizen OS 5.5</t>
+        </is>
+      </c>
+      <c r="CS100" t="inlineStr"/>
+      <c r="CT100" t="inlineStr"/>
+      <c r="CU100" t="inlineStr"/>
+      <c r="CV100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW100" t="inlineStr"/>
+      <c r="CX100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY100" t="inlineStr"/>
+      <c r="CZ100" t="inlineStr"/>
+      <c r="DA100" t="inlineStr"/>
+      <c r="DB100" t="inlineStr"/>
+      <c r="DC100" t="inlineStr"/>
+      <c r="DD100" t="inlineStr"/>
+      <c r="DE100" t="inlineStr"/>
+      <c r="DF100" t="inlineStr"/>
+      <c r="DG100" t="inlineStr"/>
+      <c r="DH100" t="inlineStr"/>
+      <c r="DI100" t="inlineStr"/>
+      <c r="DJ100" t="inlineStr"/>
+      <c r="DK100" t="inlineStr"/>
+      <c r="DL100" t="inlineStr"/>
+      <c r="DM100" t="inlineStr"/>
+      <c r="DN100" t="inlineStr"/>
+      <c r="DO100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy View2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Versions: SM-T920 (Wi-Fi only); SM-T927 (EMEA); SM-T927A (AT&amp;T)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_view2-9672.php</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2019, April. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>417.1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>263.4</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>64GB</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>3GB</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>About 660 EUR</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Li-Po 12000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Built-in kickstand</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>417.1 x 263.4 x 17.3 mm (16.42 x 10.37 x 0.68 in)</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Nano-SIM (cellular model only)</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>2.23 kg (4.92 lb)</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, EDR</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS - cellular model only</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr"/>
+      <c r="AV101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>1080 x 1920 pixels, 16:9 ratio (~127 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>17.3 inches, 825.1 cm 2 (~75.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr"/>
+      <c r="BA101" t="inlineStr"/>
+      <c r="BB101" t="inlineStr"/>
+      <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM101" t="inlineStr">
+        <is>
+          <t>2019, April. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="BN101" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO101" t="inlineStr"/>
+      <c r="BP101" t="inlineStr"/>
+      <c r="BQ101" t="inlineStr"/>
+      <c r="BR101" t="inlineStr"/>
+      <c r="BS101" t="inlineStr"/>
+      <c r="BT101" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU101" t="inlineStr"/>
+      <c r="BV101" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW101" t="inlineStr">
+        <is>
+          <t>64GB 3GB RAM</t>
+        </is>
+      </c>
+      <c r="BX101" t="inlineStr"/>
+      <c r="BY101" t="inlineStr">
+        <is>
+          <t>Dark Grey</t>
+        </is>
+      </c>
+      <c r="BZ101" t="inlineStr">
+        <is>
+          <t>SM-T927A, SM-T920</t>
+        </is>
+      </c>
+      <c r="CA101" t="inlineStr">
+        <is>
+          <t>About 660 EUR</t>
+        </is>
+      </c>
+      <c r="CB101" t="inlineStr">
+        <is>
+          <t>1.14 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC101" t="inlineStr"/>
+      <c r="CD101" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 - SM-T927A</t>
+        </is>
+      </c>
+      <c r="CE101" t="inlineStr">
+        <is>
+          <t>2, 4, 5, 12, 14, 29, 30, 66 - SM-T927A</t>
+        </is>
+      </c>
+      <c r="CF101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="CG101" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100 - Global</t>
+        </is>
+      </c>
+      <c r="CH101" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20 - Global</t>
+        </is>
+      </c>
+      <c r="CI101" t="inlineStr"/>
+      <c r="CJ101" t="inlineStr"/>
+      <c r="CK101" t="inlineStr"/>
+      <c r="CL101" t="inlineStr">
+        <is>
+          <t>HSPA, LTE - cellular model only</t>
+        </is>
+      </c>
+      <c r="CM101" t="inlineStr">
+        <is>
+          <t>HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN101" t="inlineStr"/>
+      <c r="CO101" t="inlineStr">
+        <is>
+          <t>Octa-core (2x1.6 GHz Cortex-A73 &amp; 6x1.6 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="CP101" t="inlineStr">
+        <is>
+          <t>Exynos 7884 (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ101" t="inlineStr">
+        <is>
+          <t>Mali-G71 MP2</t>
+        </is>
+      </c>
+      <c r="CR101" t="inlineStr">
+        <is>
+          <t>Android 8.1 (Oreo)</t>
+        </is>
+      </c>
+      <c r="CS101" t="inlineStr"/>
+      <c r="CT101" t="inlineStr">
+        <is>
+          <t>5 MP</t>
+        </is>
+      </c>
+      <c r="CU101" t="inlineStr">
+        <is>
+          <t>4K@30fps</t>
+        </is>
+      </c>
+      <c r="CV101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW101" t="inlineStr"/>
+      <c r="CX101" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers (4 speakers)</t>
+        </is>
+      </c>
+      <c r="CY101" t="inlineStr"/>
+      <c r="CZ101" t="inlineStr"/>
+      <c r="DA101" t="inlineStr"/>
+      <c r="DB101" t="inlineStr"/>
+      <c r="DC101" t="inlineStr"/>
+      <c r="DD101" t="inlineStr"/>
+      <c r="DE101" t="inlineStr"/>
+      <c r="DF101" t="inlineStr"/>
+      <c r="DG101" t="inlineStr"/>
+      <c r="DH101" t="inlineStr"/>
+      <c r="DI101" t="inlineStr"/>
+      <c r="DJ101" t="inlineStr"/>
+      <c r="DK101" t="inlineStr"/>
+      <c r="DL101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DM101" t="inlineStr"/>
+      <c r="DN101" t="inlineStr"/>
+      <c r="DO101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S10 5G</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Also available with 4G/LTE onlyVersions: SM-G977B (Global); SM-G977U (USA); SM-G977N (Korea); SM-G9770 (China)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s10_5g-9588.php</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2019, February. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>162.6</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>128GB | 256GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>About 380 EUR</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>25W wired, PD3.0 15W wireless (Qi) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Li-Ion 4500 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min)</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>162.6 x 77.1 x 7.9 mm (6.40 x 3.04 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>198 g (6.98 oz)</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>FM radio (USA &amp; Canada only)</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1, OTG, DisplayPort</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 6</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>1440 x 3040 pixels, 19:9 ratio (~502 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>6.7 inches, 112.0 cm 2 (~89.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED, HDR10+</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr"/>
+      <c r="BA102" t="inlineStr"/>
+      <c r="BB102" t="inlineStr"/>
+      <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>ANT+ Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BM102" t="inlineStr">
+        <is>
+          <t>2019, February. Released 2019, April</t>
+        </is>
+      </c>
+      <c r="BN102" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO102" t="inlineStr"/>
+      <c r="BP102" t="inlineStr">
+        <is>
+          <t>LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ102" t="inlineStr"/>
+      <c r="BR102" t="inlineStr">
+        <is>
+          <t>12 MP, f/1.5-2.4, 26mm (wide), 1/2.55", 1.4µm, dual pixel PDAF, OIS 12 MP, f/2.4, 52mm (telephoto), 1/3.6", 1.0µm, AF, OIS, 2x optical zoom 16 MP, f/2.2, 12mm (ultrawide), 1/3.1", 1.0µm, Super Steady video 0.3 MP, TOF 3D, (depth)</t>
+        </is>
+      </c>
+      <c r="BS102" t="inlineStr">
+        <is>
+          <t>4K@60fps (no EIS), 4K@30fps, 1080p@30/60/240fps, 720p@960fps, HDR10+, stereo sound rec., gyro-EIS &amp; OIS</t>
+        </is>
+      </c>
+      <c r="BT102" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="BU102" t="inlineStr"/>
+      <c r="BV102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW102" t="inlineStr">
+        <is>
+          <t>128GB 8GB RAM, 256GB 8GB RAM, 512GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BX102" t="inlineStr"/>
+      <c r="BY102" t="inlineStr">
+        <is>
+          <t>Crown Silver, Majestic Black, Royal Gold</t>
+        </is>
+      </c>
+      <c r="BZ102" t="inlineStr">
+        <is>
+          <t>SM-G977U, SM-G977N, SM-G977B, SM-G9770, SM-G977P, SM-G977T</t>
+        </is>
+      </c>
+      <c r="CA102" t="inlineStr">
+        <is>
+          <t>About 380 EUR</t>
+        </is>
+      </c>
+      <c r="CB102" t="inlineStr">
+        <is>
+          <t>0.46 W/kg (head)     1.59 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC102" t="inlineStr">
+        <is>
+          <t>0.26 W/kg (head)     1.55 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD102" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="CE102" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - Global, China</t>
+        </is>
+      </c>
+      <c r="CF102" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG102" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100 - USA</t>
+        </is>
+      </c>
+      <c r="CH102" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - Global</t>
+        </is>
+      </c>
+      <c r="CI102" t="inlineStr">
+        <is>
+          <t>78 NSA/Sub6</t>
+        </is>
+      </c>
+      <c r="CJ102" t="inlineStr"/>
+      <c r="CK102" t="inlineStr"/>
+      <c r="CL102" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (7CA) Cat20 2000/150 Mbps, 5G (2+ Gbps DL)</t>
+        </is>
+      </c>
+      <c r="CM102" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="CN102" t="inlineStr"/>
+      <c r="CO102" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.73 GHz Mongoose M4 &amp; 2x2.31 GHz Cortex-A75 &amp; 4x1.95 GHz Cortex-A55) - Global Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485) - USA</t>
+        </is>
+      </c>
+      <c r="CP102" t="inlineStr">
+        <is>
+          <t>Exynos 9820 (8 nm) - Global Qualcomm SM8150 Snapdragon 855 (7 nm) - USA</t>
+        </is>
+      </c>
+      <c r="CQ102" t="inlineStr">
+        <is>
+          <t>Mali-G76 MP12 - Global Adreno 640 - USA</t>
+        </is>
+      </c>
+      <c r="CR102" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4.1</t>
+        </is>
+      </c>
+      <c r="CS102" t="inlineStr"/>
+      <c r="CT102" t="inlineStr">
+        <is>
+          <t>10 MP, f/1.9, 26mm (wide), 1/3", 1.22µm, dual pixel PDAF TOF 3D, (depth sensor)</t>
+        </is>
+      </c>
+      <c r="CU102" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW102" t="inlineStr"/>
+      <c r="CX102" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY102" t="inlineStr"/>
+      <c r="CZ102" t="inlineStr"/>
+      <c r="DA102" t="inlineStr"/>
+      <c r="DB102" t="inlineStr"/>
+      <c r="DC102" t="inlineStr"/>
+      <c r="DD102" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support Tuned by AKG</t>
+        </is>
+      </c>
+      <c r="DE102" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 6), glass back (Gorilla Glass 6), aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF102" t="inlineStr"/>
+      <c r="DG102" t="inlineStr"/>
+      <c r="DH102" t="inlineStr"/>
+      <c r="DI102" t="inlineStr"/>
+      <c r="DJ102" t="inlineStr"/>
+      <c r="DK102" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL102" t="inlineStr"/>
+      <c r="DM102" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO - USA</t>
+        </is>
+      </c>
+      <c r="DN102" t="inlineStr">
+        <is>
+          <t>2, 3, 4, 5, 7, 8, 12, 13, 18, 19, 20, 26, 28, 38, 39, 40, 41, 46, 48, 66 - USA</t>
+        </is>
+      </c>
+      <c r="DO102" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 20, 24, 25, 26, 28, 38, 39, 40, 41, 66 - China</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S10+</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Versions: SM-G975F/DS (Global); SM-G975U (USA); SM-G975W (Canada)Also known as Samsung Galaxy S10+ Performance Edition (1 TB, 12 GB RAM model only)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s10+-9535.php</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>157.6</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>74.1</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>128GB | 1TB | 512GB</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>12GB | 6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>285.00</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>$ 285.00 / C$ 849.00 / € 159.00</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>15W wired, PD2.0 15W wireless (Qi) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Li-Ion 4100 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min)</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>157.6 x 74.1 x 7.8 mm (6.20 x 2.92 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>175 g / 198 g (ceramic) (6.17 oz)</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>FM radio (USA &amp; Canada only)</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1, OTG, DisplayPort</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr"/>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 6</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>1440 x 3040 pixels, 19:9 ratio (~522 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>6.4 inches, 103.8 cm 2 (~88.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED, HDR10+</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr"/>
+      <c r="BA103" t="inlineStr"/>
+      <c r="BB103" t="inlineStr"/>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>ANT+ Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer, heart rate, SpO2</t>
+        </is>
+      </c>
+      <c r="BM103" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO103" t="inlineStr"/>
+      <c r="BP103" t="inlineStr">
+        <is>
+          <t>LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ103" t="inlineStr"/>
+      <c r="BR103" t="inlineStr">
+        <is>
+          <t>12 MP, f/1.5-2.4, 26mm (wide), 1/2.55", 1.4µm, dual pixel PDAF, OIS 12 MP, f/2.4, 52mm (telephoto), 1/3.6", 1.0µm, AF, OIS, 2x optical zoom 16 MP, f/2.2, 12mm (ultrawide), 1/3.1", 1.0µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="BS103" t="inlineStr">
+        <is>
+          <t>4K@60fps (no EIS), 4K@30fps, 1080p@30/60/240fps, 720p@960fps, HDR10+, stereo sound rec., gyro-EIS &amp; OIS</t>
+        </is>
+      </c>
+      <c r="BT103" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="BU103" t="inlineStr"/>
+      <c r="BV103" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot) - dual SIM model only</t>
+        </is>
+      </c>
+      <c r="BW103" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 512GB 8GB RAM, 1TB 12GB RAM</t>
+        </is>
+      </c>
+      <c r="BX103" t="inlineStr"/>
+      <c r="BY103" t="inlineStr">
+        <is>
+          <t>Prism White, Prism Black, Prism Green, Prism Blue, Canary Yellow, Flamingo Pink, Ceramic Black, Ceramic White, Cardinal Red, Smoke Blue</t>
+        </is>
+      </c>
+      <c r="BZ103" t="inlineStr">
+        <is>
+          <t>SM-G975F, SM-G975U, SM-G975W, SM-G975U1, SM-G9750, SM-G975N, SM-G975X, SC-05L</t>
+        </is>
+      </c>
+      <c r="CA103" t="inlineStr">
+        <is>
+          <t>$ 285.00 / C$ 849.00 / € 159.00</t>
+        </is>
+      </c>
+      <c r="CB103" t="inlineStr">
+        <is>
+          <t>1.06 W/kg (head)     1.03 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC103" t="inlineStr">
+        <is>
+          <t>0.52 W/kg (head)     1.58 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD103" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 - USA</t>
+        </is>
+      </c>
+      <c r="CE103" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO - USA</t>
+        </is>
+      </c>
+      <c r="CF103" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG103" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - Global, USA</t>
+        </is>
+      </c>
+      <c r="CH103" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - Global</t>
+        </is>
+      </c>
+      <c r="CI103" t="inlineStr"/>
+      <c r="CJ103" t="inlineStr"/>
+      <c r="CK103" t="inlineStr"/>
+      <c r="CL103" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (7CA) Cat20 2000/150 Mbps</t>
+        </is>
+      </c>
+      <c r="CM103" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="CN103" t="inlineStr">
+        <is>
+          <t>-24.7 LUFS (Very good)</t>
+        </is>
+      </c>
+      <c r="CO103" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.73 GHz Mongoose M4 &amp; 2x2.31 GHz Cortex-A75 &amp; 4x1.95 GHz Cortex-A55) - EMEA/LATAM Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485) - USA/China</t>
+        </is>
+      </c>
+      <c r="CP103" t="inlineStr">
+        <is>
+          <t>Exynos 9820 (8 nm) - EMEA/LATAM Qualcomm SM8150 Snapdragon 855 (7 nm) - USA/China</t>
+        </is>
+      </c>
+      <c r="CQ103" t="inlineStr">
+        <is>
+          <t>Mali-G76 MP12 - EMEA/LATAM Adreno 640 - USA/China</t>
+        </is>
+      </c>
+      <c r="CR103" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4.1</t>
+        </is>
+      </c>
+      <c r="CS103" t="inlineStr"/>
+      <c r="CT103" t="inlineStr"/>
+      <c r="CU103" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW103" t="inlineStr"/>
+      <c r="CX103" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY103" t="inlineStr"/>
+      <c r="CZ103" t="inlineStr"/>
+      <c r="DA103" t="inlineStr"/>
+      <c r="DB103" t="inlineStr">
+        <is>
+          <t>Noise -93.0dB / Crosstalk -94.3dB</t>
+        </is>
+      </c>
+      <c r="DC103" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD103" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support Tuned by AKG</t>
+        </is>
+      </c>
+      <c r="DE103" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 6), glass back (Gorilla Glass 5), aluminum frame Glass front (Gorilla Glass 6), ceramic back, ceramic frame</t>
+        </is>
+      </c>
+      <c r="DF103" t="inlineStr"/>
+      <c r="DG103" t="inlineStr">
+        <is>
+          <t>Endurance rating 91h</t>
+        </is>
+      </c>
+      <c r="DH103" t="inlineStr">
+        <is>
+          <t>Contrast ratio: Infinite (nominal), 4.514 (sunlight)</t>
+        </is>
+      </c>
+      <c r="DI103" t="inlineStr">
+        <is>
+          <t>AnTuTu: 333736 (v7), 399901 (v8) GeekBench: 10387 (v4.4), 2190 (v5.1) GFXBench: 23fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ103" t="inlineStr">
+        <is>
+          <t>10 MP, f/1.9, 26mm (wide), 1/3", 1.22µm, dual pixel PDAF 8 MP, f/2.2, 22mm (wide), 1/4.0", 1.12µm, depth sensor</t>
+        </is>
+      </c>
+      <c r="DK103" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL103" t="inlineStr"/>
+      <c r="DM103" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 17, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 46, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="DN103" t="inlineStr"/>
+      <c r="DO103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Also available with 5GVersions: SM-G973F/DS (Global); SM-G973U (USA); SM-G973W (Canada); SM-G9730 (China)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s10-9536.php</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>149.9</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>128GB | 512GB</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>15W wired, PD2.0 15W wireless (Qi) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Li-Ion 3400 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min)</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>149.9 x 70.4 x 7.8 mm (5.90 x 2.77 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>157 g (5.54 oz)</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>FM radio (USA &amp; Canada only)</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1, OTG, DisplayPort</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 6</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>1440 x 3040 pixels, 19:9 ratio (~550 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>6.1 inches, 93.2 cm 2 (~88.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED, HDR10+</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr"/>
+      <c r="BA104" t="inlineStr"/>
+      <c r="BB104" t="inlineStr"/>
+      <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>ANT+ Samsung DeX (desktop experience support)</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>Fingerprint (under display, ultrasonic), accelerometer, gyro, proximity, compass, barometer, heart rate, SpO2</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO104" t="inlineStr"/>
+      <c r="BP104" t="inlineStr">
+        <is>
+          <t>LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ104" t="inlineStr"/>
+      <c r="BR104" t="inlineStr">
+        <is>
+          <t>12 MP, f/1.5-2.4, 26mm (wide), 1/2.55", 1.4µm, dual pixel PDAF, OIS 12 MP, f/2.4, 52mm (telephoto), 1/3.6", 1.0µm, AF, OIS, 2x optical zoom 16 MP, f/2.2, 12mm (ultrawide), 1/3.1", 1.0µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="BS104" t="inlineStr">
+        <is>
+          <t>4K@60fps (no EIS), 4K@30fps, 1080p@30/60/240fps, 720p@960fps, HDR10+, stereo sound rec., gyro-EIS &amp; OIS</t>
+        </is>
+      </c>
+      <c r="BT104" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="BU104" t="inlineStr"/>
+      <c r="BV104" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot) - dual SIM model only</t>
+        </is>
+      </c>
+      <c r="BW104" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 512GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BX104" t="inlineStr"/>
+      <c r="BY104" t="inlineStr">
+        <is>
+          <t>Prism White, Prism Black, Prism Green, Prism Blue, Canary Yellow, Flamingo Pink, Cardinal Red, Smoke Blue</t>
+        </is>
+      </c>
+      <c r="BZ104" t="inlineStr">
+        <is>
+          <t>SM-G973F, SM-G973U, SM-G973W, SM-G973U1, SM-G9730, SM-G973N, SM-G973X, SCV41, SM-G973C</t>
+        </is>
+      </c>
+      <c r="CA104" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="CB104" t="inlineStr">
+        <is>
+          <t>0.93 W/kg (head)     0.79 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC104" t="inlineStr">
+        <is>
+          <t>0.48 W/kg (head)     1.59 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD104" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 - USA</t>
+        </is>
+      </c>
+      <c r="CE104" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO - USA</t>
+        </is>
+      </c>
+      <c r="CF104" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG104" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - Global, USA</t>
+        </is>
+      </c>
+      <c r="CH104" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - Global</t>
+        </is>
+      </c>
+      <c r="CI104" t="inlineStr"/>
+      <c r="CJ104" t="inlineStr"/>
+      <c r="CK104" t="inlineStr"/>
+      <c r="CL104" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (7CA) Cat20 2000/150 Mbps</t>
+        </is>
+      </c>
+      <c r="CM104" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="CN104" t="inlineStr">
+        <is>
+          <t>Voice 82dB / Noise 74dB / Ring 85dB</t>
+        </is>
+      </c>
+      <c r="CO104" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.73 GHz Mongoose M4 &amp; 2x2.31 GHz Cortex-A75 &amp; 4x1.95 GHz Cortex-A55) - EMEA/LATAM Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485) - USA/China</t>
+        </is>
+      </c>
+      <c r="CP104" t="inlineStr">
+        <is>
+          <t>Exynos 9820 (8 nm) - EMEA/LATAM Qualcomm SM8150 Snapdragon 855 (7 nm) - USA/China</t>
+        </is>
+      </c>
+      <c r="CQ104" t="inlineStr">
+        <is>
+          <t>Mali-G76 MP12 - EMEA/LATAM Adreno 640 - USA/China</t>
+        </is>
+      </c>
+      <c r="CR104" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4.1</t>
+        </is>
+      </c>
+      <c r="CS104" t="inlineStr"/>
+      <c r="CT104" t="inlineStr">
+        <is>
+          <t>10 MP, f/1.9, 26mm (wide), 1/3", 1.22µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CU104" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW104" t="inlineStr"/>
+      <c r="CX104" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY104" t="inlineStr"/>
+      <c r="CZ104" t="inlineStr"/>
+      <c r="DA104" t="inlineStr"/>
+      <c r="DB104" t="inlineStr">
+        <is>
+          <t>Noise -92.2dB / Crosstalk -92.7dB</t>
+        </is>
+      </c>
+      <c r="DC104" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD104" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support Tuned by AKG</t>
+        </is>
+      </c>
+      <c r="DE104" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 6), glass back (Gorilla Glass 5), aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF104" t="inlineStr"/>
+      <c r="DG104" t="inlineStr">
+        <is>
+          <t>Endurance rating 79h</t>
+        </is>
+      </c>
+      <c r="DH104" t="inlineStr">
+        <is>
+          <t>Contrast ratio: Infinite (nominal), 4.498 (sunlight)</t>
+        </is>
+      </c>
+      <c r="DI104" t="inlineStr">
+        <is>
+          <t>AnTuTu: 328366 (v7) GeekBench: 10174 (v4.4) GFXBench: 23fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ104" t="inlineStr"/>
+      <c r="DK104" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL104" t="inlineStr"/>
+      <c r="DM104" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 17, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 46, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="DN104" t="inlineStr"/>
+      <c r="DO104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S10e</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Versions: SM-G970F/DS (Global); SM-G970U (USA); SM-G970W (Canada)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_s10e-9537.php</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>142.2</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>128GB | 256GB</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>6GB | 8GB</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>15W wired, PD2.0 15W wireless (Qi) 4.5W reverse wireless</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Li-Ion 3100 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min)</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>142.2 x 69.9 x 7.9 mm (5.60 x 2.75 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>· Nano-SIM · Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>150 g (5.29 oz)</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE, aptX</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS, GALILEO</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>FM radio (USA &amp; Canada only)</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>USB Type-C 3.1</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 5</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>1080 x 2280 pixels, 19:9 ratio (~438 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>5.8 inches, 82.8 cm 2 (~83.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Dynamic AMOLED, HDR10+</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr"/>
+      <c r="BA105" t="inlineStr"/>
+      <c r="BB105" t="inlineStr"/>
+      <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>ANT+</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass, barometer</t>
+        </is>
+      </c>
+      <c r="BM105" t="inlineStr">
+        <is>
+          <t>2019, February 20. Released 2019, March 08</t>
+        </is>
+      </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO105" t="inlineStr">
+        <is>
+          <t>12 MP, f/1.5-2.4, 26mm (wide), 1/2.55", 1.4µm, dual pixel PDAF, OIS 16 MP, f/2.2, 12mm (ultrawide), 1/3.1", 1.0µm, Super Steady video</t>
+        </is>
+      </c>
+      <c r="BP105" t="inlineStr">
+        <is>
+          <t>LED flash, auto-HDR, panorama</t>
+        </is>
+      </c>
+      <c r="BQ105" t="inlineStr"/>
+      <c r="BR105" t="inlineStr"/>
+      <c r="BS105" t="inlineStr">
+        <is>
+          <t>4K@60fps (no EIS), 4K@30fps, 1080p@30/60/240fps, 720p@960fps, HDR10+, stereo sound rec., gyro-EIS &amp; OIS</t>
+        </is>
+      </c>
+      <c r="BT105" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="BU105" t="inlineStr"/>
+      <c r="BV105" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot) - dual SIM model only</t>
+        </is>
+      </c>
+      <c r="BW105" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM, 256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="BX105" t="inlineStr"/>
+      <c r="BY105" t="inlineStr">
+        <is>
+          <t>Prism White, Prism Black, Prism Green, Prism Blue, Canary Yellow, Flamingo Pink</t>
+        </is>
+      </c>
+      <c r="BZ105" t="inlineStr">
+        <is>
+          <t>SM-G970F, SM-G970U, SM-G970W, SM-G9700, SM-G970U1, SM-G970N, SM-G970X</t>
+        </is>
+      </c>
+      <c r="CA105" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB105" t="inlineStr">
+        <is>
+          <t>0.56 W/kg (head)     0.70 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC105" t="inlineStr">
+        <is>
+          <t>0.58 W/kg (head)     1.57 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD105" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 - USA</t>
+        </is>
+      </c>
+      <c r="CE105" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO - USA</t>
+        </is>
+      </c>
+      <c r="CF105" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG105" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100 - Global, USA</t>
+        </is>
+      </c>
+      <c r="CH105" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 32, 38, 39, 40, 41, 66 - Global</t>
+        </is>
+      </c>
+      <c r="CI105" t="inlineStr"/>
+      <c r="CJ105" t="inlineStr"/>
+      <c r="CK105" t="inlineStr"/>
+      <c r="CL105" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (7CA) Cat20 2000/150 Mbps</t>
+        </is>
+      </c>
+      <c r="CM105" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE</t>
+        </is>
+      </c>
+      <c r="CN105" t="inlineStr">
+        <is>
+          <t>Voice 71dB / Noise 76dB / Ring 80dB</t>
+        </is>
+      </c>
+      <c r="CO105" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.73 GHz Mongoose M4 &amp; 2x2.31 GHz Cortex-A75 &amp; 4x1.95 GHz Cortex-A55) - EMEA/LATAM Octa-core (1x2.84 GHz Kryo 485 &amp; 3x2.42 GHz Kryo 485 &amp; 4x1.78 GHz Kryo 485) - USA/China</t>
+        </is>
+      </c>
+      <c r="CP105" t="inlineStr">
+        <is>
+          <t>Exynos 9820 (8 nm) - EMEA/LATAM Qualcomm SM8150 Snapdragon 855 (7 nm) - USA/China</t>
+        </is>
+      </c>
+      <c r="CQ105" t="inlineStr">
+        <is>
+          <t>Mali-G76 MP12 - EMEA/LATAM Adreno 640 - USA/China</t>
+        </is>
+      </c>
+      <c r="CR105" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 12, One UI 4.1</t>
+        </is>
+      </c>
+      <c r="CS105" t="inlineStr"/>
+      <c r="CT105" t="inlineStr">
+        <is>
+          <t>10 MP, f/1.9, 26mm (wide), 1/3", 1.22µm, dual pixel PDAF</t>
+        </is>
+      </c>
+      <c r="CU105" t="inlineStr">
+        <is>
+          <t>4K@30/60fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW105" t="inlineStr"/>
+      <c r="CX105" t="inlineStr">
+        <is>
+          <t>Yes, with stereo speakers</t>
+        </is>
+      </c>
+      <c r="CY105" t="inlineStr"/>
+      <c r="CZ105" t="inlineStr"/>
+      <c r="DA105" t="inlineStr"/>
+      <c r="DB105" t="inlineStr">
+        <is>
+          <t>Noise -92.9dB / Crosstalk -89.4dB</t>
+        </is>
+      </c>
+      <c r="DC105" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD105" t="inlineStr">
+        <is>
+          <t>High-bitrate audio support Tuned by AKG</t>
+        </is>
+      </c>
+      <c r="DE105" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 5), glass back (Gorilla Glass 5), aluminum frame</t>
+        </is>
+      </c>
+      <c r="DF105" t="inlineStr"/>
+      <c r="DG105" t="inlineStr">
+        <is>
+          <t>Endurance rating 83h</t>
+        </is>
+      </c>
+      <c r="DH105" t="inlineStr">
+        <is>
+          <t>Contrast ratio: infinite</t>
+        </is>
+      </c>
+      <c r="DI105" t="inlineStr">
+        <is>
+          <t>AnTuTu: 325192 (v7), 389694 (v8) GeekBench: 10081 (v4.4), 2141 (v5.1) GFXBench: 40fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ105" t="inlineStr"/>
+      <c r="DK105" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL105" t="inlineStr"/>
+      <c r="DM105" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 14, 17, 18, 19, 20, 25, 26, 28, 29, 30, 38, 39, 40, 41, 46, 66, 71 - USA</t>
+        </is>
+      </c>
+      <c r="DN105" t="inlineStr"/>
+      <c r="DO105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M40</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Versions: SM-M405FN/DS (Global); SM-M405F/DS (India); SM-M405G/DS (LATAM)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m40-9721.php</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2019, June. Released 2019, June</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>155.3</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>128GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>15W wired</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Li-Po 3500 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>155.3 x 73.9 x 7.9 mm (6.11 x 2.91 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>168 g (5.93 oz)</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr"/>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass 3</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>6.3 inches, 97.4 cm 2 (~84.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr"/>
+      <c r="BA106" t="inlineStr"/>
+      <c r="BB106" t="inlineStr"/>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM106" t="inlineStr">
+        <is>
+          <t>2019, June. Released 2019, June</t>
+        </is>
+      </c>
+      <c r="BN106" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO106" t="inlineStr"/>
+      <c r="BP106" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ106" t="inlineStr"/>
+      <c r="BR106" t="inlineStr">
+        <is>
+          <t>32 MP, f/1.7, 26mm (wide), 1/2.8", 0.8µm, PDAF 8 MP, f/2.2, 12mm (ultrawide), 1/4.0", 1.12µm, PDAF Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="BS106" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT106" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU106" t="inlineStr"/>
+      <c r="BV106" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="BW106" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BX106" t="inlineStr"/>
+      <c r="BY106" t="inlineStr">
+        <is>
+          <t>Seawater Blue, Midnight Blue, Cocktail Orange</t>
+        </is>
+      </c>
+      <c r="BZ106" t="inlineStr">
+        <is>
+          <t>SM-M405F, SM-M405FN, SM-M405G</t>
+        </is>
+      </c>
+      <c r="CA106" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="CB106" t="inlineStr">
+        <is>
+          <t>0.20 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CC106" t="inlineStr">
+        <is>
+          <t>0.27 W/kg (head)     1.17 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD106" t="inlineStr"/>
+      <c r="CE106" t="inlineStr"/>
+      <c r="CF106" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG106" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH106" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI106" t="inlineStr"/>
+      <c r="CJ106" t="inlineStr"/>
+      <c r="CK106" t="inlineStr"/>
+      <c r="CL106" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (2CA) Cat6 400/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM106" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN106" t="inlineStr"/>
+      <c r="CO106" t="inlineStr">
+        <is>
+          <t>Octa-core (2x2.0 GHz Kryo 460 Gold &amp; 6x1.7 GHz Kryo 460 Silver)</t>
+        </is>
+      </c>
+      <c r="CP106" t="inlineStr">
+        <is>
+          <t>Qualcomm SDM675 Snapdragon 675 (11 nm)</t>
+        </is>
+      </c>
+      <c r="CQ106" t="inlineStr">
+        <is>
+          <t>Adreno 612</t>
+        </is>
+      </c>
+      <c r="CR106" t="inlineStr">
+        <is>
+          <t>Android 9.0 (Pie), upgradable to Android 11, One UI 3.1</t>
+        </is>
+      </c>
+      <c r="CS106" t="inlineStr"/>
+      <c r="CT106" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, 26mm (wide), 1/3.06", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CU106" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW106" t="inlineStr"/>
+      <c r="CX106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY106" t="inlineStr"/>
+      <c r="CZ106" t="inlineStr"/>
+      <c r="DA106" t="inlineStr"/>
+      <c r="DB106" t="inlineStr"/>
+      <c r="DC106" t="inlineStr"/>
+      <c r="DD106" t="inlineStr"/>
+      <c r="DE106" t="inlineStr">
+        <is>
+          <t>Glass front (Gorilla Glass 3), plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF106" t="inlineStr"/>
+      <c r="DG106" t="inlineStr"/>
+      <c r="DH106" t="inlineStr"/>
+      <c r="DI106" t="inlineStr"/>
+      <c r="DJ106" t="inlineStr"/>
+      <c r="DK106" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL106" t="inlineStr"/>
+      <c r="DM106" t="inlineStr"/>
+      <c r="DN106" t="inlineStr"/>
+      <c r="DO106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Galaxy A40s in ChinaVersions: SM-M305F/DS, SM-M305FN/DS (Global); SM-M305M/DS (LATAM/Brazil); SM-M305G/DS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m30-9505.php</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2019, February 27. Released 2019, March</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>128GB | 32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>3GB | 4GB | 6GB</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>15W wired</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>159 x 75.1 x 8.5 mm (6.26 x 2.96 x 0.33 in)</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>174 g (6.14 oz)</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr"/>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~403 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>6.4 inches, 100.5 cm 2 (~84.2% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr"/>
+      <c r="BA107" t="inlineStr"/>
+      <c r="BB107" t="inlineStr"/>
+      <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM107" t="inlineStr">
+        <is>
+          <t>2019, February 27. Released 2019, March</t>
+        </is>
+      </c>
+      <c r="BN107" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO107" t="inlineStr"/>
+      <c r="BP107" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ107" t="inlineStr"/>
+      <c r="BR107" t="inlineStr">
+        <is>
+          <t>13 MP, f/1.9, PDAF 5 MP, f/2.2, 12mm (ultrawide) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="BS107" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT107" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU107" t="inlineStr"/>
+      <c r="BV107" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW107" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM, 32GB 4GB RAM, 64GB 4GB RAM, 64GB 6GB RAM, 128GB 6GB RAM</t>
+        </is>
+      </c>
+      <c r="BX107" t="inlineStr"/>
+      <c r="BY107" t="inlineStr">
+        <is>
+          <t>Black, Blue</t>
+        </is>
+      </c>
+      <c r="BZ107" t="inlineStr">
+        <is>
+          <t>SM-M305F, SM-M305FN, SM-M305G, SM-M305M, SM-A3051, SM-A3058, SM-A3050</t>
+        </is>
+      </c>
+      <c r="CA107" t="inlineStr">
+        <is>
+          <t>About 260 EUR</t>
+        </is>
+      </c>
+      <c r="CB107" t="inlineStr">
+        <is>
+          <t>0.28 W/kg (head)     0.39 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC107" t="inlineStr">
+        <is>
+          <t>0.45 W/kg (head)     1.32 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD107" t="inlineStr"/>
+      <c r="CE107" t="inlineStr"/>
+      <c r="CF107" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG107" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH107" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 20, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI107" t="inlineStr"/>
+      <c r="CJ107" t="inlineStr"/>
+      <c r="CK107" t="inlineStr"/>
+      <c r="CL107" t="inlineStr">
+        <is>
+          <t>HSPA, LTE</t>
+        </is>
+      </c>
+      <c r="CM107" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN107" t="inlineStr">
+        <is>
+          <t>Voice 65dB / Noise 66dB / Ring 70dB</t>
+        </is>
+      </c>
+      <c r="CO107" t="inlineStr">
+        <is>
+          <t>Octa-core (2x1.8 GHz Cortex-A73 &amp; 6x1.6 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="CP107" t="inlineStr">
+        <is>
+          <t>Exynos 7904 (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ107" t="inlineStr">
+        <is>
+          <t>Mali-G71 MP2</t>
+        </is>
+      </c>
+      <c r="CR107" t="inlineStr">
+        <is>
+          <t>Android 8.1 (Oreo), upgradable to Android 10, One UI 2</t>
+        </is>
+      </c>
+      <c r="CS107" t="inlineStr"/>
+      <c r="CT107" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0, 26mm (wide), 1/3.06", 1.0µm</t>
+        </is>
+      </c>
+      <c r="CU107" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW107" t="inlineStr"/>
+      <c r="CX107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY107" t="inlineStr"/>
+      <c r="CZ107" t="inlineStr"/>
+      <c r="DA107" t="inlineStr"/>
+      <c r="DB107" t="inlineStr">
+        <is>
+          <t>Noise -90.5dB / Crosstalk -90.0dB</t>
+        </is>
+      </c>
+      <c r="DC107" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD107" t="inlineStr"/>
+      <c r="DE107" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF107" t="inlineStr"/>
+      <c r="DG107" t="inlineStr">
+        <is>
+          <t>Endurance rating 119h</t>
+        </is>
+      </c>
+      <c r="DH107" t="inlineStr">
+        <is>
+          <t>640 nits max brightness (measured)</t>
+        </is>
+      </c>
+      <c r="DI107" t="inlineStr">
+        <is>
+          <t>AnTuTu: 101651 (v7) GeekBench: 4188 (v4.4) GFXBench: 4.6fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ107" t="inlineStr"/>
+      <c r="DK107" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL107" t="inlineStr"/>
+      <c r="DM107" t="inlineStr"/>
+      <c r="DN107" t="inlineStr"/>
+      <c r="DO107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M20</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Versions: SM-M205F/DS (Global); SM-M205FN/DS (Europe); SM-M205G/DS (APAC); SM-M205M/DS (LATAM/Brazil)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_galaxy_m20-9506.php</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24 UTC</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2019, January 28. Released 2019, February</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>156.4</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>32GB | 64GB</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>3GB | 4GB</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>About 400 EUR</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>15W wired</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Li-Po 5000 mAh, non-removable</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>156.4 x 74.5 x 8.8 mm (6.16 x 2.93 x 0.35 in)</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>186 g (6.56 oz)</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>Yes (market/region dependent)</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>1080 x 2340 pixels, 19.5:9 ratio (~409 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>6.3 inches, 97.4 cm 2 (~83.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>PLS LCD</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr"/>
+      <c r="BA108" t="inlineStr"/>
+      <c r="BB108" t="inlineStr"/>
+      <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="inlineStr">
+        <is>
+          <t>Fingerprint (rear-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM108" t="inlineStr">
+        <is>
+          <t>2019, January 28. Released 2019, February</t>
+        </is>
+      </c>
+      <c r="BN108" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO108" t="inlineStr">
+        <is>
+          <t>13 MP, f/1.9, 1/3.1", 1.12µm, PDAF 5 MP, f/2.2, 12mm (ultrawide)</t>
+        </is>
+      </c>
+      <c r="BP108" t="inlineStr">
+        <is>
+          <t>LED flash, panorama, HDR</t>
+        </is>
+      </c>
+      <c r="BQ108" t="inlineStr"/>
+      <c r="BR108" t="inlineStr"/>
+      <c r="BS108" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="BT108" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BU108" t="inlineStr"/>
+      <c r="BV108" t="inlineStr">
+        <is>
+          <t>microSDXC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW108" t="inlineStr">
+        <is>
+          <t>32GB 3GB RAM, 64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="BX108" t="inlineStr"/>
+      <c r="BY108" t="inlineStr">
+        <is>
+          <t>Ocean Blue, Charcoal Black</t>
+        </is>
+      </c>
+      <c r="BZ108" t="inlineStr">
+        <is>
+          <t>SM-M205F, SM-M205FN, SM-M205G, SM-M205M, SM-M205N</t>
+        </is>
+      </c>
+      <c r="CA108" t="inlineStr">
+        <is>
+          <t>About 400 EUR</t>
+        </is>
+      </c>
+      <c r="CB108" t="inlineStr"/>
+      <c r="CC108" t="inlineStr">
+        <is>
+          <t>0.25 W/kg (head)     1.59 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CD108" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CE108" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 28, 38, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="CF108" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG108" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH108" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 7, 8, 20, 38, 40, 41</t>
+        </is>
+      </c>
+      <c r="CI108" t="inlineStr"/>
+      <c r="CJ108" t="inlineStr"/>
+      <c r="CK108" t="inlineStr"/>
+      <c r="CL108" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/5.76 Mbps, LTE (2CA) Cat12 600/50 Mbps</t>
+        </is>
+      </c>
+      <c r="CM108" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="CN108" t="inlineStr">
+        <is>
+          <t>Voice 67dB / Noise 66dB / Ring 68dB</t>
+        </is>
+      </c>
+      <c r="CO108" t="inlineStr">
+        <is>
+          <t>Octa-core (2x1.8 GHz Cortex-A73 &amp; 6x1.6 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="CP108" t="inlineStr">
+        <is>
+          <t>Exynos 7904 (14 nm)</t>
+        </is>
+      </c>
+      <c r="CQ108" t="inlineStr">
+        <is>
+          <t>Mali-G71 MP2</t>
+        </is>
+      </c>
+      <c r="CR108" t="inlineStr">
+        <is>
+          <t>Android 8.1 (Oreo), upgradable to Android 10, One UI 2</t>
+        </is>
+      </c>
+      <c r="CS108" t="inlineStr"/>
+      <c r="CT108" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.0, 25mm (wide)</t>
+        </is>
+      </c>
+      <c r="CU108" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="CV108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW108" t="inlineStr"/>
+      <c r="CX108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY108" t="inlineStr"/>
+      <c r="CZ108" t="inlineStr"/>
+      <c r="DA108" t="inlineStr"/>
+      <c r="DB108" t="inlineStr">
+        <is>
+          <t>Noise -90.5dB / Crosstalk -91.7dB</t>
+        </is>
+      </c>
+      <c r="DC108" t="inlineStr">
+        <is>
+          <t>Photo / Video</t>
+        </is>
+      </c>
+      <c r="DD108" t="inlineStr"/>
+      <c r="DE108" t="inlineStr">
+        <is>
+          <t>Glass front, plastic back, plastic frame</t>
+        </is>
+      </c>
+      <c r="DF108" t="inlineStr"/>
+      <c r="DG108" t="inlineStr">
+        <is>
+          <t>Endurance rating 103h</t>
+        </is>
+      </c>
+      <c r="DH108" t="inlineStr">
+        <is>
+          <t>Contrast ratio: 1333:1 (nominal), 2.960 (sunlight)</t>
+        </is>
+      </c>
+      <c r="DI108" t="inlineStr">
+        <is>
+          <t>AnTuTu: 108658 (v7) GeekBench: 4160 (v4.4) GFXBench: 4.4fps (ES 3.1 onscreen)</t>
+        </is>
+      </c>
+      <c r="DJ108" t="inlineStr"/>
+      <c r="DK108" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="DL108" t="inlineStr"/>
+      <c r="DM108" t="inlineStr"/>
+      <c r="DN108" t="inlineStr"/>
+      <c r="DO108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gsmarena_new_2026-06-03.xlsx
+++ b/gsmarena_new_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO108"/>
+  <dimension ref="A1:DO125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30236,55 +30236,37 @@
           <t>2019, August 07. Released 2019, August 23</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H91" t="n">
+        <v>2019</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
+      <c r="J91" t="n">
+        <v>151</v>
+      </c>
+      <c r="K91" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="L91" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>168</v>
+      </c>
+      <c r="N91" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2280</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>401</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -30296,40 +30278,26 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
+      <c r="T91" t="n">
+        <v>12</v>
+      </c>
+      <c r="U91" t="n">
+        <v>10</v>
+      </c>
+      <c r="V91" t="n">
+        <v>3500</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1.52</v>
       </c>
       <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr"/>
@@ -30693,55 +30661,37 @@
           <t>2019, August. Released 2019, September</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H92" t="n">
+        <v>2019</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
+      <c r="J92" t="n">
+        <v>44</v>
+      </c>
+      <c r="K92" t="n">
+        <v>44</v>
+      </c>
+      <c r="L92" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M92" t="n">
+        <v>42</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>360</v>
+      </c>
+      <c r="P92" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>364</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -30755,10 +30705,8 @@
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+      <c r="V92" t="n">
+        <v>340</v>
       </c>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
@@ -31062,55 +31010,37 @@
           <t>2019, August. Released 2019, September</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H93" t="n">
+        <v>2019</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
+      <c r="J93" t="n">
+        <v>44</v>
+      </c>
+      <c r="K93" t="n">
+        <v>44</v>
+      </c>
+      <c r="L93" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M93" t="n">
+        <v>30</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O93" t="n">
+        <v>360</v>
+      </c>
+      <c r="P93" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>364</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -31124,10 +31054,8 @@
       </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+      <c r="V93" t="n">
+        <v>340</v>
       </c>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
@@ -31294,11 +31222,7 @@
       <c r="CC93" t="inlineStr"/>
       <c r="CD93" t="inlineStr"/>
       <c r="CE93" t="inlineStr"/>
-      <c r="CF93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CF93" t="inlineStr"/>
       <c r="CG93" t="inlineStr">
         <is>
           <t>HSDPA 900 / 2100 - 44mm LTE version only</t>
@@ -31415,55 +31339,37 @@
           <t>2019, August 12. Released 2019, August 27</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H94" t="n">
+        <v>2019</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>156.9</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
+      <c r="J94" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="K94" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L94" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M94" t="n">
+        <v>168</v>
+      </c>
+      <c r="N94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O94" t="n">
+        <v>720</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1520</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>271</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -31475,30 +31381,20 @@
           <t>2GB | 3GB</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
+      <c r="T94" t="n">
+        <v>13</v>
+      </c>
+      <c r="U94" t="n">
+        <v>8</v>
+      </c>
+      <c r="V94" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X94" t="n">
+        <v>1.06</v>
       </c>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
@@ -31804,55 +31700,37 @@
           <t>2019, July. Released 2019, August</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H95" t="n">
+        <v>2019</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>147.3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="J95" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="K95" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L95" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M95" t="n">
+        <v>141</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="O95" t="n">
+        <v>720</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1560</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>295</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -31864,30 +31742,20 @@
           <t>2GB | 3GB</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+      <c r="T95" t="n">
+        <v>8</v>
+      </c>
+      <c r="U95" t="n">
+        <v>5</v>
+      </c>
+      <c r="V95" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0.54</v>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
@@ -32197,55 +32065,37 @@
           <t>2019, July 31. Released 2019, August</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H96" t="n">
+        <v>2019</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>244.5</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>159.5</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
+      <c r="J96" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M96" t="n">
+        <v>420</v>
+      </c>
+      <c r="N96" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P96" t="n">
+        <v>2560</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>287</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -32257,32 +32107,22 @@
           <t>4GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
+      <c r="T96" t="n">
+        <v>13</v>
+      </c>
+      <c r="U96" t="n">
+        <v>8</v>
+      </c>
+      <c r="V96" t="n">
+        <v>7040</v>
       </c>
       <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
+      <c r="X96" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="Z96" t="n">
+        <v>1.22</v>
       </c>
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
@@ -32594,55 +32434,37 @@
           <t>2019, July 05. Released 2019, July</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H97" t="n">
+        <v>2019</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>124.4</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="J97" t="n">
+        <v>210</v>
+      </c>
+      <c r="K97" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
+        <v>345</v>
+      </c>
+      <c r="N97" t="n">
+        <v>8</v>
+      </c>
+      <c r="O97" t="n">
+        <v>800</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>189</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -32654,32 +32476,22 @@
           <t>2GB | 3GB</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
+      <c r="T97" t="n">
+        <v>8</v>
+      </c>
+      <c r="U97" t="n">
+        <v>2</v>
+      </c>
+      <c r="V97" t="n">
+        <v>5100</v>
       </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="Y97" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>1.19</v>
       </c>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
@@ -32967,55 +32779,37 @@
           <t>2019, June. Released 2019, July</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H98" t="n">
+        <v>2019</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>146.2</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="J98" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="K98" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L98" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M98" t="n">
+        <v>172</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
+      </c>
+      <c r="O98" t="n">
+        <v>720</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>294</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -33027,32 +32821,22 @@
           <t>3GB</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
+      <c r="T98" t="n">
+        <v>16</v>
+      </c>
+      <c r="U98" t="n">
+        <v>5</v>
+      </c>
+      <c r="V98" t="n">
+        <v>2800</v>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
+      <c r="Y98" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1.31</v>
       </c>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
@@ -33344,55 +33128,37 @@
           <t>2019, April. Released 2019, April</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H99" t="n">
+        <v>2019</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>141.6</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="J99" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="K99" t="n">
+        <v>71</v>
+      </c>
+      <c r="L99" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>142</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
+      </c>
+      <c r="O99" t="n">
+        <v>540</v>
+      </c>
+      <c r="P99" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>220</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -33404,32 +33170,22 @@
           <t>1GB</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
+      <c r="T99" t="n">
+        <v>5</v>
+      </c>
+      <c r="U99" t="n">
+        <v>5</v>
+      </c>
+      <c r="V99" t="n">
+        <v>2600</v>
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="Y99" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>1.09</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -33725,55 +33481,37 @@
           <t>2019, February. Released 2019, April</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H100" t="n">
+        <v>2019</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
+      <c r="J100" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="L100" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>25</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>360</v>
+      </c>
+      <c r="P100" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>302</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -33787,10 +33525,8 @@
       </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="V100" t="n">
+        <v>230</v>
       </c>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
@@ -33957,11 +33693,7 @@
       <c r="CC100" t="inlineStr"/>
       <c r="CD100" t="inlineStr"/>
       <c r="CE100" t="inlineStr"/>
-      <c r="CF100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CF100" t="inlineStr"/>
       <c r="CG100" t="inlineStr"/>
       <c r="CH100" t="inlineStr"/>
       <c r="CI100" t="inlineStr"/>
@@ -34070,51 +33802,35 @@
           <t>2019, April. Released 2019, April</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H101" t="n">
+        <v>2019</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>417.1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>263.4</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
+      <c r="J101" t="n">
+        <v>417.1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="L101" t="n">
+        <v>17.3</v>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="N101" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1920</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>127</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -34127,21 +33843,15 @@
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
+      <c r="U101" t="n">
+        <v>5</v>
+      </c>
+      <c r="V101" t="n">
+        <v>12000</v>
       </c>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="X101" t="n">
+        <v>1.14</v>
       </c>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
@@ -34310,11 +34020,7 @@
           <t>2, 4, 5, 12, 14, 29, 30, 66 - SM-T927A</t>
         </is>
       </c>
-      <c r="CF101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="CF101" t="inlineStr"/>
       <c r="CG101" t="inlineStr">
         <is>
           <t>HSDPA 900 / 2100 - Global</t>
@@ -34439,55 +34145,37 @@
           <t>2019, February. Released 2019, April</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H102" t="n">
+        <v>2019</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>162.6</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
+      <c r="J102" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="K102" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="L102" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M102" t="n">
+        <v>198</v>
+      </c>
+      <c r="N102" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P102" t="n">
+        <v>3040</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>502</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -34499,40 +34187,26 @@
           <t>8GB</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="T102" t="n">
+        <v>12</v>
+      </c>
+      <c r="U102" t="n">
+        <v>10</v>
+      </c>
+      <c r="V102" t="n">
+        <v>4500</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>1.55</v>
       </c>
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr"/>
@@ -34880,55 +34554,37 @@
           <t>2019, February 20. Released 2019, March 08</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H103" t="n">
+        <v>2019</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>157.6</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>74.1</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+      <c r="J103" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="K103" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L103" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M103" t="n">
+        <v>175</v>
+      </c>
+      <c r="N103" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3040</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>522</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -34940,50 +34596,32 @@
           <t>12GB | 6GB | 8GB</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>285.00</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>159.00</t>
-        </is>
+      <c r="T103" t="n">
+        <v>12</v>
+      </c>
+      <c r="U103" t="n">
+        <v>10</v>
+      </c>
+      <c r="V103" t="n">
+        <v>4100</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>285</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>159</v>
       </c>
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr"/>
@@ -35341,55 +34979,37 @@
           <t>2019, February 20. Released 2019, March 08</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H104" t="n">
+        <v>2019</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>149.9</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="J104" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="K104" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M104" t="n">
+        <v>157</v>
+      </c>
+      <c r="N104" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1440</v>
+      </c>
+      <c r="P104" t="n">
+        <v>3040</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>550</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -35401,40 +35021,26 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
+      <c r="T104" t="n">
+        <v>12</v>
+      </c>
+      <c r="U104" t="n">
+        <v>10</v>
+      </c>
+      <c r="V104" t="n">
+        <v>3400</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>1.59</v>
       </c>
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr"/>
@@ -35794,55 +35400,37 @@
           <t>2019, February 20. Released 2019, March 08</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H105" t="n">
+        <v>2019</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>142.2</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>2280</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
+      <c r="J105" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L105" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M105" t="n">
+        <v>150</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2280</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>438</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -35854,40 +35442,26 @@
           <t>6GB | 8GB</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="T105" t="n">
+        <v>12</v>
+      </c>
+      <c r="U105" t="n">
+        <v>10</v>
+      </c>
+      <c r="V105" t="n">
+        <v>3100</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>1.57</v>
       </c>
       <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr"/>
@@ -36247,55 +35821,37 @@
           <t>2019, June. Released 2019, June</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H106" t="n">
+        <v>2019</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>155.3</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J106" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="K106" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="L106" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M106" t="n">
+        <v>168</v>
+      </c>
+      <c r="N106" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P106" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>409</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
@@ -36307,36 +35863,24 @@
           <t>4GB | 6GB</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
+      <c r="T106" t="n">
+        <v>32</v>
+      </c>
+      <c r="U106" t="n">
+        <v>16</v>
+      </c>
+      <c r="V106" t="n">
+        <v>3500</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0.2</v>
       </c>
       <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="Y106" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1.17</v>
       </c>
       <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
@@ -36648,55 +36192,37 @@
           <t>2019, February 27. Released 2019, March</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H107" t="n">
+        <v>2019</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
+      <c r="J107" t="n">
+        <v>159</v>
+      </c>
+      <c r="K107" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="L107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M107" t="n">
+        <v>174</v>
+      </c>
+      <c r="N107" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P107" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>403</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
@@ -36708,40 +36234,26 @@
           <t>3GB | 4GB | 6GB</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
+      <c r="T107" t="n">
+        <v>13</v>
+      </c>
+      <c r="U107" t="n">
+        <v>16</v>
+      </c>
+      <c r="V107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1.32</v>
       </c>
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr"/>
@@ -37073,55 +36585,37 @@
           <t>2019, January 28. Released 2019, February</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="H108" t="n">
+        <v>2019</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>Discontinued</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>156.4</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="J108" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="K108" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="L108" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M108" t="n">
+        <v>186</v>
+      </c>
+      <c r="N108" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2340</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>409</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
@@ -37133,32 +36627,22 @@
           <t>3GB | 4GB</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
+      <c r="T108" t="n">
+        <v>13</v>
+      </c>
+      <c r="U108" t="n">
+        <v>8</v>
+      </c>
+      <c r="V108" t="n">
+        <v>5000</v>
       </c>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
+      <c r="Y108" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>1.59</v>
       </c>
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
@@ -37458,6 +36942,6183 @@
       <c r="DN108" t="inlineStr"/>
       <c r="DO108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Samsung T479 Gravity 3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>For T-Mobile</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_t479_gravity_3-3335.php</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>116.8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>70MB</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Up to 400 h</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Up to 6 h</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>116.8 x 53.6 x 15.2 mm (4.60 x 2.11 x 0.60 in)</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>123 g (4.34 oz)</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>A-GPS only; Google Maps</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr"/>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr"/>
+      <c r="BA109" t="inlineStr"/>
+      <c r="BB109" t="inlineStr"/>
+      <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>SNS integration T-Mobile Social Buzz MP4/H.264 player MP3/eAAC+/WAV player Organizer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, Push Email, IM, RSS</t>
+        </is>
+      </c>
+      <c r="BL109" t="inlineStr"/>
+      <c r="BM109" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BN109" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO109" t="inlineStr"/>
+      <c r="BP109" t="inlineStr"/>
+      <c r="BQ109" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR109" t="inlineStr"/>
+      <c r="BS109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT109" t="inlineStr"/>
+      <c r="BU109" t="inlineStr">
+        <is>
+          <t>90 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="BV109" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW109" t="inlineStr">
+        <is>
+          <t>70MB</t>
+        </is>
+      </c>
+      <c r="BX109" t="inlineStr">
+        <is>
+          <t>Yes, Photocall</t>
+        </is>
+      </c>
+      <c r="BY109" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ109" t="inlineStr"/>
+      <c r="CA109" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB109" t="inlineStr"/>
+      <c r="CC109" t="inlineStr">
+        <is>
+          <t>0.52 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD109" t="inlineStr"/>
+      <c r="CE109" t="inlineStr"/>
+      <c r="CF109" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG109" t="inlineStr">
+        <is>
+          <t>HSDPA 1700 / 2100</t>
+        </is>
+      </c>
+      <c r="CH109" t="inlineStr"/>
+      <c r="CI109" t="inlineStr"/>
+      <c r="CJ109" t="inlineStr"/>
+      <c r="CK109" t="inlineStr"/>
+      <c r="CL109" t="inlineStr">
+        <is>
+          <t>HSPA</t>
+        </is>
+      </c>
+      <c r="CM109" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN109" t="inlineStr"/>
+      <c r="CO109" t="inlineStr">
+        <is>
+          <t>184 MHz</t>
+        </is>
+      </c>
+      <c r="CP109" t="inlineStr"/>
+      <c r="CQ109" t="inlineStr"/>
+      <c r="CR109" t="inlineStr"/>
+      <c r="CS109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT109" t="inlineStr"/>
+      <c r="CU109" t="inlineStr"/>
+      <c r="CV109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW109" t="inlineStr"/>
+      <c r="CX109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY109" t="inlineStr"/>
+      <c r="CZ109" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA109" t="inlineStr"/>
+      <c r="DB109" t="inlineStr"/>
+      <c r="DC109" t="inlineStr"/>
+      <c r="DD109" t="inlineStr"/>
+      <c r="DE109" t="inlineStr"/>
+      <c r="DF109" t="inlineStr"/>
+      <c r="DG109" t="inlineStr"/>
+      <c r="DH109" t="inlineStr"/>
+      <c r="DI109" t="inlineStr"/>
+      <c r="DJ109" t="inlineStr"/>
+      <c r="DK109" t="inlineStr"/>
+      <c r="DL109" t="inlineStr"/>
+      <c r="DM109" t="inlineStr"/>
+      <c r="DN109" t="inlineStr"/>
+      <c r="DO109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Samsung :) Smiley</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>For T-MobileAlso known as Samsung T359</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung__)_smiley-3334.php</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>112.8</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Up to 300 h</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Up to 5 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>99.6 x 59.4 x 15 mm (3.92 x 2.34 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>112.8 g (3.95 oz)</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr"/>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>A-GPS only; Google Maps</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr"/>
+      <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr"/>
+      <c r="BA110" t="inlineStr"/>
+      <c r="BB110" t="inlineStr"/>
+      <c r="BC110" t="inlineStr"/>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>SNS integration T-Mobile Social Buzz MP4/H.264 player MP3/eAAC+/WAV player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ110" t="inlineStr"/>
+      <c r="BK110" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, Push Email, IM, RSS</t>
+        </is>
+      </c>
+      <c r="BL110" t="inlineStr"/>
+      <c r="BM110" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, June</t>
+        </is>
+      </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO110" t="inlineStr"/>
+      <c r="BP110" t="inlineStr"/>
+      <c r="BQ110" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR110" t="inlineStr"/>
+      <c r="BS110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT110" t="inlineStr"/>
+      <c r="BU110" t="inlineStr">
+        <is>
+          <t>90 received, dialed and missed calls</t>
+        </is>
+      </c>
+      <c r="BV110" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW110" t="inlineStr">
+        <is>
+          <t>50MB</t>
+        </is>
+      </c>
+      <c r="BX110" t="inlineStr">
+        <is>
+          <t>Yes, Photocall</t>
+        </is>
+      </c>
+      <c r="BY110" t="inlineStr">
+        <is>
+          <t>Black/Blue</t>
+        </is>
+      </c>
+      <c r="BZ110" t="inlineStr"/>
+      <c r="CA110" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB110" t="inlineStr">
+        <is>
+          <t>0.47 W/kg (head)     0.78 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC110" t="inlineStr">
+        <is>
+          <t>0.98 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD110" t="inlineStr"/>
+      <c r="CE110" t="inlineStr"/>
+      <c r="CF110" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG110" t="inlineStr">
+        <is>
+          <t>UMTS 1700 / 2100</t>
+        </is>
+      </c>
+      <c r="CH110" t="inlineStr"/>
+      <c r="CI110" t="inlineStr"/>
+      <c r="CJ110" t="inlineStr"/>
+      <c r="CK110" t="inlineStr"/>
+      <c r="CL110" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM110" t="inlineStr">
+        <is>
+          <t>GSM / UMTS</t>
+        </is>
+      </c>
+      <c r="CN110" t="inlineStr"/>
+      <c r="CO110" t="inlineStr">
+        <is>
+          <t>184 MHz</t>
+        </is>
+      </c>
+      <c r="CP110" t="inlineStr"/>
+      <c r="CQ110" t="inlineStr"/>
+      <c r="CR110" t="inlineStr"/>
+      <c r="CS110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT110" t="inlineStr"/>
+      <c r="CU110" t="inlineStr"/>
+      <c r="CV110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW110" t="inlineStr"/>
+      <c r="CX110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY110" t="inlineStr"/>
+      <c r="CZ110" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA110" t="inlineStr"/>
+      <c r="DB110" t="inlineStr"/>
+      <c r="DC110" t="inlineStr"/>
+      <c r="DD110" t="inlineStr"/>
+      <c r="DE110" t="inlineStr"/>
+      <c r="DF110" t="inlineStr"/>
+      <c r="DG110" t="inlineStr"/>
+      <c r="DH110" t="inlineStr"/>
+      <c r="DI110" t="inlineStr"/>
+      <c r="DJ110" t="inlineStr"/>
+      <c r="DK110" t="inlineStr"/>
+      <c r="DL110" t="inlineStr"/>
+      <c r="DM110" t="inlineStr"/>
+      <c r="DN110" t="inlineStr"/>
+      <c r="DO110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Samsung C5010 Squash</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_c5010_squash-3333.php</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, Q3</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>42MB</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Up to 550 h (2G) / Up to 400 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Up to 6 h (2G) / Up to 3 h (3G)</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 800 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>115 x 46 x 12.8 mm (4.53 x 1.81 x 0.50 in)</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>81 g (2.86 oz)</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr"/>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr"/>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr"/>
+      <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels (~102 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.6 cm 2 (~23.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr"/>
+      <c r="BA111" t="inlineStr"/>
+      <c r="BB111" t="inlineStr"/>
+      <c r="BC111" t="inlineStr"/>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>MP3/AAC player MP4/H.264 player Organizer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr"/>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr"/>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr"/>
+      <c r="BK111" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL111" t="inlineStr"/>
+      <c r="BM111" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, Q3</t>
+        </is>
+      </c>
+      <c r="BN111" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO111" t="inlineStr"/>
+      <c r="BP111" t="inlineStr"/>
+      <c r="BQ111" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR111" t="inlineStr"/>
+      <c r="BS111" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="BT111" t="inlineStr"/>
+      <c r="BU111" t="inlineStr">
+        <is>
+          <t>30 dialed, 30 received, 30 missed calls</t>
+        </is>
+      </c>
+      <c r="BV111" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW111" t="inlineStr">
+        <is>
+          <t>42MB</t>
+        </is>
+      </c>
+      <c r="BX111" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="BY111" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ111" t="inlineStr"/>
+      <c r="CA111" t="inlineStr">
+        <is>
+          <t>About 80 EUR</t>
+        </is>
+      </c>
+      <c r="CB111" t="inlineStr"/>
+      <c r="CC111" t="inlineStr">
+        <is>
+          <t>0.71 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD111" t="inlineStr"/>
+      <c r="CE111" t="inlineStr"/>
+      <c r="CF111" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG111" t="inlineStr">
+        <is>
+          <t>UMTS 900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH111" t="inlineStr"/>
+      <c r="CI111" t="inlineStr"/>
+      <c r="CJ111" t="inlineStr"/>
+      <c r="CK111" t="inlineStr"/>
+      <c r="CL111" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM111" t="inlineStr">
+        <is>
+          <t>GSM / UMTS</t>
+        </is>
+      </c>
+      <c r="CN111" t="inlineStr"/>
+      <c r="CO111" t="inlineStr"/>
+      <c r="CP111" t="inlineStr"/>
+      <c r="CQ111" t="inlineStr"/>
+      <c r="CR111" t="inlineStr"/>
+      <c r="CS111" t="inlineStr"/>
+      <c r="CT111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CU111" t="inlineStr"/>
+      <c r="CV111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW111" t="inlineStr"/>
+      <c r="CX111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY111" t="inlineStr"/>
+      <c r="CZ111" t="inlineStr"/>
+      <c r="DA111" t="inlineStr"/>
+      <c r="DB111" t="inlineStr"/>
+      <c r="DC111" t="inlineStr"/>
+      <c r="DD111" t="inlineStr"/>
+      <c r="DE111" t="inlineStr"/>
+      <c r="DF111" t="inlineStr"/>
+      <c r="DG111" t="inlineStr"/>
+      <c r="DH111" t="inlineStr"/>
+      <c r="DI111" t="inlineStr"/>
+      <c r="DJ111" t="inlineStr"/>
+      <c r="DK111" t="inlineStr"/>
+      <c r="DL111" t="inlineStr"/>
+      <c r="DM111" t="inlineStr"/>
+      <c r="DN111" t="inlineStr"/>
+      <c r="DO111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Samsung i897 Captivate</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AT&amp;T version ofSamsung Galaxy S</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i897_captivate-3408.php</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>122.4</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Up to 750 h (2G) / Up to 576 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Up to 13 h 30 min (2G) / Up to 6 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>122.4 x 64.2 x 9.9 mm (4.82 x 2.53 x 0.39 in)</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>118 g (4.16 oz)</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>3.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr"/>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n; DLNA</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>TouchWiz 3.0 UI</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~58.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr"/>
+      <c r="BA112" t="inlineStr"/>
+      <c r="BB112" t="inlineStr"/>
+      <c r="BC112" t="inlineStr"/>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>MP4/DivX/WMV/H.264 player MP3/WAV/eAAC+/FLAC player Organizer Photo/video editor Voice memo/dial/commands Predictive text input (Swype)</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr"/>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>HTML, Adobe Flash Lite</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr"/>
+      <c r="BH112" t="inlineStr"/>
+      <c r="BI112" t="inlineStr"/>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM112" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BN112" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO112" t="inlineStr"/>
+      <c r="BP112" t="inlineStr"/>
+      <c r="BQ112" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR112" t="inlineStr"/>
+      <c r="BS112" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT112" t="inlineStr"/>
+      <c r="BU112" t="inlineStr"/>
+      <c r="BV112" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW112" t="inlineStr">
+        <is>
+          <t>16GB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BX112" t="inlineStr"/>
+      <c r="BY112" t="inlineStr">
+        <is>
+          <t>Black and Grey</t>
+        </is>
+      </c>
+      <c r="BZ112" t="inlineStr"/>
+      <c r="CA112" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="CB112" t="inlineStr"/>
+      <c r="CC112" t="inlineStr">
+        <is>
+          <t>0.37 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD112" t="inlineStr"/>
+      <c r="CE112" t="inlineStr"/>
+      <c r="CF112" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG112" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH112" t="inlineStr"/>
+      <c r="CI112" t="inlineStr"/>
+      <c r="CJ112" t="inlineStr"/>
+      <c r="CK112" t="inlineStr"/>
+      <c r="CL112" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/5.76 Mbps</t>
+        </is>
+      </c>
+      <c r="CM112" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN112" t="inlineStr"/>
+      <c r="CO112" t="inlineStr">
+        <is>
+          <t>1.0 GHz Cortex-A8</t>
+        </is>
+      </c>
+      <c r="CP112" t="inlineStr">
+        <is>
+          <t>Hummingbird</t>
+        </is>
+      </c>
+      <c r="CQ112" t="inlineStr">
+        <is>
+          <t>PowerVR SGX540</t>
+        </is>
+      </c>
+      <c r="CR112" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.3 (Gingerbread)</t>
+        </is>
+      </c>
+      <c r="CS112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT112" t="inlineStr"/>
+      <c r="CU112" t="inlineStr"/>
+      <c r="CV112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW112" t="inlineStr"/>
+      <c r="CX112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY112" t="inlineStr"/>
+      <c r="CZ112" t="inlineStr"/>
+      <c r="DA112" t="inlineStr"/>
+      <c r="DB112" t="inlineStr"/>
+      <c r="DC112" t="inlineStr"/>
+      <c r="DD112" t="inlineStr"/>
+      <c r="DE112" t="inlineStr"/>
+      <c r="DF112" t="inlineStr"/>
+      <c r="DG112" t="inlineStr"/>
+      <c r="DH112" t="inlineStr"/>
+      <c r="DI112" t="inlineStr"/>
+      <c r="DJ112" t="inlineStr"/>
+      <c r="DK112" t="inlineStr"/>
+      <c r="DL112" t="inlineStr"/>
+      <c r="DM112" t="inlineStr"/>
+      <c r="DN112" t="inlineStr"/>
+      <c r="DO112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Samsung B7350 Omnia PRO 4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Omnia 735</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_b7350_omnia_pro_4-3401.php</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>117.7</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>200MB</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Up to 500 h (2G) / Up to 400 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Up to 9 h 20 min (2G) / Up to 5 h 40 min (3G)</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>117.7 x 59.8 x 11.9 mm (4.63 x 2.35 x 0.47 in)</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>122 g (4.30 oz)</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr"/>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>320 x 320 pixels, 1:1 ratio (~173 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>2.62 inches, 22.1 cm 2 (~31.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>TFT resistive touchscreen, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr"/>
+      <c r="BA113" t="inlineStr"/>
+      <c r="BB113" t="inlineStr"/>
+      <c r="BC113" t="inlineStr"/>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>MP3/WMA/WAV/eAAC+ player MP4/WMV9/H.264 player Windows Live, Yahoo! Microsoft Outlook Mobile Pocket Office Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr"/>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>WAP 2.0 / xHTML, HTML, Adobe Flash Lite</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr"/>
+      <c r="BH113" t="inlineStr"/>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
+      <c r="BM113" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO113" t="inlineStr"/>
+      <c r="BP113" t="inlineStr"/>
+      <c r="BQ113" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR113" t="inlineStr"/>
+      <c r="BS113" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="BT113" t="inlineStr"/>
+      <c r="BU113" t="inlineStr"/>
+      <c r="BV113" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW113" t="inlineStr">
+        <is>
+          <t>200MB</t>
+        </is>
+      </c>
+      <c r="BX113" t="inlineStr"/>
+      <c r="BY113" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ113" t="inlineStr"/>
+      <c r="CA113" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="CB113" t="inlineStr">
+        <is>
+          <t>0.42 W/kg (head)     0.43 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC113" t="inlineStr">
+        <is>
+          <t>0.64 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD113" t="inlineStr"/>
+      <c r="CE113" t="inlineStr"/>
+      <c r="CF113" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG113" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH113" t="inlineStr"/>
+      <c r="CI113" t="inlineStr"/>
+      <c r="CJ113" t="inlineStr"/>
+      <c r="CK113" t="inlineStr"/>
+      <c r="CL113" t="inlineStr">
+        <is>
+          <t>HSPA 7.2/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM113" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN113" t="inlineStr"/>
+      <c r="CO113" t="inlineStr"/>
+      <c r="CP113" t="inlineStr"/>
+      <c r="CQ113" t="inlineStr"/>
+      <c r="CR113" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.5 Professional</t>
+        </is>
+      </c>
+      <c r="CS113" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="CT113" t="inlineStr"/>
+      <c r="CU113" t="inlineStr"/>
+      <c r="CV113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW113" t="inlineStr"/>
+      <c r="CX113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY113" t="inlineStr"/>
+      <c r="CZ113" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA113" t="inlineStr"/>
+      <c r="DB113" t="inlineStr"/>
+      <c r="DC113" t="inlineStr"/>
+      <c r="DD113" t="inlineStr"/>
+      <c r="DE113" t="inlineStr"/>
+      <c r="DF113" t="inlineStr"/>
+      <c r="DG113" t="inlineStr"/>
+      <c r="DH113" t="inlineStr"/>
+      <c r="DI113" t="inlineStr"/>
+      <c r="DJ113" t="inlineStr"/>
+      <c r="DK113" t="inlineStr"/>
+      <c r="DL113" t="inlineStr"/>
+      <c r="DM113" t="inlineStr"/>
+      <c r="DN113" t="inlineStr"/>
+      <c r="DO113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Samsung B6520 Omnia PRO 5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_b6520_omnia_pro_5-3402.php</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>220MB</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Up to 600 h (2G) / Up to 440 h (3G)</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Up to 8 h (2G) / Up to 7 h 30 min (3G)</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>116.5 x 61.8 x 11.5 mm (4.59 x 2.43 x 0.45 in)</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>111 g (3.92 oz)</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr"/>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr"/>
+      <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>320 x 240 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~24.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr"/>
+      <c r="BA114" t="inlineStr"/>
+      <c r="BB114" t="inlineStr"/>
+      <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>MP3/WMA/WAV/eAAC+ player MP4/WMV9/H.264/DivX player Microsoft Outlook Mobile Pocket Office editor Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>WAP 2.0 / xHTML, HTML, Adobe Flash Lite</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr"/>
+      <c r="BM114" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, October</t>
+        </is>
+      </c>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO114" t="inlineStr"/>
+      <c r="BP114" t="inlineStr"/>
+      <c r="BQ114" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR114" t="inlineStr"/>
+      <c r="BS114" t="inlineStr">
+        <is>
+          <t>320p@15fps</t>
+        </is>
+      </c>
+      <c r="BT114" t="inlineStr"/>
+      <c r="BU114" t="inlineStr"/>
+      <c r="BV114" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW114" t="inlineStr">
+        <is>
+          <t>220MB</t>
+        </is>
+      </c>
+      <c r="BX114" t="inlineStr"/>
+      <c r="BY114" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ114" t="inlineStr"/>
+      <c r="CA114" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="CB114" t="inlineStr">
+        <is>
+          <t>1.02 W/kg (head)     0.37 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC114" t="inlineStr">
+        <is>
+          <t>0.79 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD114" t="inlineStr"/>
+      <c r="CE114" t="inlineStr"/>
+      <c r="CF114" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG114" t="inlineStr">
+        <is>
+          <t>HSDPA 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="CH114" t="inlineStr"/>
+      <c r="CI114" t="inlineStr"/>
+      <c r="CJ114" t="inlineStr"/>
+      <c r="CK114" t="inlineStr"/>
+      <c r="CL114" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM114" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN114" t="inlineStr"/>
+      <c r="CO114" t="inlineStr"/>
+      <c r="CP114" t="inlineStr"/>
+      <c r="CQ114" t="inlineStr"/>
+      <c r="CR114" t="inlineStr">
+        <is>
+          <t>Microsoft Windows Mobile 6.5 Standard</t>
+        </is>
+      </c>
+      <c r="CS114" t="inlineStr"/>
+      <c r="CT114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CU114" t="inlineStr"/>
+      <c r="CV114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW114" t="inlineStr"/>
+      <c r="CX114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY114" t="inlineStr"/>
+      <c r="CZ114" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA114" t="inlineStr"/>
+      <c r="DB114" t="inlineStr"/>
+      <c r="DC114" t="inlineStr"/>
+      <c r="DD114" t="inlineStr"/>
+      <c r="DE114" t="inlineStr"/>
+      <c r="DF114" t="inlineStr"/>
+      <c r="DG114" t="inlineStr"/>
+      <c r="DH114" t="inlineStr"/>
+      <c r="DI114" t="inlineStr"/>
+      <c r="DJ114" t="inlineStr"/>
+      <c r="DK114" t="inlineStr"/>
+      <c r="DL114" t="inlineStr"/>
+      <c r="DM114" t="inlineStr"/>
+      <c r="DN114" t="inlineStr"/>
+      <c r="DO114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Samsung U320 Haven</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>For Verizon</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_u320_haven-3433.php</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>24MB</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>16MB</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Up to 336 h</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>100 x 51 x 18 mm (3.94 x 2.01 x 0.71 in)</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>99 g (3.49 oz)</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr"/>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>E911 call only</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>microUSB</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>External 1" 56K display (CSTN, 96x96 pixels)</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels (~128 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.2 cm 2 (~29.9% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr"/>
+      <c r="BA115" t="inlineStr"/>
+      <c r="BB115" t="inlineStr"/>
+      <c r="BC115" t="inlineStr"/>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>MP3/AAC player MP4/H.263 player Organizer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr"/>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr">
+        <is>
+          <t>SMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL115" t="inlineStr"/>
+      <c r="BM115" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BN115" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO115" t="inlineStr"/>
+      <c r="BP115" t="inlineStr"/>
+      <c r="BQ115" t="inlineStr"/>
+      <c r="BR115" t="inlineStr"/>
+      <c r="BS115" t="inlineStr"/>
+      <c r="BT115" t="inlineStr"/>
+      <c r="BU115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BW115" t="inlineStr">
+        <is>
+          <t>24MB 16MB RAM 64MB ROM</t>
+        </is>
+      </c>
+      <c r="BX115" t="inlineStr">
+        <is>
+          <t>500 entries</t>
+        </is>
+      </c>
+      <c r="BY115" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ115" t="inlineStr"/>
+      <c r="CA115" t="inlineStr">
+        <is>
+          <t>About 90 EUR</t>
+        </is>
+      </c>
+      <c r="CB115" t="inlineStr">
+        <is>
+          <t>0.41 W/kg (head)     0.67 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC115" t="inlineStr"/>
+      <c r="CD115" t="inlineStr"/>
+      <c r="CE115" t="inlineStr"/>
+      <c r="CF115" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG115" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CH115" t="inlineStr"/>
+      <c r="CI115" t="inlineStr"/>
+      <c r="CJ115" t="inlineStr"/>
+      <c r="CK115" t="inlineStr"/>
+      <c r="CL115" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM115" t="inlineStr">
+        <is>
+          <t>CDMA / CDMA2000</t>
+        </is>
+      </c>
+      <c r="CN115" t="inlineStr"/>
+      <c r="CO115" t="inlineStr"/>
+      <c r="CP115" t="inlineStr"/>
+      <c r="CQ115" t="inlineStr"/>
+      <c r="CR115" t="inlineStr"/>
+      <c r="CS115" t="inlineStr"/>
+      <c r="CT115" t="inlineStr"/>
+      <c r="CU115" t="inlineStr"/>
+      <c r="CV115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW115" t="inlineStr"/>
+      <c r="CX115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY115" t="inlineStr"/>
+      <c r="CZ115" t="inlineStr"/>
+      <c r="DA115" t="inlineStr"/>
+      <c r="DB115" t="inlineStr"/>
+      <c r="DC115" t="inlineStr"/>
+      <c r="DD115" t="inlineStr">
+        <is>
+          <t>2.5 mm audio jack</t>
+        </is>
+      </c>
+      <c r="DE115" t="inlineStr"/>
+      <c r="DF115" t="inlineStr"/>
+      <c r="DG115" t="inlineStr"/>
+      <c r="DH115" t="inlineStr"/>
+      <c r="DI115" t="inlineStr"/>
+      <c r="DJ115" t="inlineStr"/>
+      <c r="DK115" t="inlineStr"/>
+      <c r="DL115" t="inlineStr"/>
+      <c r="DM115" t="inlineStr"/>
+      <c r="DN115" t="inlineStr"/>
+      <c r="DO115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Samsung U460 Intensity II</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>For Verizon</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_u460_intensity_ii-3450.php</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Up to 300 h</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Up to 5 h</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1000 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>124 x 73 x 17.9 mm (4.88 x 2.87 x 0.70 in)</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>116 g (4.09 oz)</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr"/>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>A-GPS only; VZ Navigator</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr"/>
+      <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~182 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.0 cm 2 (~16.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr"/>
+      <c r="BA116" t="inlineStr"/>
+      <c r="BB116" t="inlineStr"/>
+      <c r="BC116" t="inlineStr"/>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>Social Beat app for SNS integration Media Center MP4/H.263 player MP3/AAC+/WMA player Organizer Voice memo/dial Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL116" t="inlineStr"/>
+      <c r="BM116" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BN116" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO116" t="inlineStr"/>
+      <c r="BP116" t="inlineStr"/>
+      <c r="BQ116" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR116" t="inlineStr"/>
+      <c r="BS116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BT116" t="inlineStr"/>
+      <c r="BU116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV116" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW116" t="inlineStr"/>
+      <c r="BX116" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="BY116" t="inlineStr">
+        <is>
+          <t>Deep Gray, Metallic Blue</t>
+        </is>
+      </c>
+      <c r="BZ116" t="inlineStr"/>
+      <c r="CA116" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="CB116" t="inlineStr">
+        <is>
+          <t>1.04 W/kg (head)     0.50 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC116" t="inlineStr"/>
+      <c r="CD116" t="inlineStr"/>
+      <c r="CE116" t="inlineStr"/>
+      <c r="CF116" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG116" t="inlineStr">
+        <is>
+          <t>CDMA2000 1x</t>
+        </is>
+      </c>
+      <c r="CH116" t="inlineStr"/>
+      <c r="CI116" t="inlineStr"/>
+      <c r="CJ116" t="inlineStr"/>
+      <c r="CK116" t="inlineStr"/>
+      <c r="CL116" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM116" t="inlineStr">
+        <is>
+          <t>CDMA / CDMA2000</t>
+        </is>
+      </c>
+      <c r="CN116" t="inlineStr"/>
+      <c r="CO116" t="inlineStr"/>
+      <c r="CP116" t="inlineStr"/>
+      <c r="CQ116" t="inlineStr"/>
+      <c r="CR116" t="inlineStr"/>
+      <c r="CS116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT116" t="inlineStr"/>
+      <c r="CU116" t="inlineStr"/>
+      <c r="CV116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW116" t="inlineStr"/>
+      <c r="CX116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY116" t="inlineStr"/>
+      <c r="CZ116" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA116" t="inlineStr"/>
+      <c r="DB116" t="inlineStr"/>
+      <c r="DC116" t="inlineStr"/>
+      <c r="DD116" t="inlineStr">
+        <is>
+          <t>2.5 mm audio jack</t>
+        </is>
+      </c>
+      <c r="DE116" t="inlineStr"/>
+      <c r="DF116" t="inlineStr"/>
+      <c r="DG116" t="inlineStr"/>
+      <c r="DH116" t="inlineStr"/>
+      <c r="DI116" t="inlineStr"/>
+      <c r="DJ116" t="inlineStr"/>
+      <c r="DK116" t="inlineStr"/>
+      <c r="DL116" t="inlineStr"/>
+      <c r="DM116" t="inlineStr"/>
+      <c r="DN116" t="inlineStr"/>
+      <c r="DO116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Samsung M350 Seek</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>For Sprint</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_m350_seek-3434.php</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>128MB | 256MB</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>128MB</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Up to 5 h 40 min</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>105 x 53 x 15 mm (4.13 x 2.09 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>109 g (3.84 oz)</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr"/>
+      <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~154 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>2.6 inches, 20.9 cm 2 (~37.6% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>TFT,  256K colors</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr"/>
+      <c r="BA117" t="inlineStr"/>
+      <c r="BB117" t="inlineStr"/>
+      <c r="BC117" t="inlineStr"/>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>MP4/H.263 player MP3/AAC+ player Organizer Facebook, Twitter apps Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr"/>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr">
+        <is>
+          <t>SMS, MMS, Email, IM</t>
+        </is>
+      </c>
+      <c r="BL117" t="inlineStr"/>
+      <c r="BM117" t="inlineStr">
+        <is>
+          <t>2010, May. Released 2010, May</t>
+        </is>
+      </c>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO117" t="inlineStr"/>
+      <c r="BP117" t="inlineStr"/>
+      <c r="BQ117" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR117" t="inlineStr"/>
+      <c r="BS117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT117" t="inlineStr"/>
+      <c r="BU117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BV117" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW117" t="inlineStr">
+        <is>
+          <t>128MB RAM, 256MB ROM</t>
+        </is>
+      </c>
+      <c r="BX117" t="inlineStr">
+        <is>
+          <t>600 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="BY117" t="inlineStr">
+        <is>
+          <t>Blue, Red, Pink</t>
+        </is>
+      </c>
+      <c r="BZ117" t="inlineStr"/>
+      <c r="CA117" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB117" t="inlineStr">
+        <is>
+          <t>1.08 W/kg (head)     1.31 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC117" t="inlineStr"/>
+      <c r="CD117" t="inlineStr"/>
+      <c r="CE117" t="inlineStr"/>
+      <c r="CF117" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG117" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CH117" t="inlineStr"/>
+      <c r="CI117" t="inlineStr"/>
+      <c r="CJ117" t="inlineStr"/>
+      <c r="CK117" t="inlineStr"/>
+      <c r="CL117" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="CM117" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="CN117" t="inlineStr"/>
+      <c r="CO117" t="inlineStr"/>
+      <c r="CP117" t="inlineStr"/>
+      <c r="CQ117" t="inlineStr"/>
+      <c r="CR117" t="inlineStr"/>
+      <c r="CS117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT117" t="inlineStr"/>
+      <c r="CU117" t="inlineStr"/>
+      <c r="CV117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW117" t="inlineStr"/>
+      <c r="CX117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY117" t="inlineStr"/>
+      <c r="CZ117" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA117" t="inlineStr"/>
+      <c r="DB117" t="inlineStr"/>
+      <c r="DC117" t="inlineStr"/>
+      <c r="DD117" t="inlineStr"/>
+      <c r="DE117" t="inlineStr"/>
+      <c r="DF117" t="inlineStr"/>
+      <c r="DG117" t="inlineStr"/>
+      <c r="DH117" t="inlineStr"/>
+      <c r="DI117" t="inlineStr"/>
+      <c r="DJ117" t="inlineStr"/>
+      <c r="DK117" t="inlineStr"/>
+      <c r="DL117" t="inlineStr"/>
+      <c r="DM117" t="inlineStr"/>
+      <c r="DN117" t="inlineStr"/>
+      <c r="DO117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Samsung Epic 4G</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Also known as Samsung Galaxy S ProFor Sprint</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_epic_4g-3410.php</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, September</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>512MB</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Up to 300 h</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Up to 5 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>124 x 65 x 14 mm (4.88 x 2.56 x 0.55 in)</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>155 g (5.47 oz)</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr"/>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g/n; WiMAX, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>TouchWiz 3.0 UI</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>Corning Gorilla Glass</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>480 x 800 pixels, 5:3 ratio (~233 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>4.0 inches, 45.5 cm 2 (~56.5% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Super AMOLED</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr"/>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>Mobile TV MP4/DivX/WMV/H.264 player MP3/WAV/eAAC+/FLAC player Organizer Photo/video editor Document editor Voice memo/dial/commands Predictive text input (Swype)</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>HTML, Adobe Flash Lite</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity, compass</t>
+        </is>
+      </c>
+      <c r="BM118" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, September</t>
+        </is>
+      </c>
+      <c r="BN118" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO118" t="inlineStr"/>
+      <c r="BP118" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ118" t="inlineStr">
+        <is>
+          <t>5 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR118" t="inlineStr"/>
+      <c r="BS118" t="inlineStr">
+        <is>
+          <t>720p@30fps</t>
+        </is>
+      </c>
+      <c r="BT118" t="inlineStr"/>
+      <c r="BU118" t="inlineStr"/>
+      <c r="BV118" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW118" t="inlineStr">
+        <is>
+          <t>512MB 512MB RAM</t>
+        </is>
+      </c>
+      <c r="BX118" t="inlineStr"/>
+      <c r="BY118" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="BZ118" t="inlineStr"/>
+      <c r="CA118" t="inlineStr">
+        <is>
+          <t>About 200 EUR</t>
+        </is>
+      </c>
+      <c r="CB118" t="inlineStr">
+        <is>
+          <t>0.68 W/kg (head)     0.99 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC118" t="inlineStr"/>
+      <c r="CD118" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="CE118" t="inlineStr"/>
+      <c r="CF118" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG118" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CH118" t="inlineStr"/>
+      <c r="CI118" t="inlineStr"/>
+      <c r="CJ118" t="inlineStr"/>
+      <c r="CK118" t="inlineStr"/>
+      <c r="CL118" t="inlineStr">
+        <is>
+          <t>HSPA, EV-DO Rev. A 3.1 Mbps</t>
+        </is>
+      </c>
+      <c r="CM118" t="inlineStr">
+        <is>
+          <t>CDMA / HSPA / EVDO</t>
+        </is>
+      </c>
+      <c r="CN118" t="inlineStr"/>
+      <c r="CO118" t="inlineStr">
+        <is>
+          <t>1.0 GHz Cortex-A8</t>
+        </is>
+      </c>
+      <c r="CP118" t="inlineStr">
+        <is>
+          <t>Hummingbird</t>
+        </is>
+      </c>
+      <c r="CQ118" t="inlineStr">
+        <is>
+          <t>PowerVR SGX540</t>
+        </is>
+      </c>
+      <c r="CR118" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="CS118" t="inlineStr"/>
+      <c r="CT118" t="inlineStr">
+        <is>
+          <t>VGA</t>
+        </is>
+      </c>
+      <c r="CU118" t="inlineStr"/>
+      <c r="CV118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW118" t="inlineStr"/>
+      <c r="CX118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY118" t="inlineStr"/>
+      <c r="CZ118" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA118" t="inlineStr"/>
+      <c r="DB118" t="inlineStr"/>
+      <c r="DC118" t="inlineStr"/>
+      <c r="DD118" t="inlineStr"/>
+      <c r="DE118" t="inlineStr"/>
+      <c r="DF118" t="inlineStr"/>
+      <c r="DG118" t="inlineStr"/>
+      <c r="DH118" t="inlineStr"/>
+      <c r="DI118" t="inlineStr"/>
+      <c r="DJ118" t="inlineStr"/>
+      <c r="DK118" t="inlineStr"/>
+      <c r="DL118" t="inlineStr"/>
+      <c r="DM118" t="inlineStr"/>
+      <c r="DN118" t="inlineStr"/>
+      <c r="DO118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Samsung Acclaim</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Also known as Samsung R880</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_acclaim-3430.php</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Up to 450 h</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Up to 8 h</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>Optical trackpad</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>114 x 59 x 15 mm (4.49 x 2.32 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>130 g (4.59 oz)</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>2.1, A2DP</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr"/>
+      <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>320 x 480 pixels, 3:2 ratio (~180 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>3.2 inches, 30.5 cm 2 (~45.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>TFT,  256K colors</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr"/>
+      <c r="BA119" t="inlineStr"/>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>MP4/H.264 player MP3/WAV/eAAC+ player Organizer Document viewer Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM119" t="inlineStr">
+        <is>
+          <t>2010, June. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BN119" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO119" t="inlineStr"/>
+      <c r="BP119" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ119" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR119" t="inlineStr"/>
+      <c r="BS119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT119" t="inlineStr"/>
+      <c r="BU119" t="inlineStr"/>
+      <c r="BV119" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 4 GB included</t>
+        </is>
+      </c>
+      <c r="BW119" t="inlineStr"/>
+      <c r="BX119" t="inlineStr"/>
+      <c r="BY119" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="BZ119" t="inlineStr"/>
+      <c r="CA119" t="inlineStr">
+        <is>
+          <t>About 170 EUR</t>
+        </is>
+      </c>
+      <c r="CB119" t="inlineStr">
+        <is>
+          <t>0.29 W/kg (head)     0.98 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC119" t="inlineStr"/>
+      <c r="CD119" t="inlineStr"/>
+      <c r="CE119" t="inlineStr"/>
+      <c r="CF119" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG119" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CH119" t="inlineStr"/>
+      <c r="CI119" t="inlineStr"/>
+      <c r="CJ119" t="inlineStr"/>
+      <c r="CK119" t="inlineStr"/>
+      <c r="CL119" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="CM119" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="CN119" t="inlineStr"/>
+      <c r="CO119" t="inlineStr"/>
+      <c r="CP119" t="inlineStr"/>
+      <c r="CQ119" t="inlineStr"/>
+      <c r="CR119" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="CS119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT119" t="inlineStr"/>
+      <c r="CU119" t="inlineStr"/>
+      <c r="CV119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW119" t="inlineStr"/>
+      <c r="CX119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY119" t="inlineStr"/>
+      <c r="CZ119" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA119" t="inlineStr"/>
+      <c r="DB119" t="inlineStr"/>
+      <c r="DC119" t="inlineStr"/>
+      <c r="DD119" t="inlineStr"/>
+      <c r="DE119" t="inlineStr"/>
+      <c r="DF119" t="inlineStr"/>
+      <c r="DG119" t="inlineStr"/>
+      <c r="DH119" t="inlineStr"/>
+      <c r="DI119" t="inlineStr"/>
+      <c r="DJ119" t="inlineStr"/>
+      <c r="DK119" t="inlineStr"/>
+      <c r="DL119" t="inlineStr"/>
+      <c r="DM119" t="inlineStr"/>
+      <c r="DN119" t="inlineStr"/>
+      <c r="DO119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Samsung Intercept</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Also known as Samsung M910For Sprint</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_intercept-3429.php</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Up to 300 h</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Up to 5 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1500 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>Optical trackpad</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>113 x 56 x 15 mm (4.45 x 2.20 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>139 g (4.90 oz)</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr"/>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>GPS, A-GPS</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>microUSB 2.0</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g, hotspot (Android 2.2)</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr"/>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>240 x 400 pixels, 5:3 ratio (~146 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>3.2 inches, 29.1 cm 2 (~46.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr"/>
+      <c r="BA120" t="inlineStr"/>
+      <c r="BB120" t="inlineStr"/>
+      <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>MP4/H.264 player MP3/WAV/eAAC+ player Organizer Document viewer Bar code scanner Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr">
+        <is>
+          <t>Accelerometer</t>
+        </is>
+      </c>
+      <c r="BM120" t="inlineStr">
+        <is>
+          <t>2010, July. Released 2010, July</t>
+        </is>
+      </c>
+      <c r="BN120" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO120" t="inlineStr"/>
+      <c r="BP120" t="inlineStr"/>
+      <c r="BQ120" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR120" t="inlineStr"/>
+      <c r="BS120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT120" t="inlineStr"/>
+      <c r="BU120" t="inlineStr"/>
+      <c r="BV120" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW120" t="inlineStr"/>
+      <c r="BX120" t="inlineStr"/>
+      <c r="BY120" t="inlineStr">
+        <is>
+          <t>Gray Steel, Satin Pink</t>
+        </is>
+      </c>
+      <c r="BZ120" t="inlineStr"/>
+      <c r="CA120" t="inlineStr">
+        <is>
+          <t>About 150 EUR</t>
+        </is>
+      </c>
+      <c r="CB120" t="inlineStr">
+        <is>
+          <t>0.72 W/kg (head)     1.08 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC120" t="inlineStr"/>
+      <c r="CD120" t="inlineStr"/>
+      <c r="CE120" t="inlineStr"/>
+      <c r="CF120" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG120" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="CH120" t="inlineStr"/>
+      <c r="CI120" t="inlineStr"/>
+      <c r="CJ120" t="inlineStr"/>
+      <c r="CK120" t="inlineStr"/>
+      <c r="CL120" t="inlineStr">
+        <is>
+          <t>EV-DO Rev.0, 153.2 Kbps</t>
+        </is>
+      </c>
+      <c r="CM120" t="inlineStr">
+        <is>
+          <t>CDMA / EVDO</t>
+        </is>
+      </c>
+      <c r="CN120" t="inlineStr"/>
+      <c r="CO120" t="inlineStr"/>
+      <c r="CP120" t="inlineStr"/>
+      <c r="CQ120" t="inlineStr"/>
+      <c r="CR120" t="inlineStr">
+        <is>
+          <t>Android 2.1 (Eclair), upgradable to 2.2 (Froyo)</t>
+        </is>
+      </c>
+      <c r="CS120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT120" t="inlineStr"/>
+      <c r="CU120" t="inlineStr"/>
+      <c r="CV120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW120" t="inlineStr"/>
+      <c r="CX120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY120" t="inlineStr"/>
+      <c r="CZ120" t="inlineStr">
+        <is>
+          <t>QWERTY</t>
+        </is>
+      </c>
+      <c r="DA120" t="inlineStr"/>
+      <c r="DB120" t="inlineStr"/>
+      <c r="DC120" t="inlineStr"/>
+      <c r="DD120" t="inlineStr"/>
+      <c r="DE120" t="inlineStr"/>
+      <c r="DF120" t="inlineStr"/>
+      <c r="DG120" t="inlineStr"/>
+      <c r="DH120" t="inlineStr"/>
+      <c r="DI120" t="inlineStr"/>
+      <c r="DJ120" t="inlineStr"/>
+      <c r="DK120" t="inlineStr"/>
+      <c r="DL120" t="inlineStr"/>
+      <c r="DM120" t="inlineStr"/>
+      <c r="DN120" t="inlineStr"/>
+      <c r="DO120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Samsung F400</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_f400-2261.php</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, June</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>103.2</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>24MB</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Up to 620 h</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Up to 4 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 960 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>103.2 x 48.2 x 16.9 mm (4.06 x 1.90 x 0.67 in)</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>105 g (3.70 oz)</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>Stereo FM radio, RDS</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Dual slide design</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~182 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.0 cm 2 (~30.1% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr"/>
+      <c r="BA121" t="inlineStr"/>
+      <c r="BB121" t="inlineStr"/>
+      <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>MP3/AAC/eACC/WMA player Music recognition Predictive text input Photo editor Organizer</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>Yes + downloadable</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="BL121" t="inlineStr"/>
+      <c r="BM121" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, June</t>
+        </is>
+      </c>
+      <c r="BN121" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO121" t="inlineStr"/>
+      <c r="BP121" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ121" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR121" t="inlineStr"/>
+      <c r="BS121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT121" t="inlineStr"/>
+      <c r="BU121" t="inlineStr">
+        <is>
+          <t>30 dialed, 30 received, 30 missed calls</t>
+        </is>
+      </c>
+      <c r="BV121" t="inlineStr">
+        <is>
+          <t>microSDHC (dedicated slot), 1 GB included</t>
+        </is>
+      </c>
+      <c r="BW121" t="inlineStr">
+        <is>
+          <t>24MB</t>
+        </is>
+      </c>
+      <c r="BX121" t="inlineStr">
+        <is>
+          <t>1000 entries, Photo call</t>
+        </is>
+      </c>
+      <c r="BY121" t="inlineStr">
+        <is>
+          <t>Silver, Red</t>
+        </is>
+      </c>
+      <c r="BZ121" t="inlineStr"/>
+      <c r="CA121" t="inlineStr">
+        <is>
+          <t>About 100 EUR</t>
+        </is>
+      </c>
+      <c r="CB121" t="inlineStr">
+        <is>
+          <t>0.30 W/kg (head)     0.50 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC121" t="inlineStr">
+        <is>
+          <t>0.50 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD121" t="inlineStr"/>
+      <c r="CE121" t="inlineStr"/>
+      <c r="CF121" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG121" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="CH121" t="inlineStr"/>
+      <c r="CI121" t="inlineStr"/>
+      <c r="CJ121" t="inlineStr"/>
+      <c r="CK121" t="inlineStr"/>
+      <c r="CL121" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM121" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN121" t="inlineStr"/>
+      <c r="CO121" t="inlineStr"/>
+      <c r="CP121" t="inlineStr"/>
+      <c r="CQ121" t="inlineStr"/>
+      <c r="CR121" t="inlineStr"/>
+      <c r="CS121" t="inlineStr"/>
+      <c r="CT121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CU121" t="inlineStr"/>
+      <c r="CV121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW121" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="CX121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY121" t="inlineStr"/>
+      <c r="CZ121" t="inlineStr"/>
+      <c r="DA121" t="inlineStr"/>
+      <c r="DB121" t="inlineStr"/>
+      <c r="DC121" t="inlineStr"/>
+      <c r="DD121" t="inlineStr"/>
+      <c r="DE121" t="inlineStr"/>
+      <c r="DF121" t="inlineStr"/>
+      <c r="DG121" t="inlineStr"/>
+      <c r="DH121" t="inlineStr"/>
+      <c r="DI121" t="inlineStr"/>
+      <c r="DJ121" t="inlineStr"/>
+      <c r="DK121" t="inlineStr"/>
+      <c r="DL121" t="inlineStr"/>
+      <c r="DM121" t="inlineStr"/>
+      <c r="DN121" t="inlineStr"/>
+      <c r="DO121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Samsung J700</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_j700-2262.php</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, February</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>10MB</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 800 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr"/>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>99.5 x 48 x 14.8 mm (3.92 x 1.89 x 0.58 in)</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>92 g (3.25 oz)</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr"/>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>128 x 160 pixels (~102 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>2.0 inches, 12.6 cm 2 (~26.4% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>TFT, 65K colors</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr"/>
+      <c r="BA122" t="inlineStr"/>
+      <c r="BB122" t="inlineStr"/>
+      <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>MP4/3GP player/recorder MP3/AAC/AAC+/MIDI player BT printing Organizer Currency converter Voice memo Predictive text input</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS</t>
+        </is>
+      </c>
+      <c r="BL122" t="inlineStr"/>
+      <c r="BM122" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, February</t>
+        </is>
+      </c>
+      <c r="BN122" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO122" t="inlineStr"/>
+      <c r="BP122" t="inlineStr"/>
+      <c r="BQ122" t="inlineStr">
+        <is>
+          <t>1.3 MP</t>
+        </is>
+      </c>
+      <c r="BR122" t="inlineStr"/>
+      <c r="BS122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT122" t="inlineStr"/>
+      <c r="BU122" t="inlineStr">
+        <is>
+          <t>20 dialed, 20 received, 20 missed calls</t>
+        </is>
+      </c>
+      <c r="BV122" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW122" t="inlineStr">
+        <is>
+          <t>10MB</t>
+        </is>
+      </c>
+      <c r="BX122" t="inlineStr">
+        <is>
+          <t>1000 entries, Photocall</t>
+        </is>
+      </c>
+      <c r="BY122" t="inlineStr">
+        <is>
+          <t>Black, Pink</t>
+        </is>
+      </c>
+      <c r="BZ122" t="inlineStr"/>
+      <c r="CA122" t="inlineStr">
+        <is>
+          <t>About 60 EUR</t>
+        </is>
+      </c>
+      <c r="CB122" t="inlineStr">
+        <is>
+          <t>0.38 W/kg (head)     0.89 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC122" t="inlineStr">
+        <is>
+          <t>0.50 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD122" t="inlineStr"/>
+      <c r="CE122" t="inlineStr"/>
+      <c r="CF122" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG122" t="inlineStr"/>
+      <c r="CH122" t="inlineStr"/>
+      <c r="CI122" t="inlineStr"/>
+      <c r="CJ122" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="CK122" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="CL122" t="inlineStr"/>
+      <c r="CM122" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="CN122" t="inlineStr"/>
+      <c r="CO122" t="inlineStr"/>
+      <c r="CP122" t="inlineStr"/>
+      <c r="CQ122" t="inlineStr"/>
+      <c r="CR122" t="inlineStr"/>
+      <c r="CS122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT122" t="inlineStr"/>
+      <c r="CU122" t="inlineStr"/>
+      <c r="CV122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW122" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="CX122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY122" t="inlineStr"/>
+      <c r="CZ122" t="inlineStr"/>
+      <c r="DA122" t="inlineStr"/>
+      <c r="DB122" t="inlineStr"/>
+      <c r="DC122" t="inlineStr"/>
+      <c r="DD122" t="inlineStr"/>
+      <c r="DE122" t="inlineStr"/>
+      <c r="DF122" t="inlineStr"/>
+      <c r="DG122" t="inlineStr"/>
+      <c r="DH122" t="inlineStr"/>
+      <c r="DI122" t="inlineStr"/>
+      <c r="DJ122" t="inlineStr"/>
+      <c r="DK122" t="inlineStr"/>
+      <c r="DL122" t="inlineStr"/>
+      <c r="DM122" t="inlineStr"/>
+      <c r="DN122" t="inlineStr"/>
+      <c r="DO122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Samsung J630</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_j630-2323.php</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, March</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>100.7</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>40MB</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>About 50 EUR</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Up to 250 h</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Up to 3 h</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Removable battery</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>100.7 x 50.5 x 12.9 mm (3.96 x 1.99 x 0.51 in)</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>88 g (3.10 oz)</t>
+        </is>
+      </c>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr"/>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>External TFT display, 65K colors (96 x 96 pixels), 1.07 inches</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>176 x 220 pixels (~128 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>2.2 inches, 15.2 cm 2 (~30.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr"/>
+      <c r="BA123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr"/>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>MP4/3gp player Voice memo Document viewer (Word, Excel, PowerPoint, PDF) Organizer World clock Stopwatch Countdown timer</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML (NetFront 3.4)</t>
+        </is>
+      </c>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>Yes, MIDP 2.0</t>
+        </is>
+      </c>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr">
+        <is>
+          <t>SMS, EMS, MMS, Email</t>
+        </is>
+      </c>
+      <c r="BL123" t="inlineStr"/>
+      <c r="BM123" t="inlineStr">
+        <is>
+          <t>2008, February. Released 2008, March</t>
+        </is>
+      </c>
+      <c r="BN123" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO123" t="inlineStr"/>
+      <c r="BP123" t="inlineStr"/>
+      <c r="BQ123" t="inlineStr">
+        <is>
+          <t>2 MP</t>
+        </is>
+      </c>
+      <c r="BR123" t="inlineStr"/>
+      <c r="BS123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT123" t="inlineStr"/>
+      <c r="BU123" t="inlineStr">
+        <is>
+          <t>20 dialed, 20 received, 20 missed calls</t>
+        </is>
+      </c>
+      <c r="BV123" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW123" t="inlineStr">
+        <is>
+          <t>40MB</t>
+        </is>
+      </c>
+      <c r="BX123" t="inlineStr">
+        <is>
+          <t>Yes, 1000 entries</t>
+        </is>
+      </c>
+      <c r="BY123" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="BZ123" t="inlineStr"/>
+      <c r="CA123" t="inlineStr">
+        <is>
+          <t>About 50 EUR</t>
+        </is>
+      </c>
+      <c r="CB123" t="inlineStr"/>
+      <c r="CC123" t="inlineStr">
+        <is>
+          <t>0.31 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD123" t="inlineStr"/>
+      <c r="CE123" t="inlineStr"/>
+      <c r="CF123" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG123" t="inlineStr">
+        <is>
+          <t>UMTS 2100</t>
+        </is>
+      </c>
+      <c r="CH123" t="inlineStr"/>
+      <c r="CI123" t="inlineStr"/>
+      <c r="CJ123" t="inlineStr"/>
+      <c r="CK123" t="inlineStr"/>
+      <c r="CL123" t="inlineStr">
+        <is>
+          <t>Yes, 384 kbps</t>
+        </is>
+      </c>
+      <c r="CM123" t="inlineStr">
+        <is>
+          <t>GSM / UMTS</t>
+        </is>
+      </c>
+      <c r="CN123" t="inlineStr"/>
+      <c r="CO123" t="inlineStr"/>
+      <c r="CP123" t="inlineStr"/>
+      <c r="CQ123" t="inlineStr"/>
+      <c r="CR123" t="inlineStr"/>
+      <c r="CS123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CT123" t="inlineStr"/>
+      <c r="CU123" t="inlineStr"/>
+      <c r="CV123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CW123" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="CX123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY123" t="inlineStr"/>
+      <c r="CZ123" t="inlineStr"/>
+      <c r="DA123" t="inlineStr"/>
+      <c r="DB123" t="inlineStr"/>
+      <c r="DC123" t="inlineStr"/>
+      <c r="DD123" t="inlineStr"/>
+      <c r="DE123" t="inlineStr"/>
+      <c r="DF123" t="inlineStr"/>
+      <c r="DG123" t="inlineStr"/>
+      <c r="DH123" t="inlineStr"/>
+      <c r="DI123" t="inlineStr"/>
+      <c r="DJ123" t="inlineStr"/>
+      <c r="DK123" t="inlineStr"/>
+      <c r="DL123" t="inlineStr"/>
+      <c r="DM123" t="inlineStr"/>
+      <c r="DN123" t="inlineStr"/>
+      <c r="DO123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Samsung i560</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i560-2154.php</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2007, October. Released 2008, March</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>150MB</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Up to 360 h</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>Up to 4 h 30 min</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion battery</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr"/>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>103 x 51 x 15.9 mm (4.06 x 2.01 x 0.63 in)</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>111 g (3.92 oz)</t>
+        </is>
+      </c>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr"/>
+      <c r="AV124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~167 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>2.4 inches, 17.8 cm 2 (~34.0% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr"/>
+      <c r="BA124" t="inlineStr"/>
+      <c r="BB124" t="inlineStr"/>
+      <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>WMV/RV/MP4/3GP player MP3/WMA/WAV/RA/AAC/M4A player Organizer Document viewer (Word, Excel, PowerPoint, PDF)</t>
+        </is>
+      </c>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML, HTML, RSS feeds</t>
+        </is>
+      </c>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+      <c r="BM124" t="inlineStr">
+        <is>
+          <t>2007, October. Released 2008, March</t>
+        </is>
+      </c>
+      <c r="BN124" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO124" t="inlineStr"/>
+      <c r="BP124" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ124" t="inlineStr">
+        <is>
+          <t>3.15 MP</t>
+        </is>
+      </c>
+      <c r="BR124" t="inlineStr"/>
+      <c r="BS124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT124" t="inlineStr"/>
+      <c r="BU124" t="inlineStr"/>
+      <c r="BV124" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW124" t="inlineStr">
+        <is>
+          <t>150MB</t>
+        </is>
+      </c>
+      <c r="BX124" t="inlineStr"/>
+      <c r="BY124" t="inlineStr">
+        <is>
+          <t>Black, Silver</t>
+        </is>
+      </c>
+      <c r="BZ124" t="inlineStr"/>
+      <c r="CA124" t="inlineStr">
+        <is>
+          <t>About 110 EUR</t>
+        </is>
+      </c>
+      <c r="CB124" t="inlineStr">
+        <is>
+          <t>0.17 W/kg (head)     0.56 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC124" t="inlineStr">
+        <is>
+          <t>0.93 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD124" t="inlineStr"/>
+      <c r="CE124" t="inlineStr"/>
+      <c r="CF124" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG124" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="CH124" t="inlineStr"/>
+      <c r="CI124" t="inlineStr"/>
+      <c r="CJ124" t="inlineStr"/>
+      <c r="CK124" t="inlineStr"/>
+      <c r="CL124" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM124" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN124" t="inlineStr"/>
+      <c r="CO124" t="inlineStr">
+        <is>
+          <t>330 MHz ARM 1136</t>
+        </is>
+      </c>
+      <c r="CP124" t="inlineStr">
+        <is>
+          <t>TI OMAP 2430</t>
+        </is>
+      </c>
+      <c r="CQ124" t="inlineStr">
+        <is>
+          <t>PowerVR MBX</t>
+        </is>
+      </c>
+      <c r="CR124" t="inlineStr">
+        <is>
+          <t>Symbian OS 9.1, Series 60 v3.1 UI</t>
+        </is>
+      </c>
+      <c r="CS124" t="inlineStr"/>
+      <c r="CT124" t="inlineStr">
+        <is>
+          <t>QCIF videocall camera</t>
+        </is>
+      </c>
+      <c r="CU124" t="inlineStr"/>
+      <c r="CV124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW124" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="CX124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY124" t="inlineStr"/>
+      <c r="CZ124" t="inlineStr"/>
+      <c r="DA124" t="inlineStr"/>
+      <c r="DB124" t="inlineStr"/>
+      <c r="DC124" t="inlineStr"/>
+      <c r="DD124" t="inlineStr"/>
+      <c r="DE124" t="inlineStr"/>
+      <c r="DF124" t="inlineStr"/>
+      <c r="DG124" t="inlineStr"/>
+      <c r="DH124" t="inlineStr"/>
+      <c r="DI124" t="inlineStr"/>
+      <c r="DJ124" t="inlineStr"/>
+      <c r="DK124" t="inlineStr"/>
+      <c r="DL124" t="inlineStr"/>
+      <c r="DM124" t="inlineStr"/>
+      <c r="DN124" t="inlineStr"/>
+      <c r="DO124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Samsung i550</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Also version Samsung i550w with WLAN</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/samsung_i550-2115.php</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:30 UTC</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2007, August. Released 2008, February</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>150MB</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Up to 360 h</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Up to 8 h</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>Removable Li-Ion 1200 mAh battery</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>Trackball</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>115 x 53 x 13.8 mm (4.53 x 2.09 x 0.54 in)</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>Mini-SIM</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>109 g (3.84 oz)</t>
+        </is>
+      </c>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>2.0, A2DP</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>FM radio</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 b/g (Samsung i550w only)</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr"/>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>240 x 320 pixels, 4:3 ratio (~154 ppi density)</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>2.6 inches, 20.9 cm 2 (~34.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>TFT, 256K colors</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr"/>
+      <c r="BA125" t="inlineStr"/>
+      <c r="BB125" t="inlineStr"/>
+      <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>WMV/RV/MP4/3GP player MP3/WMA/WAV/RA/AAC/M4A player Organizer Document viewer (Word, Excel, PowerPoint, PDF)</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>WAP 2.0/xHTML</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr">
+        <is>
+          <t>2007, August. Released 2008, February</t>
+        </is>
+      </c>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t>Discontinued</t>
+        </is>
+      </c>
+      <c r="BO125" t="inlineStr"/>
+      <c r="BP125" t="inlineStr">
+        <is>
+          <t>LED flash</t>
+        </is>
+      </c>
+      <c r="BQ125" t="inlineStr">
+        <is>
+          <t>3.15 MP, AF</t>
+        </is>
+      </c>
+      <c r="BR125" t="inlineStr"/>
+      <c r="BS125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BT125" t="inlineStr"/>
+      <c r="BU125" t="inlineStr"/>
+      <c r="BV125" t="inlineStr">
+        <is>
+          <t>microSD (dedicated slot)</t>
+        </is>
+      </c>
+      <c r="BW125" t="inlineStr">
+        <is>
+          <t>150MB</t>
+        </is>
+      </c>
+      <c r="BX125" t="inlineStr"/>
+      <c r="BY125" t="inlineStr">
+        <is>
+          <t>Black, Silver</t>
+        </is>
+      </c>
+      <c r="BZ125" t="inlineStr"/>
+      <c r="CA125" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="CB125" t="inlineStr">
+        <is>
+          <t>0.32 W/kg (head)     0.41 W/kg (body)</t>
+        </is>
+      </c>
+      <c r="CC125" t="inlineStr">
+        <is>
+          <t>0.72 W/kg (head)</t>
+        </is>
+      </c>
+      <c r="CD125" t="inlineStr"/>
+      <c r="CE125" t="inlineStr"/>
+      <c r="CF125" t="inlineStr">
+        <is>
+          <t>GSM 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="CG125" t="inlineStr">
+        <is>
+          <t>HSDPA 2100</t>
+        </is>
+      </c>
+      <c r="CH125" t="inlineStr"/>
+      <c r="CI125" t="inlineStr"/>
+      <c r="CJ125" t="inlineStr"/>
+      <c r="CK125" t="inlineStr"/>
+      <c r="CL125" t="inlineStr">
+        <is>
+          <t>HSPA 3.6/0.384 Mbps</t>
+        </is>
+      </c>
+      <c r="CM125" t="inlineStr">
+        <is>
+          <t>GSM / HSPA</t>
+        </is>
+      </c>
+      <c r="CN125" t="inlineStr">
+        <is>
+          <t>Voice 73dB / Noise 66dB / Ring 78dB</t>
+        </is>
+      </c>
+      <c r="CO125" t="inlineStr">
+        <is>
+          <t>330 MHz ARM 1136</t>
+        </is>
+      </c>
+      <c r="CP125" t="inlineStr">
+        <is>
+          <t>TI OMAP 2430</t>
+        </is>
+      </c>
+      <c r="CQ125" t="inlineStr">
+        <is>
+          <t>PowerVR MBX</t>
+        </is>
+      </c>
+      <c r="CR125" t="inlineStr">
+        <is>
+          <t>Symbian OS 9.2, Series 60 v3.1 UI</t>
+        </is>
+      </c>
+      <c r="CS125" t="inlineStr"/>
+      <c r="CT125" t="inlineStr">
+        <is>
+          <t>VGA videocall camera</t>
+        </is>
+      </c>
+      <c r="CU125" t="inlineStr"/>
+      <c r="CV125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CW125" t="inlineStr">
+        <is>
+          <t>Vibration; Downloadable polyphonic, MP3 ringtones</t>
+        </is>
+      </c>
+      <c r="CX125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY125" t="inlineStr"/>
+      <c r="CZ125" t="inlineStr"/>
+      <c r="DA125" t="inlineStr"/>
+      <c r="DB125" t="inlineStr">
+        <is>
+          <t>Noise -90.8dB / Crosstalk -89.1dB</t>
+        </is>
+      </c>
+      <c r="DC125" t="inlineStr"/>
+      <c r="DD125" t="inlineStr"/>
+      <c r="DE125" t="inlineStr"/>
+      <c r="DF125" t="inlineStr"/>
+      <c r="DG125" t="inlineStr"/>
+      <c r="DH125" t="inlineStr"/>
+      <c r="DI125" t="inlineStr"/>
+      <c r="DJ125" t="inlineStr"/>
+      <c r="DK125" t="inlineStr"/>
+      <c r="DL125" t="inlineStr"/>
+      <c r="DM125" t="inlineStr"/>
+      <c r="DN125" t="inlineStr"/>
+      <c r="DO125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gsmarena_new_2026-06-03.xlsx
+++ b/gsmarena_new_2026-06-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,36 @@
           <t>Misc_Models</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Main Camera_Single</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Network_2</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Main Camera_Penta</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Selfie camera_Features</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -694,10 +724,8 @@
           <t>2026-06-03 14:07 UTC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E2" t="n">
+        <v>2025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -909,6 +937,12 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -931,10 +965,8 @@
           <t>2026-06-03 14:07 UTC</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2025</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1146,6 +1178,761 @@
           <t>ZL.H01SI.002</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ulefone Tab A7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/ulefone_tab_a7-10994.php</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:33 UTC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2021, May 27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 5, 7, 8, 20</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HSPA 21.1/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2021, May 27</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, May 27</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>243.6 x 162.4 x 7.9 mm (9.59 x 6.39 x 0.31 in)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>566 g (1.25 lb)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>10.1 inches, 295.8 cm 2 (~74.8% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1200 x 1920 pixels, 16:10 ratio (~224 ppi density)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Unisoc SC9863A (28 nm)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Octa-core (4x1.6 GHz Cortex-A55 &amp; 4x1.2 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>IMG8322</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>64GB 4GB RAM</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>LED flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>5 MP</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, BDS</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Accelerometer, proximity</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Li-Po 7680 mAh</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>10W wired</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Space Gray</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>About 130 EUR</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>eMMC 5.1</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>13 MP</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ulefone Armor 11T 5G</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/ulefone_armor_11t_5g-10974.php</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:33 UTC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2021, May 29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, June 07</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>GSM / CDMA / HSPA / EVDO / LTE / 5G</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 34, 38, 39, 40, 41, 66</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1, 3, 5, 8, 20, 28, 38, 41, 77, 78, 79 SA/NSA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>HSPA, LTE, 5G</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2021, May 29</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, June 07</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>163.8 x 81.6 x 14.2 mm (6.45 x 3.21 x 0.56 in)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>293 g (10.34 oz)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>IP68/IP69K dust tight and water resistant (high pressure water jets; immersible up to 1.5m for 30 min) Drop resistant up to 1.2m MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6.1 inches, 91.3 cm 2 (~68.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>720 x 1560 pixels, 19.5:9 ratio (~282 ppi density)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Mediatek Dimensity 800 (7 nm)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A76 &amp; 4x2.0 GHz Cortex-A55)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Mali-G57 MP4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>256GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Dual-LED dual-tone flash, HDR, panorama</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>4K@30fps, 1080p@30fps</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>5.0, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass, baroceptor</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Li-Po 5200 mAh</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>18W wired 10W wireless</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>About 590 EUR</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Front glass, aluminum back with rubber, aluminum frame</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Oleophobic coating</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>UFS 2.1</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>CDMA 800 / 1900 &amp; TD-SCDMA</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>CDMA2000 1xEV-DO</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>48 MP, f/1.8, 26mm (wide), 1/2.0", 0.8µm, PDAF FLIR thermal camera (Lepton module) 5 MP 2 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>HDR, panorama</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ulefone Armor 8 Pro</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.gsmarena.com/ulefone_armor_8_pro-10898.php</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:33 UTC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2021, April 28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GSM / HSPA / LTE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GSM 850 / 900 / 1800 / 1900</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 7, 8, 12, 13, 17, 18, 19, 20, 25, 26, 28, 66</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>HSPA 42.2/11.5 Mbps, LTE Cat7 300/150 Mbps</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2021, April 28</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Available. Released 2021, April 28</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>166 x 81.8 x 15 mm (6.54 x 3.22 x 0.59 in)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>282 g (9.95 oz)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Nano-SIM + Nano-SIM</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>IP68 dust tight and water resistant (immersible up to 1.5m for 30 min) Drop resistant up to 1.2m MIL-STD-810G compliant</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>IPS LCD</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6.1 inches, 91.3 cm 2 (~67.3% screen-to-body ratio)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>720 x 1560 pixels, 19.5:9 ratio (~282 ppi density)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Android 11</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Mediatek MT6771 Helio P60 (12 nm)</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Octa-core (4x2.0 GHz Cortex-A73 &amp; 4x2.0 GHz Cortex-A53)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Mali-G72 MP3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>microSDXC (uses shared SIM slot)</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>128GB 6GB RAM, 128GB 8GB RAM</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>16 MP, f/2.2, (wide), PDAF 5 MP (macro) Auxiliary lens</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>LED flash, Panorama, HDR</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>8 MP, f/2.2</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1080p@30fps</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Wi-Fi 802.11 a/b/g/n/ac, Wi-Fi Direct</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>4.2, A2DP, LE</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>GPS, GLONASS, GALILEO, BDS</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>FM radio, RDS, recording</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>USB Type-C 2.0, OTG</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Fingerprint (side-mounted), accelerometer, gyro, proximity, compass</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Li-Po 5580 mAh</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>15W wired</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Black, Orange, Red</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>About 190 EUR</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Front glass, aluminum back with rubber, aluminum frame</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Scratch-resistant glass, oleophobic coating</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
